--- a/workspaces/nasdaq_hourly_24hrs/volatility/bb_pct_20.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/volatility/bb_pct_20.xlsx
@@ -625,158 +625,158 @@
         <v>26</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-17.17662246120605</v>
+        <v>-17.14235713645416</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-6.0498775664989</v>
+        <v>-6.016460799248158</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-11.36322743445859</v>
+        <v>-11.33369272804691</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>3.196893417707798</v>
+        <v>3.236126155127472</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>10.47610888169416</v>
+        <v>10.54930494527892</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>10.67685446815025</v>
+        <v>10.74734686010741</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>9.886525601973965</v>
+        <v>9.955260487614545</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1.944461463616541</v>
+        <v>2.013525574744527</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>9.647278390549403</v>
+        <v>9.716372495034292</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>5.015605107497649</v>
+        <v>5.085650897801301</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>1.465910940817203</v>
+        <v>1.535653723154994</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-2.660521805507564</v>
+        <v>-2.590412483729445</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.008831051378841437</v>
+        <v>0.08035052610105708</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>3.618369440645395</v>
+        <v>3.690207461436891</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.9019738255935508</v>
+        <v>-0.8293086111613377</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.2881009991975816</v>
+        <v>-0.2161070480006018</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>3.417428652068033</v>
+        <v>3.489629993834619</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-2.082919599875275</v>
+        <v>-4.302250570928855</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-1.867112642188118</v>
+        <v>-4.080426437924999</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-1.680824531647083</v>
+        <v>-3.887524379042716</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-2.223932668117179</v>
+        <v>-4.45471970262367</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-6.144360431775496</v>
+        <v>-6.076153185432965</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-2.026489525953515</v>
+        <v>-1.956766514221407</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-2.103013945119216</v>
+        <v>-2.033159597411057</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.07278</t>
+          <t>X ≈ -0.07279</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>45</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>8.499103545825029</v>
+        <v>8.53223792019655</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-5.090848908297382</v>
+        <v>-5.059023598115481</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4.52530020625359</v>
+        <v>4.563201463520066</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3.816240760084931</v>
+        <v>3.854611233540162</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1.242599736623184</v>
+        <v>1.30895907853872</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1.428649946066457</v>
+        <v>1.494415081055756</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-1.552930924500821</v>
+        <v>-1.486856721672552</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-4.043466021795552</v>
+        <v>-3.977041839296177</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-8.429918469233236</v>
+        <v>-8.363522496244244</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-9.203054713707154</v>
+        <v>-9.135722932239787</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-15.5763351580981</v>
+        <v>-15.50930438044887</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-9.212562870361914</v>
+        <v>-9.145139053193546</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-8.120612236031555</v>
+        <v>-8.051834774393313</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-6.127295497994766</v>
+        <v>-6.058209667285908</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-9.003990587092048</v>
+        <v>-8.934102388017223</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-8.412609804396531</v>
+        <v>-8.343367088614556</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-10.76810305698128</v>
+        <v>-10.69866294145762</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-13.09163284287727</v>
+        <v>-13.02597471671612</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-10.65700946342604</v>
+        <v>-10.59402608070526</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-10.47342745767562</v>
+        <v>-10.41051264668559</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-11.01922492734739</v>
+        <v>-10.95602581148946</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-11.09851055310225</v>
+        <v>-11.0318625422418</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-10.8271993500511</v>
+        <v>-10.75748013632182</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-13.12865497076024</v>
+        <v>-13.05880062305346</v>
       </c>
     </row>
     <row r="8">
@@ -789,76 +789,76 @@
         <v>44</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-8.171560223549889</v>
+        <v>-8.138549347387794</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-8.504234242233672</v>
+        <v>-8.473538377731849</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-5.416745954419468</v>
+        <v>-5.384981457255577</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-6.128745713128609</v>
+        <v>-6.096522244537844</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-13.27690083850539</v>
+        <v>-13.21958248314956</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-6.310897980095369</v>
+        <v>-6.247561560755749</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-7.082581424487422</v>
+        <v>-7.016547946797431</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-7.361942303284302</v>
+        <v>-7.295545024238983</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-5.058805882501922</v>
+        <v>-4.992402718296695</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-10.35945768946569</v>
+        <v>-10.29214044675414</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-10.088602057504</v>
+        <v>-10.02155800250219</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-14.9011953463152</v>
+        <v>-14.8338011365347</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-4.69523094611246</v>
+        <v>-4.626448525899228</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-9.451965522370244</v>
+        <v>-9.382895707152116</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-14.64776069070701</v>
+        <v>-14.57789323043008</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-16.32673113028104</v>
+        <v>-16.2575113404757</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-14.19667509000092</v>
+        <v>-14.1272456883554</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-12.03212285276507</v>
+        <v>-11.96624691795224</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-14.08558277013346</v>
+        <v>-14.02491065442186</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-11.63325227009709</v>
+        <v>-11.57123439918951</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-12.17948131383518</v>
+        <v>-12.11718935762563</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-9.987902525854686</v>
+        <v>-9.921003282548668</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-9.71634223392347</v>
+        <v>-9.646623424002705</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-9.795321637426902</v>
+        <v>-9.725467289719624</v>
       </c>
     </row>
     <row r="9">
@@ -871,158 +871,158 @@
         <v>63</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-10.75180654506692</v>
+        <v>-10.7188261125012</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-11.08439628791139</v>
+        <v>-11.05463394925863</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-6.204562280786142</v>
+        <v>-6.173421790121964</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.9747638343834737</v>
+        <v>1.011374962039724</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.9670998223230285</v>
+        <v>-0.9022306491816465</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.7969525632970473</v>
+        <v>0.8624990239767243</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-4.711836472270583</v>
+        <v>-4.64580221928027</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-9.731357822634372</v>
+        <v>-9.664986468170909</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-11.27354284246593</v>
+        <v>-11.20718297379227</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-12.04728409562476</v>
+        <v>-11.97998697559382</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-11.77707957331142</v>
+        <v>-11.71005393446568</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-4.147252186349547</v>
+        <v>-4.079826328431338</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.5219773196964539</v>
+        <v>-0.4531877994014408</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-3.909666320316759</v>
+        <v>-3.840586804025989</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-7.735600782930334</v>
+        <v>-7.665722039934728</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-7.144013930142435</v>
+        <v>-7.074779253220939</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-4.110894277330374</v>
+        <v>-4.041450367313828</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-4.215583502230658</v>
+        <v>-4.147352736946694</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.8302203168744811</v>
+        <v>-0.7614416128556698</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-3.814385546221523</v>
+        <v>-3.747657559805148</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-1.18665350608979</v>
+        <v>-1.117654431214767</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>0.3232374825894482</v>
+        <v>0.393299201765501</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-2.57564398412228</v>
+        <v>-2.505923338263813</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>0.5221386800337768</v>
+        <v>0.591993027740692</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ 0.05273</t>
+          <t>X ≈ 0.05271</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>68</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-2.188270410713514</v>
+        <v>-2.271790997385814</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>12.09523036264046</v>
+        <v>10.54951875795764</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4.817029085334276</v>
+        <v>4.042271562170207</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4.107544347890219</v>
+        <v>3.325734663168483</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.8206761763044881</v>
+        <v>0.8866742700550674</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.005742720733572</v>
+        <v>1.071361053684051</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-1.226471197467191</v>
+        <v>-1.160431387982726</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.503565200015544</v>
+        <v>-1.437163468907883</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-5.855571984789016</v>
+        <v>-5.789199851510013</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-5.162664619978479</v>
+        <v>-5.095349417172656</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.9596747861954</v>
+        <v>-1.892619057631386</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>3.624627842319434</v>
+        <v>3.692075026930766</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.503827145334661</v>
+        <v>2.572619045011528</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.6497112604509425</v>
+        <v>-0.5806297882339351</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>3.094944048079867</v>
+        <v>3.164845583375779</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>5.157620598726346</v>
+        <v>5.226878656528854</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>6.493142132463362</v>
+        <v>6.56260252750802</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>3.452041925468727</v>
+        <v>3.522701498251593</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.7312816793660133</v>
+        <v>0.8010425907335517</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-2.019110118264763</v>
+        <v>-1.951327409387197</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>0.3758467995162107</v>
+        <v>0.4458180839764196</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-2.639366351774989</v>
+        <v>-2.570263963108687</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.8954783497920005</v>
+        <v>-0.825758091177164</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>0.4987960096315831</v>
+        <v>0.5686503573391946</v>
       </c>
     </row>
     <row r="11">
@@ -1035,76 +1035,76 @@
         <v>81</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>8.005901074294108</v>
+        <v>6.722776782166214</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.537439820592908</v>
+        <v>0.9078842198335408</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-3.573628693783817</v>
+        <v>-4.226093412260084</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.6232224272183799</v>
+        <v>0.6600128869627397</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2.194445366745903</v>
+        <v>-2.130445666285318</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2.901663920371618</v>
+        <v>2.967929403800852</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.551403646804808</v>
+        <v>-1.485383640343962</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-4.286230207418058</v>
+        <v>-4.219862437751701</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.786967842681726</v>
+        <v>-1.720590535314315</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.09832315578105977</v>
+        <v>-0.03099791015738163</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.405334589615713</v>
+        <v>1.472392715141552</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>4.818385925250766</v>
+        <v>4.885828030671092</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-4.918032299943853</v>
+        <v>-4.849279612939036</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.446332661523186</v>
+        <v>-1.377263824707555</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>1.59123718712565</v>
+        <v>1.661126375631341</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-1.510723504355234</v>
+        <v>-1.44148912974304</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-6.575687772684738</v>
+        <v>-6.506260897955251</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-1.750165442853714</v>
+        <v>-1.681195068562225</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-2.766936892810598</v>
+        <v>-2.699490322525477</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>3.583607308978522</v>
+        <v>3.655043369293239</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>5.508705221543472</v>
+        <v>5.582092162299837</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>4.200766911749149</v>
+        <v>4.272098773775461</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>5.710913183536185</v>
+        <v>5.78063509692285</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>6.871345029240054</v>
+        <v>6.941199376947033</v>
       </c>
     </row>
     <row r="12">
@@ -1117,76 +1117,76 @@
         <v>102</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.7272645353822895</v>
+        <v>-0.695186116701251</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.8875388810054687</v>
+        <v>0.9222908333897024</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-2.489908719918326</v>
+        <v>-2.45832528445488</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-2.227930967034723</v>
+        <v>-2.194051229369038</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.616060576723214</v>
+        <v>-1.551766550227306</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.432821148434748</v>
+        <v>-1.368019257339064</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.225858246290009</v>
+        <v>-1.159859804355186</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.5267779964218278</v>
+        <v>-0.4604101435532257</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>6.347100259419136</v>
+        <v>6.413506047085249</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>10.46093530662237</v>
+        <v>10.52830125985761</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>9.761274925599452</v>
+        <v>9.828359866702392</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>7.531403957621265</v>
+        <v>7.598845819981506</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>11.29992231678954</v>
+        <v>11.36872703873046</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>11.08298315772327</v>
+        <v>11.1520857929433</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>9.451561817317476</v>
+        <v>9.521466136481031</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>11.0271649574273</v>
+        <v>11.09642457746628</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>9.918054331556775</v>
+        <v>9.987510241087804</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>11.77071536957614</v>
+        <v>11.84431078070261</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>12.96520470306107</v>
+        <v>13.04336157777009</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>12.17716879265477</v>
+        <v>12.2546589939077</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>12.61795981912469</v>
+        <v>12.69645860550477</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>13.52606558561683</v>
+        <v>13.60069081499731</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>13.80532708410983</v>
+        <v>13.87505151335328</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>12.75369797041601</v>
+        <v>12.82355231812351</v>
       </c>
     </row>
     <row r="13">
@@ -1199,158 +1199,158 @@
         <v>112</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>5.631366847106079</v>
+        <v>5.672456936714276</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.688676415563741</v>
+        <v>-2.658961674066788</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-2.358315899063157</v>
+        <v>-2.326832900318557</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.363195237142698</v>
+        <v>1.400937422278773</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2.772264534551013</v>
+        <v>2.839967967973735</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.5897644594328852</v>
+        <v>-0.5241766009867064</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.366417867505156</v>
+        <v>-1.299730321377176</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.1300471559759302</v>
+        <v>0.1971178757177796</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.1722828754399899</v>
+        <v>0.2393528756466168</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.2840314492917244</v>
+        <v>0.3520551615677903</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.109523309540819</v>
+        <v>-2.041784793073965</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-6.8398429883229</v>
+        <v>-6.771750468986539</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.740914712572341</v>
+        <v>-1.671431177334391</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.964265570373122</v>
+        <v>-1.894472956347002</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.8474160360016825</v>
+        <v>-0.77679476188964</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-4.705180209549518</v>
+        <v>-4.635217063121431</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-4.841368553427742</v>
+        <v>-4.771196430078518</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-5.838447030167416</v>
+        <v>-5.770310363043748</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-4.728942957287963</v>
+        <v>-4.662420404287225</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-2.22923735236914</v>
+        <v>-2.689947883355003</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.9888632485006568</v>
+        <v>-1.451848711748717</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-1.065034096805071</v>
+        <v>-1.528001391516462</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-2.575724919929094</v>
+        <v>-3.036173781159576</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-4.438178780284041</v>
+        <v>-4.368324432576763</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ 0.2201</t>
+          <t>X ≈ 0.22</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>113</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-14.3100887304732</v>
+        <v>-14.29809497354682</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-8.496896124502292</v>
+        <v>-8.476179327405106</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-7.332068892272162</v>
+        <v>-7.308331541637095</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-9.813664211601669</v>
+        <v>-9.787951475687493</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-12.33210967571877</v>
+        <v>-12.778114265265</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-5.97817450553768</v>
+        <v>-6.40980530764103</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-4.123043475173702</v>
+        <v>-4.559188548095491</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.257726860220323</v>
+        <v>-2.203406191329847</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.591665529867498</v>
+        <v>-2.535479456451014</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.281086169093193</v>
+        <v>-0.6742974292686625</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.5552477662231965</v>
+        <v>-0.399199256237452</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.2772136103405742</v>
+        <v>-0.1686088637491423</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.609364664221701</v>
+        <v>-2.540625695437704</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.065720075895506</v>
+        <v>-0.9966656282919004</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.04268528312015718</v>
+        <v>0.1125603398560955</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.6370796876777476</v>
+        <v>0.7063153395712192</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-2.147677026403677</v>
+        <v>-2.078239594799072</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.4852259467320792</v>
+        <v>-0.415812562332448</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-2.036803497921468</v>
+        <v>-1.96891418803402</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-1.850292139011287</v>
+        <v>-1.782955856350846</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-4.161607769508812</v>
+        <v>-4.096051398188571</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.7017949469765554</v>
+        <v>-0.6320743507483115</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.4272810326752676</v>
+        <v>-0.3575996382662581</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-1.388241991409203</v>
+        <v>-1.318387643701925</v>
       </c>
     </row>
     <row r="15">
@@ -1360,79 +1360,79 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.777094030607564</v>
+        <v>-2.256728442464151</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>4.536716148058474</v>
+        <v>5.143205918488619</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.116743675324983</v>
+        <v>2.7111854383771</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.939647404763775</v>
+        <v>1.994109191222783</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.6149654103272155</v>
+        <v>0.6813950881120832</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-2.065174675935047</v>
+        <v>-2.021187340369316</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-8.037367823748163</v>
+        <v>-8.612277751182049</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-8.314545567905284</v>
+        <v>-8.339449859893435</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-8.27371795356359</v>
+        <v>-8.297042239889457</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-10.00527706605558</v>
+        <v>-10.04559677307758</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-9.735108224094731</v>
+        <v>-9.210274758391861</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-8.100648629008489</v>
+        <v>-7.552471382577863</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-6.34968886252296</v>
+        <v>-5.769141167105694</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-6.573020963011921</v>
+        <v>-5.991960741920764</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-4.354849501139469</v>
+        <v>-3.744816525543875</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-5.681567106857187</v>
+        <v>-5.090600027983676</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-6.77771398849341</v>
+        <v>-6.195654657650842</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-6.882639684406435</v>
+        <v>-6.302898794780205</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-2.826669715279216</v>
+        <v>-2.209170977859685</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-2.640203121485406</v>
+        <v>-2.023379875018627</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-2.223399974967798</v>
+        <v>-1.595836603103287</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-3.261047511005088</v>
+        <v>-2.642556350920152</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-1.065217349038619</v>
+        <v>-0.4263340656225694</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>0.7816014394963915</v>
+        <v>1.439581253969692</v>
       </c>
     </row>
     <row r="16">
@@ -1442,79 +1442,79 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.791995583389074</v>
+        <v>1.362534326896238</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-4.446712674707406</v>
+        <v>-4.835749292602621</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-4.206082086493147</v>
+        <v>-4.607660290231635</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-5.764184270355472</v>
+        <v>-6.159618083753266</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-8.661828221450094</v>
+        <v>-9.011626578754026</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-4.25715062389628</v>
+        <v>-4.632814721395889</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-5.034632507917536</v>
+        <v>-5.410713153664233</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-4.470734496301631</v>
+        <v>-4.852895698527412</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.2101853760544685</v>
+        <v>-0.6225377195409578</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-3.519646214696188</v>
+        <v>-3.913913543809329</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-3.246401933211864</v>
+        <v>-3.639211561332367</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-4.372855134890997</v>
+        <v>-4.756986147015766</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-5.504207532016203</v>
+        <v>-5.884858709515719</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-4.883555807157315</v>
+        <v>-5.271147538309251</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-7.240140486505474</v>
+        <v>-7.612819141540868</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-6.645855240458395</v>
+        <v>-7.019360631299541</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-6.272341022531371</v>
+        <v>-7.157827080159549</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-2.992936213279542</v>
+        <v>-3.907606703392517</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-4.469604928981205</v>
+        <v>-5.370549087667783</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-2.591027709379667</v>
+        <v>-3.502258024382797</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-5.673984743975964</v>
+        <v>-6.066751182527284</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-1.518446654092294</v>
+        <v>-1.940916471667471</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-1.244385768920246</v>
+        <v>-1.666441759185417</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-3.863118247596589</v>
+        <v>-4.263282415770043</v>
       </c>
     </row>
     <row r="17">
@@ -1527,76 +1527,76 @@
         <v>105</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-3.263461367060557</v>
+        <v>-3.23681296414594</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>2.086705565096146</v>
+        <v>2.122863282235905</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3.465820513937388</v>
+        <v>3.505423723970985</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.09780076579831842</v>
+        <v>-0.0627509273176301</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.423350724208198</v>
+        <v>-1.361828657507004</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.633802743148628</v>
+        <v>-2.108837994291392</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.380359544473322</v>
+        <v>0.8990830154859353</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>4.893725152536227</v>
+        <v>4.416063307570717</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>2.09209860898757</v>
+        <v>1.613654846069224</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.313794005712332</v>
+        <v>1.382594588338584</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>5.385706334598247</v>
+        <v>5.457354732242834</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>4.157296791569941</v>
+        <v>4.226950518203154</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2.077943685605284</v>
+        <v>2.147624124090143</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2.806549630128366</v>
+        <v>2.876553004269489</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>4.995037678095251</v>
+        <v>5.065884530583013</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>7.116763688188009</v>
+        <v>6.616192774196293</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>6.032248982995981</v>
+        <v>5.531228960000917</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>6.877824324825283</v>
+        <v>6.381247457396</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>7.09339650023211</v>
+        <v>6.602442754720521</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>8.230379192812165</v>
+        <v>8.313329999444349</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>7.691397802954334</v>
+        <v>7.770783831478319</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>1.908934304190403</v>
+        <v>1.980652155783503</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>3.136359460330844</v>
+        <v>3.207507820646725</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>2.109440267335003</v>
+        <v>2.179294615042281</v>
       </c>
     </row>
     <row r="18">
@@ -1606,407 +1606,407 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>10.0308351346813</v>
+        <v>9.971388830261176</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>5.115505134876841</v>
+        <v>5.10336326039576</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.2281662788463379</v>
+        <v>0.2698124572936678</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-3.923754645474268</v>
+        <v>-3.842018752598541</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-3.150801868793287</v>
+        <v>-3.042099469529312</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.4782946676672992</v>
+        <v>0.5424057324663849</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>3.131826183734809</v>
+        <v>3.173460277226553</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.5823198646937371</v>
+        <v>-0.5045204743441971</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.750858573044859</v>
+        <v>1.803033520598397</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.320691813580005</v>
+        <v>-1.234164735730609</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-3.336625990403498</v>
+        <v>-3.227621595693535</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>2.111718092253341</v>
+        <v>2.161249353438656</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>5.566242050419795</v>
+        <v>5.574123921746484</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>7.6408893868607</v>
+        <v>7.623303965866853</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>5.83056864291374</v>
+        <v>5.835193715270769</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>5.282030135392723</v>
+        <v>5.296641616051588</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>7.441164287868645</v>
+        <v>7.435824954503005</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>5.042091491956484</v>
+        <v>5.062200730869634</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>9.85328568005442</v>
+        <v>9.825618388610529</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>3.158492102820098</v>
+        <v>3.194282380396729</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>2.147851366409249</v>
+        <v>1.515372576067065</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>3.221263817557364</v>
+        <v>2.575890251021598</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-1.098344597785378</v>
+        <v>-1.695089581951159</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.0252066948981593</v>
+        <v>-0.6345581988105309</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 0.4293</t>
+          <t>X ≈ 0.4292</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.914174769991618</v>
+        <v>-1.861129273763865</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>3.335952673497069</v>
+        <v>3.34500390640634</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>3.711536354383256</v>
+        <v>3.723252780288888</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>6.710210844769158</v>
+        <v>6.696928729876831</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>9.118777785679157</v>
+        <v>9.11916621828648</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>5.606755597317509</v>
+        <v>5.628274455331528</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>4.808434211025926</v>
+        <v>4.839512733148176</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.727267334782297</v>
+        <v>1.784267284151134</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.950324904879984</v>
+        <v>-1.865261512954447</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>2.455485467323996</v>
+        <v>1.965358761475912</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.801471648061323</v>
+        <v>1.318857413877033</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.5881524457414855</v>
+        <v>0.1144300090147325</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.3821030432036423</v>
+        <v>-0.09840509138970788</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>3.895221035857197</v>
+        <v>3.9257880377614</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>4.719314640956703</v>
+        <v>4.188374625525931</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>6.251424764714635</v>
+        <v>5.7128206571806</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>7.049563654237062</v>
+        <v>6.505136111282113</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>6.945321390520974</v>
+        <v>6.403716365524247</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>5.298461690868471</v>
+        <v>5.322251385243511</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>5.488099519816302</v>
+        <v>5.509097195211751</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>0.2703954496358563</v>
+        <v>0.3369213976158818</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>2.997619174489351</v>
+        <v>3.038853213984559</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>1.027676109583325</v>
+        <v>0.5355501486888343</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-4.655134721539056</v>
+        <v>-5.095837660089998</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.4711</t>
+          <t>X ≈ 0.471</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-4.216053459058202</v>
+        <v>-4.136700692962968</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-7.605048469570583</v>
+        <v>-7.495916364808522</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-7.02391720200378</v>
+        <v>-6.913890420920218</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-10.79511285207875</v>
+        <v>-10.65038988276581</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-5.058834475090919</v>
+        <v>-4.935783775464877</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-7.917607107720848</v>
+        <v>-7.775222011266408</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-11.75253326997559</v>
+        <v>-11.56955467713949</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-4.908733648714694</v>
+        <v>-4.789937995753093</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-4.865784447286281</v>
+        <v>-4.74880818627522</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-3.610547592070787</v>
+        <v>-3.503733760906108</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-6.392156762274482</v>
+        <v>-6.254470364676301</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-9.73285090383002</v>
+        <v>-9.557390612292359</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-10.87021025478187</v>
+        <v>-10.67894450318191</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-12.11531681414584</v>
+        <v>-11.90852704323028</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-10.74116084709848</v>
+        <v>-10.55401435058354</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-8.101780468793493</v>
+        <v>-7.946837903681612</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-8.237222137654278</v>
+        <v>-8.084526429593829</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-12.42096106323039</v>
+        <v>-12.23370733574838</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-15.26008527072492</v>
+        <v>-15.04811898512686</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-16.08980974059918</v>
+        <v>-15.87137418526029</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-14.60261889293597</v>
+        <v>-14.39371833302385</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-16.10900473012596</v>
+        <v>-16.48976631463496</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-13.79449220745632</v>
+        <v>-14.19508958195112</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-10.81572980069198</v>
+        <v>-11.24061880487114</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.513</t>
+          <t>X ≈ 0.5129</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>98</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.164761613832241</v>
+        <v>-1.132488199758185</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.501120121408917</v>
+        <v>-1.468522492503013</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.956593824593966</v>
+        <v>-2.923308133476986</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.638845114627031</v>
+        <v>-1.604005969267874</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.9901183774695568</v>
+        <v>-0.9255545915831362</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.2228726870424751</v>
+        <v>0.2882283887033807</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-3.615248539226101</v>
+        <v>-3.55117656899877</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.857923520832401</v>
+        <v>-1.792521017316083</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.814830131899967</v>
+        <v>-1.749357176207177</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.595369169286272</v>
+        <v>-2.529398653818987</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.322490120988931</v>
+        <v>-2.254919846858577</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.606155922024847</v>
+        <v>-2.536184239097764</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.969362566940745</v>
+        <v>1.42737204275393</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.2911988272359238</v>
+        <v>-0.8301546653299141</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>3.129746107202166</v>
+        <v>2.582548580280637</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>3.724510137907899</v>
+        <v>3.183422566846652</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>4.610379320066983</v>
+        <v>4.67993504957991</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>1.445778625720436</v>
+        <v>1.516034985422976</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>3.701506854109731</v>
+        <v>3.772742692877685</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>1.848624897113915</v>
+        <v>1.918772176315329</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>2.32578205631166</v>
+        <v>2.396634171614608</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0.2099752527817031</v>
+        <v>0.2799718836746621</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>0.4846024098060084</v>
+        <v>0.5544465961569429</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>1.429168158491464</v>
+        <v>1.499022506198742</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.5548</t>
+          <t>X ≈ 0.5547</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-8.136360951765639</v>
+        <v>-8.025195191535154</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-8.475428587587302</v>
+        <v>-8.362516428773276</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.145167361456778</v>
+        <v>-2.080034489010146</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.2659462392181524</v>
+        <v>-0.2175091708314199</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-4.989665672193524</v>
+        <v>-4.869796017801889</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-10.86021985964139</v>
+        <v>-10.69708778183283</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-6.456138736911235</v>
+        <v>-6.324014814551226</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-4.127407836013944</v>
+        <v>-4.017417312426517</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.2647736346051417</v>
+        <v>0.3354773661353505</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-3.138402675918677</v>
+        <v>-3.036665743811049</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.6126219721878527</v>
+        <v>0.6846539738173121</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.8400663205164705</v>
+        <v>0.4008156925932909</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-4.643750830121441</v>
+        <v>-5.04138718757364</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-7.822159692192272</v>
+        <v>-8.70802984689518</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-8.485073672683399</v>
+        <v>-9.379512603313565</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-7.88470330112365</v>
+        <v>-8.260344880736255</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-8.889247266320169</v>
+        <v>-9.25720796081572</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-9.866008533947593</v>
+        <v>-9.708454810495425</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-7.037206977388429</v>
+        <v>-6.906356533019576</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-5.978827857063706</v>
+        <v>-5.857441757534311</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-4.790863314186716</v>
+        <v>-4.675849994466056</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-4.86637584300108</v>
+        <v>-4.751695955874958</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-5.458510732940958</v>
+        <v>-5.339290208910143</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-2.404017289601015</v>
+        <v>-2.828915565581688</v>
       </c>
     </row>
     <row r="23">
@@ -2016,79 +2016,79 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.9595358149305042</v>
+        <v>-1.29547609999684</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.294617104030095</v>
+        <v>-1.630158727520765</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3.46460302592314</v>
+        <v>3.179165821401384</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2.751060980849047</v>
+        <v>2.466462924161235</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.8367755910280579</v>
+        <v>0.5695506808886677</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.02353189334162</v>
+        <v>0.7561087934069377</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.026131523388742</v>
+        <v>0.7656783982756181</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.351490812713898</v>
+        <v>-2.635812467012776</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.310257424324774</v>
+        <v>-2.594607797575662</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.533977932277395</v>
+        <v>-1.805303043251683</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.261129439073841</v>
+        <v>-1.531400352466186</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.315417140998534</v>
+        <v>-2.590757726689731</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.3391331656874002</v>
+        <v>-0.5901695188811544</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-3.661265170520032</v>
+        <v>-3.934339474211278</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>0.330966381140513</v>
+        <v>0.0921661083600398</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.6243611661376747</v>
+        <v>-0.8759469696969688</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-1.533648658735856</v>
+        <v>-1.791114106674264</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-3.964213470180511</v>
+        <v>-4.239704810495802</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-1.422508911899499</v>
+        <v>-1.680063429571298</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-2.01065891472868</v>
+        <v>-2.274467619603449</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>2.097303466971212</v>
+        <v>1.870486212430876</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>1.246154612878989</v>
+        <v>1.013390251021775</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>0.7457359809111495</v>
+        <v>0.506614963503651</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-0.1053991568067545</v>
+        <v>-0.3504672897196244</v>
       </c>
     </row>
     <row r="24">
@@ -2098,735 +2098,735 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-4.077044006200609</v>
+        <v>-4.456667808963303</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-2.787111708118516</v>
+        <v>-3.153016050164581</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-3.413476492575832</v>
+        <v>-3.771040477996436</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2.501980185306323</v>
+        <v>-2.845384465261674</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.3833656321421941</v>
+        <v>0.0960814215521637</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.5700575450351195</v>
+        <v>0.2825757725740985</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.6104907310625762</v>
+        <v>0.3305854148771488</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.3319724470912604</v>
+        <v>0.05241026512982216</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.876836197980957</v>
+        <v>-2.363908716204648</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-6.087515193027876</v>
+        <v>-5.593650590333041</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.752715750285965</v>
+        <v>-1.223973242872368</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.4072147364830272</v>
+        <v>0.9550109269171401</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.530284612085232</v>
+        <v>-1.805962681988916</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.1256251629571636</v>
+        <v>-0.3884678212637453</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-2.410572662157165</v>
+        <v>-2.687034711312094</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.189496352372899</v>
+        <v>-0.45330352707402</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>0.4894180835591087</v>
+        <v>0.2324514670957711</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>0.3844346674642836</v>
+        <v>0.1276107632748662</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-1.025458429766864</v>
+        <v>-1.295842118095976</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-3.277439024390148</v>
+        <v>-3.568012701570304</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-4.633647563469687</v>
+        <v>-4.930231000684238</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-3.083586358949695</v>
+        <v>-3.366732699798355</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-3.621819322548497</v>
+        <v>-3.911930118463566</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-5.32377692197975</v>
+        <v>-5.627106633982017</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.6803</t>
+          <t>X ≈ 0.6802</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>8.010082862067378</v>
+        <v>8.534230795155331</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>11.56835644735416</v>
+        <v>12.04298758406304</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>10.77851035162969</v>
+        <v>11.24650246855015</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>5.522670335005607</v>
+        <v>6.049736122237661</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>9.700270651080615</v>
+        <v>10.19858034498112</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>4.695664202453017</v>
+        <v>5.260330118336228</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>4.572609102041355</v>
+        <v>5.129872085415379</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>4.294097793242102</v>
+        <v>4.851703923210763</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1.739793332526546</v>
+        <v>1.69002282257712</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>5.50917471661127</v>
+        <v>5.402088102219139</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>3.188684313065309</v>
+        <v>3.113388049090155</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>1.61088911088919</v>
+        <v>1.55364834093298</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4.382501788505863</v>
+        <v>4.915250817013238</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.213093029419568</v>
+        <v>2.772643200954448</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-1.04324080702041</v>
+        <v>-0.448699276255347</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>0.2011698919516931</v>
+        <v>0.7867132867132867</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.7164268471534285</v>
+        <v>1.293821790761527</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>1.260794080408644</v>
+        <v>1.830006727965838</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.8275665939899639</v>
+        <v>1.404872467864593</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.9334415584416291</v>
+        <v>-0.3313586452442934</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-0.1779406687382803</v>
+        <v>0.4081464688408829</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-3.500648971134069</v>
+        <v>-2.872827697696273</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-3.225873804652018</v>
+        <v>-2.598352985214369</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-1.353763195868531</v>
+        <v>-0.7511083153606464</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.7221</t>
+          <t>X ≈ 0.722</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.178929063812042</v>
+        <v>0.9908947800012697</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.593581766013642</v>
+        <v>-1.793165055663138</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.349867557076706</v>
+        <v>1.173451710850877</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.095097282867435</v>
+        <v>1.926672804112528</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.2234189044266657</v>
+        <v>-0.371938807970885</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>3.38006892998402</v>
+        <v>3.248097281988315</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>3.576056253777516</v>
+        <v>3.449751335591792</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>2.809358915197684</v>
+        <v>3.171200419870289</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>6.265846941574331</v>
+        <v>6.644399621773026</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>2.072647974288437</v>
+        <v>2.435358803158778</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>1.661918396055491</v>
+        <v>1.731063114268657</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.4072147364829704</v>
+        <v>0.4698847281472069</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.7461381521422297</v>
+        <v>0.8142556578692108</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.426438171087248</v>
+        <v>-1.370323300050323</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.6219547759782103</v>
+        <v>-0.2601623230125085</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-3.441528872698285</v>
+        <v>-3.097147950089074</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-1.136598176603314</v>
+        <v>-0.780084694909732</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-2.704996226844933</v>
+        <v>-2.355513634024987</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-1.5132633078155</v>
+        <v>-1.159230096237906</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>0.1371951219512155</v>
+        <v>0.4982039490241803</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.4060052870466819</v>
+        <v>-0.04434221894174328</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-2.433179854884415</v>
+        <v>-2.080972494076434</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-3.134014444499904</v>
+        <v>-2.78688993845708</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-4.185565539865863</v>
+        <v>-3.843114348543097</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.764</t>
+          <t>X ≈ 0.7639</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>8.037590305960919</v>
+        <v>8.242560958316915</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>3.648360737262536</v>
+        <v>3.871909720505215</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.4940424295263028</v>
+        <v>-0.2566922881670308</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>4.19756966268595</v>
+        <v>4.411519611672738</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3.381849427211399</v>
+        <v>3.627298645851916</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.31676178796598</v>
+        <v>1.572112365581589</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.796147908164201</v>
+        <v>3.042316148058944</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.51759326264564</v>
+        <v>2.315674210032327</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.044494275935378</v>
+        <v>-1.230282554241313</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.4339225655474976</v>
+        <v>0.2389542360899171</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>2.510083634464642</v>
+        <v>2.306735851346005</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.330088830088783</v>
+        <v>1.131125461350877</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>1.106498512502597</v>
+        <v>0.904824381041891</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>1.786042602369129</v>
+        <v>1.580606491142348</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>1.127111363331828</v>
+        <v>0.9224631935618319</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>2.623072313854117</v>
+        <v>2.413711102051856</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>2.93942907015559</v>
+        <v>2.728224458347924</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>3.735346554961318</v>
+        <v>3.520244741073888</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>2.149667916091225</v>
+        <v>1.942414148903985</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>1.435810810810757</v>
+        <v>1.23239897232493</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>2.243961753164207</v>
+        <v>2.035144284179523</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>3.969808499323349</v>
+        <v>3.753020295864644</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>1.541880963102876</v>
+        <v>1.336912048705443</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>4.619092776987507</v>
+        <v>4.400093248396963</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.8058</t>
+          <t>X ≈ 0.8057</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>218</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3.206612539203334</v>
+        <v>3.239886831522163</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>6.541161795201212</v>
+        <v>6.574834803814554</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>4.642745734784789</v>
+        <v>4.678100158453276</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>4.387668017921918</v>
+        <v>4.423861735340822</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>4.481113829228121</v>
+        <v>4.546786859123799</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>3.750847249574406</v>
+        <v>3.816321852560677</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>4.812843502841446</v>
+        <v>4.879235553991393</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>2.699426472001782</v>
+        <v>2.766161723917214</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>3.199658133354703</v>
+        <v>3.266364502162205</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>5.636831896897192</v>
+        <v>5.704458000437633</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>3.61761318236119</v>
+        <v>3.684939660948217</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>5.632097260537662</v>
+        <v>5.699768239151595</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>4.966321638380784</v>
+        <v>5.035321768625742</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>2.451386845695026</v>
+        <v>2.520664910527749</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>1.792455606657704</v>
+        <v>1.86252161294717</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.3647779217025402</v>
+        <v>-0.2953850430914642</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.9575872121816928</v>
+        <v>-0.8880177763991668</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>0.3135761607138008</v>
+        <v>0.3832883087704246</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.8464474653451575</v>
+        <v>-0.7769670992960229</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>0.2580275229358335</v>
+        <v>0.3273099033325622</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-1.661319675053008</v>
+        <v>-1.591383053624355</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.8198435380350588</v>
+        <v>-0.7497978223728978</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>0.3723628211076146</v>
+        <v>0.4421080827696997</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.1622941144911252</v>
+        <v>-0.09243976678384769</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.8477</t>
+          <t>X ≈ 0.8476</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>231</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.4273681589975737</v>
+        <v>-0.3940938666787446</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-3.359946271044478</v>
+        <v>-3.326273262431137</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-2.635144570628448</v>
+        <v>-2.599790146959961</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.1142655793818648</v>
+        <v>0.1504592968007685</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-1.116805071443032</v>
+        <v>-1.051132041547355</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-1.362540891336728</v>
+        <v>-1.297066288350457</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>1.760696872713176</v>
+        <v>1.827088923863123</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>5.811146556198942</v>
+        <v>5.877881808114374</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>8.450065218624175</v>
+        <v>8.516771587431677</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>7.676229807854746</v>
+        <v>7.743855911395187</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>3.621584745965741</v>
+        <v>3.688911224552768</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>1.177988677988708</v>
+        <v>1.245659656602641</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>1.785099191103242</v>
+        <v>1.854099321348201</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>4.59404541037194</v>
+        <v>4.663323475204663</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>3.935114171334668</v>
+        <v>4.005180177624133</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>4.097273788055588</v>
+        <v>4.166666666666664</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>3.53027966100624</v>
+        <v>3.599849096788766</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>3.858196677811385</v>
+        <v>3.927908825868009</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>4.507220273643632</v>
+        <v>4.576700639692767</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>4.694264069264065</v>
+        <v>4.763546449660794</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>1.553661062863512</v>
+        <v>1.623597684292164</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>1.477706007220903</v>
+        <v>1.547751722883064</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>4.349883771105631</v>
+        <v>4.419629032767716</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>1.676539834434564</v>
+        <v>1.746394182141842</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.8895</t>
+          <t>X ≈ 0.8894</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>179</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-3.394791796812214</v>
+        <v>-3.361517504493385</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-1.495330439948198</v>
+        <v>-1.461657431334856</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.4169244032282364</v>
+        <v>0.4522788268967233</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-3.090164999350392</v>
+        <v>-3.053971281931489</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>3.248475830150696</v>
+        <v>3.314148860046373</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>2.876981225280403</v>
+        <v>2.942455828266674</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>1.545455875349269</v>
+        <v>1.611847926499216</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-2.085054077431863</v>
+        <v>-2.018318825516431</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-2.602197230286329</v>
+        <v>-2.535490861478827</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.141395769547387</v>
+        <v>-1.073769666006946</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.2502819333221211</v>
+        <v>0.3176084119091485</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.704789623784031</v>
+        <v>-1.637118645170098</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-4.505258495902467</v>
+        <v>-4.436258365657508</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-2.49197843542845</v>
+        <v>-2.422700370595727</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>1.877023286428113</v>
+        <v>1.947089292717578</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>3.030742553926594</v>
+        <v>3.10013543253767</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>1.220671206146378</v>
+        <v>1.290240641928904</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>2.233006225805291</v>
+        <v>2.302718373861914</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>0.7731517351058272</v>
+        <v>0.8426321011549618</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.7157821229050256</v>
+        <v>-0.646499742508297</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>1.534313557482491</v>
+        <v>1.604250178911144</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.2176191517914035</v>
+        <v>-0.1475734361292425</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>0.6158152325678259</v>
+        <v>0.6855604942299109</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.01878532457772053</v>
+        <v>0.05106902312955697</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.9313</t>
+          <t>X ≈ 0.9312</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>120</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.3407880724174603</v>
+        <v>-0.3075137800986312</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.6759635870617871</v>
+        <v>-0.6422905784484456</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>6.217669282185412</v>
+        <v>6.253023705853899</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5.503875968992254</v>
+        <v>5.540069686411158</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>5.138606183968207</v>
+        <v>5.204279213863884</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>7.825770796974965</v>
+        <v>7.891245399961235</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>4.552904664920945</v>
+        <v>4.619296716070892</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>4.274350019402405</v>
+        <v>4.341085271317837</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>1.81586608442506</v>
+        <v>1.882572453232562</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>8.542030673655624</v>
+        <v>8.609656777196065</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>7.983056607437604</v>
+        <v>8.050383086024631</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>10.20396270396273</v>
+        <v>10.27163368257666</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>5.746138152142258</v>
+        <v>5.815138282387217</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>4.691448007774589</v>
+        <v>4.760726072607312</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>4.032516768737246</v>
+        <v>4.102582775026711</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>3.794243485025262</v>
+        <v>3.863636363636338</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>3.66014979087636</v>
+        <v>3.729719226658887</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>5.221833041447752</v>
+        <v>5.291545189504376</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>4.604622871046239</v>
+        <v>4.674103237095373</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>2.291666666666671</v>
+        <v>2.3609490470634</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>5.915132924335374</v>
+        <v>5.985069545764027</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>5.839177868692765</v>
+        <v>5.909223584354926</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>2.780619701841566</v>
+        <v>2.850364963503651</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>5.204678362573084</v>
+        <v>5.274532710280361</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.9731</t>
+          <t>X ≈ 0.973</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>97</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>4.057837357135796</v>
+        <v>4.091111649454625</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.6298783373368337</v>
+        <v>0.6635513459501752</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-1.840749961800846</v>
+        <v>-1.805395538132359</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-5.64732678014866</v>
+        <v>-5.611133062729756</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-2.919813060018051</v>
+        <v>-2.854140030122373</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-6.856359787217436</v>
+        <v>-6.790885184231165</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-1.443658908962178</v>
+        <v>-1.377266857812231</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-5.845924894686952</v>
+        <v>-5.77918964277152</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-5.804408829664339</v>
+        <v>-5.737702460856838</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-6.578244240433726</v>
+        <v>-6.510618136893285</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-3.211101468163747</v>
+        <v>-3.14377498957672</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>3.726299473722129</v>
+        <v>3.793970452336062</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>2.601808255234985</v>
+        <v>2.670808385479944</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.7123320609540116</v>
+        <v>-0.6430539961212887</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-1.371263299991277</v>
+        <v>-1.301197293701811</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-1.807131085421418</v>
+        <v>-1.737738206810342</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>0.1206308905327234</v>
+        <v>0.1902003263152494</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-2.046208195665656</v>
+        <v>-1.976496047609032</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-2.861012867785384</v>
+        <v>-2.791532501736249</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.6121134020618513</v>
+        <v>-0.5428310216651226</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-1.155313811059806</v>
+        <v>-1.085377189631153</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-1.231268866702415</v>
+        <v>-1.161223151040254</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>3.167217639985893</v>
+        <v>3.236962901647978</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>3.091276300717425</v>
+        <v>3.161130648424702</v>
       </c>
     </row>
     <row r="33">
@@ -2839,76 +2839,76 @@
         <v>57</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-9.814472282943782</v>
+        <v>-9.781197990624953</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.3766679918855829</v>
+        <v>0.4103410004989243</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-4.571804402025116</v>
+        <v>-4.536449978356629</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-3.531211750305964</v>
+        <v>-3.49501803288706</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-5.650867500242335</v>
+        <v>-5.585194470346657</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-5.463702887235556</v>
+        <v>-5.398228284249285</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-9.74534094911413</v>
+        <v>-9.678948897964183</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-8.26950962972041</v>
+        <v>-8.202774377804978</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-11.73676549452234</v>
+        <v>-11.67005912571484</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-16.01937283511636</v>
+        <v>-15.95174673157592</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-13.99062760308873</v>
+        <v>-13.92330112450171</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-10.76094957673905</v>
+        <v>-10.69327859812512</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-10.13105483031394</v>
+        <v>-10.06205470006898</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-3.334867781699167</v>
+        <v>-3.265589716866444</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-5.74818498564872</v>
+        <v>-5.678118979359255</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-5.153124936027339</v>
+        <v>-5.083732057416263</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-5.287218630176262</v>
+        <v>-5.217649194393736</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-3.63781608135929</v>
+        <v>-3.568103933302666</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>0.08707901139710827</v>
+        <v>0.1565593774462428</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-1.480263157894733</v>
+        <v>-1.410980777498004</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>3.239694327844127</v>
+        <v>3.30963094927278</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.3450326576230225</v>
+        <v>-0.2749869419608615</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-1.824643456053167</v>
+        <v>-1.754898194391082</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.1461988304093609</v>
+        <v>-0.07634448270208338</v>
       </c>
     </row>
     <row r="34">
@@ -2921,76 +2921,76 @@
         <v>45</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>6.32587859424919</v>
+        <v>6.359152886568019</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>3.768480857382649</v>
+        <v>3.80215386599599</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>4.55100261551874</v>
+        <v>4.586357039187227</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.60723514211886</v>
+        <v>-0.5710414246999562</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-3.194727149365121</v>
+        <v>-3.129054119469444</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.436881908086093</v>
+        <v>1.502356511072364</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-3.78042866841237</v>
+        <v>-3.714036617262423</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>2.607683352735734</v>
+        <v>2.674418604651166</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-4.017467248908311</v>
+        <v>-3.950760880100809</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-7.013524881899933</v>
+        <v>-6.945898778359492</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-2.294721170340168</v>
+        <v>-2.22739469175314</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>4.092851592851574</v>
+        <v>4.160522571465506</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>14.07947148547559</v>
+        <v>14.14847161572055</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>11.63589245221902</v>
+        <v>11.70517051705174</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>8.75473899095946</v>
+        <v>8.824804997248926</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>9.349799040580841</v>
+        <v>9.419191919191917</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>4.771260901987475</v>
+        <v>4.840830337770001</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>4.666277485892223</v>
+        <v>4.735989633948847</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-1.784266017842661</v>
+        <v>-1.714785651793527</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>5.069444444444443</v>
+        <v>5.138726824841171</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>6.748466257668746</v>
+        <v>6.818402879097398</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>11.11695564647055</v>
+        <v>11.18700136213271</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>9.169508590730452</v>
+        <v>9.239253852392537</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>11.31578947368421</v>
+        <v>11.38564382139149</v>
       </c>
     </row>
   </sheetData>
@@ -3184,79 +3184,79 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3335</v>
+        <v>3339</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.05266089904439042</v>
+        <v>-0.05346991783804356</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.05996756122970481</v>
+        <v>-0.07449228581394607</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.02045119972142828</v>
+        <v>0.02275858818931908</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.03875968992247891</v>
+        <v>0.041460230709923</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.04133217968624336</v>
+        <v>-0.009332311223055001</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.1654782085938322</v>
+        <v>-0.1502349775846952</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.3247437982243682</v>
+        <v>-0.326058475185917</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.4072420203985914</v>
+        <v>-0.4084675014907475</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.3188507464697636</v>
+        <v>-0.3201812996255953</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.2691999117685313</v>
+        <v>-0.2706137080863726</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.2165749033680839</v>
+        <v>-0.2180442490992078</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.1198069712714016</v>
+        <v>-0.1214011432940083</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.09093210196837731</v>
+        <v>-0.09259536944917812</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.1450751182222731</v>
+        <v>-0.1466813348001494</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.1281672476153304</v>
+        <v>-0.1298143965697491</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.05375172742234469</v>
+        <v>-0.05547102827437556</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.1700407708317044</v>
+        <v>-0.1716260648209271</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.1374483956779997</v>
+        <v>-0.1390768200650001</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.130906071069532</v>
+        <v>-0.1147590622365655</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.1357067984426479</v>
+        <v>-0.1196015214584492</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.06199909084337918</v>
+        <v>-0.04580943258576298</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.1200170169330406</v>
+        <v>-0.1037504675412748</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.0970781398850562</v>
+        <v>-0.09873683290353341</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.1851267348781747</v>
+        <v>-0.1866832226336683</v>
       </c>
     </row>
     <row r="7">
@@ -3266,161 +3266,161 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3309</v>
+        <v>3313</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.08188820963381716</v>
+        <v>0.08064148200620735</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.01290268962589636</v>
+        <v>-0.02786047737770048</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.1098968462879668</v>
+        <v>0.1118825647127508</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.01394510034181451</v>
+        <v>0.01638890139061999</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1239714869077275</v>
+        <v>-0.09219514511047322</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.2506703057819024</v>
+        <v>-0.2357578051669478</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.4049774048744652</v>
+        <v>-0.4067449505957583</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.4257201982723871</v>
+        <v>-0.4274749931847168</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.3971581981356707</v>
+        <v>-0.3989468893210812</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.3107245205630065</v>
+        <v>-0.3126489872149776</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.2297947981848836</v>
+        <v>-0.2318070463459989</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.099843663417019</v>
+        <v>-0.1020246582800226</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.09171597685114108</v>
+        <v>-0.09395262670371807</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.1746458521390295</v>
+        <v>-0.1767927470253738</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.1220871717533072</v>
+        <v>-0.1243248554953809</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.05191036112855585</v>
+        <v>-0.05421037734988232</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.1982288049795997</v>
+        <v>-0.2003591337992106</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.1221621305498317</v>
+        <v>-0.1064047652740356</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.1172640732305723</v>
+        <v>-0.08363701220097397</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.1235662541503189</v>
+        <v>-0.09003134509346467</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.04501200320084564</v>
+        <v>-0.01120886904184459</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.07268158967831084</v>
+        <v>-0.05687981536343756</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.08191806250888334</v>
+        <v>-0.08415525375645672</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.1700572070854065</v>
+        <v>-0.1721923123577227</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.05186</t>
+          <t>X &gt; -0.05187</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3264</v>
+        <v>3268</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.03415795768499663</v>
+        <v>-0.03573606992725331</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.05710576008005575</v>
+        <v>0.04141808456636653</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.04902271908255784</v>
+        <v>0.05058839382954261</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.03847625526125853</v>
+        <v>-0.03646299730789337</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.1428120828203774</v>
+        <v>-0.1114888844202113</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2738226989599681</v>
+        <v>-0.2595820952159187</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.389150839806085</v>
+        <v>-0.3918719304921936</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.3758431878377877</v>
+        <v>-0.3785978487309194</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.2864124223392892</v>
+        <v>-0.289275560584386</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.1881280565031176</v>
+        <v>-0.1911562309340411</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.0182156571934371</v>
+        <v>-0.02143759101104337</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.02579125211990885</v>
+        <v>0.02249803075642376</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.01897652672212757</v>
+        <v>0.01562653383668788</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.09257807209505842</v>
+        <v>-0.09580628392509283</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>0.0003655407743323735</v>
+        <v>-0.003015189349881098</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>0.06335663487238463</v>
+        <v>0.05993039743803763</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.05250443569649121</v>
+        <v>-0.05579864685164893</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>0.05664491052086618</v>
+        <v>0.07149628974887889</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.02804491652395313</v>
+        <v>0.06108988745713617</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.01912484700122974</v>
+        <v>0.05208054553433783</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>0.1062868882166157</v>
+        <v>0.1395000545842606</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>0.07932891992771118</v>
+        <v>0.09424448779125072</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>0.06622460230098426</v>
+        <v>0.06281525411240807</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>0.008599931200549804</v>
+        <v>0.005254864503143608</v>
       </c>
     </row>
     <row r="9">
@@ -3430,243 +3430,243 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3220</v>
+        <v>3224</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.07703635899141403</v>
+        <v>0.07484823038548427</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.174093014770051</v>
+        <v>0.1576271677987222</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.123710241329178</v>
+        <v>0.1247711089187931</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.04474481807604747</v>
+        <v>0.04624252591732869</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.03665993744364471</v>
+        <v>0.0674056932299365</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.1913285025717784</v>
+        <v>-0.1778602910956479</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.29768781318311</v>
+        <v>-0.3014607193515531</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.2803809639000079</v>
+        <v>-0.2841978252438366</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.221199592448869</v>
+        <v>-0.2250889616577894</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.04914094350611009</v>
+        <v>-0.05330160764120961</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.1193921072828559</v>
+        <v>0.1150404791209709</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.2297624975643515</v>
+        <v>0.2252514933373106</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.0833942685869431</v>
+        <v>0.07897991554523998</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.0353141787782576</v>
+        <v>0.03094059405940186</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.2005262718877461</v>
+        <v>0.1958975382579098</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.2873205670670274</v>
+        <v>0.282625011727184</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.1407699459151246</v>
+        <v>0.1362434343599404</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.2218330414477521</v>
+        <v>0.235783107719989</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.2209019408136825</v>
+        <v>0.2533305896415854</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.1783498759305147</v>
+        <v>0.2107113946558741</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>0.2741669506048936</v>
+        <v>0.3067749721206283</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>0.2168935732241195</v>
+        <v>0.2309290107115274</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>0.1998994286344811</v>
+        <v>0.1953262038137282</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>0.1425665613308595</v>
+        <v>0.1380562834813688</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; 0.03181</t>
+          <t>X &gt; 0.0318</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3157</v>
+        <v>3161</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.2931330023096521</v>
+        <v>0.2899704966309287</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.3987635330053863</v>
+        <v>0.3810920366296671</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.2499950588436732</v>
+        <v>0.2502966238316588</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.02618568027834556</v>
+        <v>0.02700704870262172</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.05669062001105374</v>
+        <v>0.08673093510653729</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2110502976778079</v>
+        <v>-0.1985950702318604</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.2096005893875699</v>
+        <v>-0.2148762478249751</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.09178053878114412</v>
+        <v>-0.09723493865592303</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.0006428535350053721</v>
+        <v>-0.006211415702559009</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.1902898511037989</v>
+        <v>0.1844020235454522</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.356793981174981</v>
+        <v>0.3507193617707429</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.3171086885959014</v>
+        <v>0.3110534239831324</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.09547485460590366</v>
+        <v>0.08958623191399795</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.1140388450573226</v>
+        <v>0.1081016905729726</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>0.3588968783031916</v>
+        <v>0.3525827750267041</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0.4356177078095698</v>
+        <v>0.4292610347236163</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.2256146865120385</v>
+        <v>0.2195065503059794</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.3103845910998686</v>
+        <v>0.3231407661236574</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.241877773007019</v>
+        <v>0.2735554073439985</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>0.2580275229357767</v>
+        <v>0.2896032782784843</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>0.3033185783438199</v>
+        <v>0.3351644224243699</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>0.2147714109529772</v>
+        <v>0.2276929075680911</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>0.2552872129245358</v>
+        <v>0.2491631924726576</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>0.1349919514232667</v>
+        <v>0.1290091417893962</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; 0.07365</t>
+          <t>X &gt; 0.07363</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3089</v>
+        <v>3093</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.3477576161282343</v>
+        <v>0.3462911502336254</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.1412822301840251</v>
+        <v>0.157537876574608</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.1494582139743414</v>
+        <v>0.1669295705477865</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.06365970314593739</v>
+        <v>-0.04551589917442556</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.0398725501412045</v>
+        <v>0.06914407872874762</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.2378362883712342</v>
+        <v>-0.2265152177993599</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.1872156099931317</v>
+        <v>-0.1940880973139016</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.06070208071576388</v>
+        <v>-0.06777643879910755</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.1282451946764809</v>
+        <v>0.1209283235909737</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.3081276316261565</v>
+        <v>0.3004780332346897</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.4077877902333142</v>
+        <v>0.4000394434129575</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.2442982960891911</v>
+        <v>0.2367212322597396</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.04245835872712433</v>
+        <v>0.03499643841556122</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.1308517318085549</v>
+        <v>0.1232435400908685</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.2986666395382755</v>
+        <v>0.2907548180374562</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.3316694408680476</v>
+        <v>0.3237847986153923</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.08764386542926417</v>
+        <v>0.08005277518482501</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.2412254137813008</v>
+        <v>0.2527980148191986</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.2311042328217141</v>
+        <v>0.2619585342529902</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.3081555124474633</v>
+        <v>0.3388704256309794</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>0.3017219713384023</v>
+        <v>0.33273168754382</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>0.2776012483972892</v>
+        <v>0.2892063466906336</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>0.2806197018415659</v>
+        <v>0.272795474169456</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>0.1269833156323443</v>
+        <v>0.1193435735199486</v>
       </c>
     </row>
     <row r="12">
@@ -3676,79 +3676,79 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3008</v>
+        <v>3012</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.1415376626337377</v>
+        <v>0.1748119549525669</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.103686231240161</v>
+        <v>0.1373592398535024</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.2497142111579933</v>
+        <v>0.2850686348264801</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.08215619668300889</v>
+        <v>-0.0644892828653596</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.10003869085525</v>
+        <v>0.1282963925886875</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.3223773511731522</v>
+        <v>-0.3124215970654944</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.1504804933103756</v>
+        <v>-0.159362021953541</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.05308374982375597</v>
+        <v>0.04388324443966951</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.1798184180893827</v>
+        <v>0.1704512411113299</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.3190726162604633</v>
+        <v>0.309392226931493</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.3809256589999421</v>
+        <v>0.3712012578186616</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.1211263885220148</v>
+        <v>0.1116954518243745</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.1760354010650005</v>
+        <v>0.1663464915894437</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.1733224551662289</v>
+        <v>0.1635958297816629</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.2638600523193304</v>
+        <v>0.2539021964686867</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.381281750895667</v>
+        <v>0.3712573046569076</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.2670753357375162</v>
+        <v>0.2571747564346083</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.29484996809893</v>
+        <v>0.3048077889738749</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.3118360583457189</v>
+        <v>0.3415990911583862</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.2199535192563076</v>
+        <v>0.2496904759508141</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>0.1615073292949774</v>
+        <v>0.1915636269677066</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>0.1719574921700726</v>
+        <v>0.1820966897869525</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>0.1343917191230588</v>
+        <v>0.1246762811272788</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.05463014806520761</v>
+        <v>-0.06411270804631641</v>
       </c>
     </row>
     <row r="13">
@@ -3758,161 +3758,161 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2906</v>
+        <v>2910</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.1720324404030507</v>
+        <v>0.2053067327218798</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.07617316507496952</v>
+        <v>0.109846173688311</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.345874410390536</v>
+        <v>0.3812288340590229</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.006839945280439963</v>
+        <v>0.01015515649662291</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.1602734208253125</v>
+        <v>0.1871851967698674</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.2834010031618988</v>
+        <v>-0.2754212667054006</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.1127349562133588</v>
+        <v>-0.1242930275188385</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.07343677739327603</v>
+        <v>0.06155950752394546</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.03665190118647388</v>
+        <v>-0.04837748404651165</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.03690467018720511</v>
+        <v>-0.04879633710922349</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.05167733649714279</v>
+        <v>0.03971322410520628</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.138972824158003</v>
+        <v>-0.1507407466471022</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.214410732934958</v>
+        <v>-0.2263142698567293</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.2096043829827181</v>
+        <v>-0.2215677359373984</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.05862638265307396</v>
+        <v>-0.07094025091318201</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.007613448395254352</v>
+        <v>-0.004676393565283377</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.07167203438414305</v>
+        <v>-0.0838885492130288</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.1079505380781853</v>
+        <v>-0.0996696354784703</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.1322945685506909</v>
+        <v>-0.1036173258981066</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.1997422680412342</v>
+        <v>-0.1711022349878846</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.2757115812220903</v>
+        <v>-0.2467522794964765</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.2967689446955788</v>
+        <v>-0.2882457847049551</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.3454552895585081</v>
+        <v>-0.3572956342290894</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.5041998204964102</v>
+        <v>-0.5158452965924738</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; 0.1992</t>
+          <t>X &gt; 0.1991</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2794</v>
+        <v>2798</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.04680988370243711</v>
+        <v>-0.01353559138360794</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.1870046443274944</v>
+        <v>0.2206776529408359</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.4542743082641252</v>
+        <v>0.489628731932612</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.06175903634392199</v>
+        <v>-0.04551589917442556</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.05556941053996667</v>
+        <v>0.08099803795113303</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.2711201487945587</v>
+        <v>-0.265463940958611</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.06247995046365418</v>
+        <v>-0.07724192783615536</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.07116749951165957</v>
+        <v>0.05613329693149183</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.04502723940485964</v>
+        <v>-0.0598949251779004</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.04976968285063776</v>
+        <v>-0.06484185814274923</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.1383110059159804</v>
+        <v>0.1230326586742123</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.1296375761234856</v>
+        <v>0.1142889491720567</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.1532194495708339</v>
+        <v>-0.1684682749898627</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.1392672129799521</v>
+        <v>-0.1546036956636812</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.02700704078656457</v>
+        <v>-0.04268588878689172</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.1965300159291914</v>
+        <v>0.1806776289473362</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.1195255354558284</v>
+        <v>0.1037377848316225</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0.1217615618194472</v>
+        <v>0.1273181277407218</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.05196621152753522</v>
+        <v>0.07886514185727833</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.1183881343816964</v>
+        <v>-0.07027639059290891</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.2471242559768569</v>
+        <v>-0.198513966268365</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.2659723458994989</v>
+        <v>-0.2386201135245116</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.2560529278543129</v>
+        <v>-0.2500639142661853</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.3465027397891021</v>
+        <v>-0.3616359816424293</v>
       </c>
     </row>
     <row r="15">
@@ -3922,79 +3922,79 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2681</v>
+        <v>2685</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.5543652411334818</v>
+        <v>0.587639533452311</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.5530176196642174</v>
+        <v>0.5866906282775588</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.7824566214534627</v>
+        <v>0.8178110451219496</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.3492686715278097</v>
+        <v>0.3645009425931534</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.5776909087672095</v>
+        <v>0.6221822801349006</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.03057664177779174</v>
+        <v>-0.006875272640129992</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.1086665166352816</v>
+        <v>0.1113837586030613</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.1271783397390749</v>
+        <v>0.1512275100315037</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.02016117045052823</v>
+        <v>0.04429168638034042</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.06371474486841322</v>
+        <v>-0.0391925175329817</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.1207377668578999</v>
+        <v>0.1450111340503852</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.1234174747185861</v>
+        <v>0.1261948906469428</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.04969673071385472</v>
+        <v>-0.06863446176431154</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.1002186588921248</v>
+        <v>-0.1191649625586564</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.02994446436039055</v>
+        <v>-0.04921952894951431</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.1779615292049854</v>
+        <v>0.1585558184071161</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.215084613967619</v>
+        <v>0.1955677453151523</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.147345145730803</v>
+        <v>0.150176141885332</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.1400046215117783</v>
+        <v>0.1650472887018708</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.04539106145251282</v>
+        <v>0.001802856941779396</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.08213483522746401</v>
+        <v>-0.03448352686166345</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.2476030978869304</v>
+        <v>-0.2220613318461915</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.2488359282852102</v>
+        <v>-0.2455382022319199</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.3025950428726318</v>
+        <v>-0.3213704554551953</v>
       </c>
     </row>
     <row r="16">
@@ -4004,161 +4004,161 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2577</v>
+        <v>2582</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.6888129571835719</v>
+        <v>0.7011058005008763</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.3922474811492762</v>
+        <v>0.4049241391637963</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.7286087931249199</v>
+        <v>0.7422813927186738</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.285085750202029</v>
+        <v>0.2994933323651026</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.5761866215486435</v>
+        <v>0.6198201890343356</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.05153363977143499</v>
+        <v>0.07347877188973229</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.4374160592817162</v>
+        <v>0.4593841983814642</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.467861027513635</v>
+        <v>0.489933849730285</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.3548772856610256</v>
+        <v>0.377040483594044</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.3374969281635884</v>
+        <v>0.3599785275177965</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.5184901855847528</v>
+        <v>0.5182080538495981</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.4553161455713735</v>
+        <v>0.4325088434518065</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.2045520786412638</v>
+        <v>0.1587676260165338</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.1610042513245915</v>
+        <v>0.1151100046273541</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.1445957466698786</v>
+        <v>0.09820358904010362</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.414434551382115</v>
+        <v>0.367952817701557</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.497293017016105</v>
+        <v>0.4505235576720423</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.4310542735283391</v>
+        <v>0.4075993481117237</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.2597307103849857</v>
+        <v>0.2597585518528547</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.05932777993026406</v>
+        <v>0.08259054919270881</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>0.004280211157087876</v>
+        <v>0.02780127827113432</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.1259895088437375</v>
+        <v>-0.1255040169876978</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.2158892198031168</v>
+        <v>-0.2383259737542929</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.3463499649395203</v>
+        <v>-0.3916175608272923</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 0.3247</t>
+          <t>X &gt; 0.3246</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2459</v>
+        <v>2463</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.6358745473046525</v>
+        <v>0.6691488396234817</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.6244545972090876</v>
+        <v>0.658127605822429</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.9654097381411617</v>
+        <v>1.000764161809649</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.575371989496773</v>
+        <v>0.6115657069156768</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.019491115844637</v>
+        <v>1.085164145740315</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.2582944137091374</v>
+        <v>0.3008636381913945</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.7000031804405324</v>
+        <v>0.7429983213589182</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.7048493446385677</v>
+        <v>0.7480729955860141</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.381992940025583</v>
+        <v>0.425335167383345</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.5225896043967992</v>
+        <v>0.5664718919058984</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.6991560131642416</v>
+        <v>0.7190740441892771</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.6870055360124283</v>
+        <v>0.6832396204983624</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.4784982494658294</v>
+        <v>0.4507658127515626</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.4030774871525082</v>
+        <v>0.3753473767789899</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.498966985187451</v>
+        <v>0.4707621375334554</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.7532365828734413</v>
+        <v>0.7248713318838966</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.8221473548227749</v>
+        <v>0.8181214975429114</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.5953612590685395</v>
+        <v>0.6160888000520401</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.4866772762431424</v>
+        <v>0.5317872197793463</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.1865103532277743</v>
+        <v>0.2557927336245029</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>0.2767630353562325</v>
+        <v>0.3222599639532291</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.05916968650159049</v>
+        <v>-0.03779224999343</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.1665347697031478</v>
+        <v>-0.1693264697078831</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.1775908525549994</v>
+        <v>-0.2045578297115043</v>
       </c>
     </row>
     <row r="18">
@@ -4168,79 +4168,79 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2354</v>
+        <v>2358</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.8098041441646089</v>
+        <v>0.8430784364834381</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.5592309983866031</v>
+        <v>0.5929040069999445</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.8538790960601901</v>
+        <v>0.8892335197286769</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.6053988116318507</v>
+        <v>0.6415925290507545</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.128453899704247</v>
+        <v>1.194126929599925</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.3426912707482472</v>
+        <v>0.408165873734518</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.6696559339564914</v>
+        <v>0.7360479851064383</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.5180048417374294</v>
+        <v>0.5847400936528615</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.3057138001610795</v>
+        <v>0.3724201689685813</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.4872979892149232</v>
+        <v>0.5301305504616991</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.4901127745276455</v>
+        <v>0.5080819015914741</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.5322134451740581</v>
+        <v>0.5254407891756259</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.4071551012947765</v>
+        <v>0.37520596428228</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.2958707857878196</v>
+        <v>0.2639705358601958</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>0.298420076625284</v>
+        <v>0.2661447281737566</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.4693919158989104</v>
+        <v>0.4625351353432734</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.589751147958637</v>
+        <v>0.6082503001052189</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>0.3151324477242525</v>
+        <v>0.3593705392288342</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.1919850423778726</v>
+        <v>0.2614654084270072</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.1722858354537777</v>
+        <v>-0.1030034550570491</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.05396621298607585</v>
+        <v>-0.009417307501450978</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.1469568228748557</v>
+        <v>-0.1276720899453281</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.3138601283070557</v>
+        <v>-0.3196944088458054</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.2796037104940226</v>
+        <v>-0.3107090199995213</v>
       </c>
     </row>
     <row r="19">
@@ -4250,161 +4250,161 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2267</v>
+        <v>2270</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.4559313183265274</v>
+        <v>0.4892056106453566</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.3843761903254403</v>
+        <v>0.4180491989387818</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.877891894956349</v>
+        <v>0.9132463186248359</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.7792128172640744</v>
+        <v>0.8154065346829782</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.292677654384143</v>
+        <v>1.35835068427982</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.3374872586035735</v>
+        <v>0.4029618615898443</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.5751659420152748</v>
+        <v>0.6415579931652218</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.5602316831399534</v>
+        <v>0.6269669350553855</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.2502538993049441</v>
+        <v>0.3169602681124459</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.5566826883076246</v>
+        <v>0.5985261386488858</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.6369704157049796</v>
+        <v>0.6529021252747782</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.4715972544833136</v>
+        <v>0.4620261840411999</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.2091663211563173</v>
+        <v>0.1736620082219886</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.01399314207660751</v>
+        <v>-0.02132520944402216</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>0.08611441925118868</v>
+        <v>0.05025208021579886</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.2846986979474622</v>
+        <v>0.2751336506285895</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.3268164575430319</v>
+        <v>0.3435689919171097</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>0.133727314575502</v>
+        <v>0.1770581793766794</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.1787838837261617</v>
+        <v>-0.1093035176770272</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.3001101321585935</v>
+        <v>-0.2308277517618649</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.1384647261785759</v>
+        <v>-0.0685281047499231</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.2762180472760889</v>
+        <v>-0.232479793031267</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.2837541958656615</v>
+        <v>-0.266375124602078</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.2893666308102283</v>
+        <v>-0.2981545143892248</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 0.4502</t>
+          <t>X &gt; 0.4501</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2160</v>
+        <v>2162</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.5733393514052523</v>
+        <v>0.6066136437240814</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.2381638367609256</v>
+        <v>0.271836845374267</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.7375215444199341</v>
+        <v>0.772875968088421</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.4854087483089629</v>
+        <v>0.5216024657278666</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.9049958423246167</v>
+        <v>0.9706688722202941</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.07646331775061554</v>
+        <v>0.1419379207368863</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.3654623749855901</v>
+        <v>0.431854426135537</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.502420194841001</v>
+        <v>0.569155446756433</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.3592640530307634</v>
+        <v>0.4259704218382652</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.4626216247174639</v>
+        <v>0.5302477282579048</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.5792844750280608</v>
+        <v>0.6196351635869632</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.4658234556570946</v>
+        <v>0.4793899152636172</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.2005995483511995</v>
+        <v>0.1872527791554219</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.1782713878467916</v>
+        <v>-0.2184983041240329</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.1434005917314565</v>
+        <v>-0.1564626445267976</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.01087523221183773</v>
+        <v>0.003500812188434566</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.006208519330236584</v>
+        <v>0.03577562980267146</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.203698873445866</v>
+        <v>-0.1339867253892422</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.4501104006158059</v>
+        <v>-0.3806300345666713</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.5868408880666109</v>
+        <v>-0.5175585076698823</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.1587184478508661</v>
+        <v>-0.08878182642221333</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.438394242983918</v>
+        <v>-0.3958951328821954</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.3487185674781941</v>
+        <v>-0.3064342964408482</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.07309941520468044</v>
+        <v>-0.05849226659289286</v>
       </c>
     </row>
     <row r="21">
@@ -4414,243 +4414,243 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2062</v>
+        <v>2063</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.8009632580131125</v>
+        <v>0.8342375503319417</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.6109256243557297</v>
+        <v>0.6445986329690712</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.106396906762086</v>
+        <v>1.141751330430573</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.02153441117899</v>
+        <v>1.057728128597894</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.188436856440383</v>
+        <v>1.25410988633606</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.4563948898632333</v>
+        <v>0.521869492849504</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.9413903930293301</v>
+        <v>1.007782444179277</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.7595943348353984</v>
+        <v>0.8263295867508305</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.607593225208781</v>
+        <v>0.6742995940162828</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.6562058066986651</v>
+        <v>0.723831910239106</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.9106138839784279</v>
+        <v>0.9495122587387144</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.9505325183291262</v>
+        <v>0.9610386172645988</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.7267583071809867</v>
+        <v>0.708703836330109</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.3890566683012793</v>
+        <v>0.3424870788965677</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.3602756958660152</v>
+        <v>0.3424988769950801</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.3736585763162807</v>
+        <v>0.3850245799398309</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.3849841744601434</v>
+        <v>0.4254556607674118</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.3769469532267209</v>
+        <v>0.4466591012833447</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.2537584341420498</v>
+        <v>0.3232388001911843</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.1499636451769319</v>
+        <v>0.2192460255736606</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>0.5277520873665651</v>
+        <v>0.5976887087952178</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0.3063777394311771</v>
+        <v>0.3764234550933381</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>0.2903143213277559</v>
+        <v>0.360059582989841</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.4374620677137315</v>
+        <v>0.478119719490266</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.5339</t>
+          <t>X &gt; 0.5338</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.8990493259565255</v>
+        <v>0.9323236182753547</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.7163128357024391</v>
+        <v>0.7499858443157805</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.30913269681956</v>
+        <v>1.344487120488047</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.154282473057286</v>
+        <v>1.19047619047619</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.297142769334059</v>
+        <v>1.362815799229736</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.4680472197392191</v>
+        <v>0.5335218227254899</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.168758323457553</v>
+        <v>1.2351503746075</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.8902036779389917</v>
+        <v>0.9569389298544237</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.7284677104412935</v>
+        <v>0.7951740792487954</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.8184534378832495</v>
+        <v>0.8860795414236904</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.071939847566405</v>
+        <v>1.109326175455529</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.12800475211462</v>
+        <v>1.13545482078802</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.664754632304998</v>
+        <v>0.6728618596229623</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.4230001706244124</v>
+        <v>0.4009699750462872</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.2220841987626798</v>
+        <v>0.230781385431726</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.2064572254833053</v>
+        <v>0.2454607108727203</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.1741447018178448</v>
+        <v>0.2132729736917796</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>0.3236142119312149</v>
+        <v>0.3933263599878387</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0.08172210768745458</v>
+        <v>0.1512024737365891</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.0652035623409688</v>
+        <v>0.1344859427376974</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.4380336876941513</v>
+        <v>0.5079703091228041</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>0.3111880468098178</v>
+        <v>0.3812337624719788</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>0.2806197018415659</v>
+        <v>0.350364963503651</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>0.3879777515751286</v>
+        <v>0.4272044660055698</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.5757</t>
+          <t>X &gt; 0.5756</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1849</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.461013729384341</v>
+        <v>1.49428802170317</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.288000376902176</v>
+        <v>1.321673385515517</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.523975588491709</v>
+        <v>1.559330012160196</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.242614707730993</v>
+        <v>1.278808425149897</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.68815573351776</v>
+        <v>1.753828763413438</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.172617643821837</v>
+        <v>1.238092246808108</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.642994755011053</v>
+        <v>1.709386806161</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.20227794733033</v>
+        <v>1.269013199245762</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.757307525866473</v>
+        <v>0.8240138946739748</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.064553196178124</v>
+        <v>1.132179299718565</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.100507481784106</v>
+        <v>1.135968671610222</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.145913307892762</v>
+        <v>1.181543592486555</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.9949212781562906</v>
+        <v>1.031354498603399</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.9358143319137184</v>
+        <v>0.9724377843189842</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>0.7636326872517571</v>
+        <v>0.8336986935412227</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.7096932777060161</v>
+        <v>0.7790861563170921</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.7378494483488751</v>
+        <v>0.8074188841314012</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>0.9573657618371456</v>
+        <v>1.027077909893769</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.5244894656018531</v>
+        <v>0.5939698316509876</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.4411168199026534</v>
+        <v>0.510399200299382</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>0.7632490231275213</v>
+        <v>0.8331856445561741</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>0.6332106792209871</v>
+        <v>0.7032563948831481</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>0.6375694043834841</v>
+        <v>0.7073146660455691</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>0.5616280651150163</v>
+        <v>0.6314824128222938</v>
       </c>
     </row>
     <row r="24">
@@ -4660,243 +4660,243 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.642554945207955</v>
+        <v>1.701777741388007</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.481696687972097</v>
+        <v>1.541216970912757</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.378428530684339</v>
+        <v>1.438854135586759</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.129481237247141</v>
+        <v>1.19047619047619</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.752009244204494</v>
+        <v>1.841909875884781</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.183799075107856</v>
+        <v>1.273939941192388</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.689259497382714</v>
+        <v>1.77957546171551</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.468810604333648</v>
+        <v>1.559436026253955</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.9873748971308203</v>
+        <v>1.078275124544959</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.259443030812292</v>
+        <v>1.350655615755862</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1.27763025084846</v>
+        <v>1.334355211460178</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.405513091559605</v>
+        <v>1.462109873052832</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>1.094975361444561</v>
+        <v>1.151955936278014</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1.280595294596246</v>
+        <v>1.337381124872074</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>0.7960826602101037</v>
+        <v>0.8888504488597491</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>0.8097473609942867</v>
+        <v>0.9021798461077921</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>0.9082118063802369</v>
+        <v>1.000685719008295</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>1.326484204238454</v>
+        <v>1.418796787412568</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>0.670514343914455</v>
+        <v>0.7631018812944816</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.625</v>
+        <v>0.717524681384532</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>0.6631949398392507</v>
+        <v>0.7560360381134359</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>0.5872398841966415</v>
+        <v>0.680190076704335</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>0.6294569111438975</v>
+        <v>0.7222417793084119</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>0.6116551067591445</v>
+        <v>0.7045152785546307</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.6594</t>
+          <t>X &gt; 0.6593</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1597</v>
+        <v>1599</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.083075089868728</v>
+        <v>2.171652886568033</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.810477798002871</v>
+        <v>1.899376088218219</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.747498235043139</v>
+        <v>1.836357039187227</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.409174258520828</v>
+        <v>1.498403019744494</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.857421369616929</v>
+        <v>1.975112547197213</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.231069086503567</v>
+        <v>1.349578733294599</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1.772345632797474</v>
+        <v>1.890130049404242</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.556369210057383</v>
+        <v>1.674418604651166</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1.284994161187647</v>
+        <v>1.340905786565877</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>1.82530142876616</v>
+        <v>1.880490110529379</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1.511025716183177</v>
+        <v>1.529549752691302</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>1.482401443265566</v>
+        <v>1.500800349243299</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.297171339368276</v>
+        <v>1.377638282387188</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1.388901566530542</v>
+        <v>1.469059405940598</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>1.043057365689855</v>
+        <v>1.161682212174924</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>0.8867085236393564</v>
+        <v>1.005600090965942</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.9404670524084082</v>
+        <v>1.059300214776471</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>1.399040305067032</v>
+        <v>1.51731129331926</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.8011371686876529</v>
+        <v>0.9201945441622925</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>0.9255635566687488</v>
+        <v>1.044501267200978</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>1.071154631703358</v>
+        <v>1.189885055457594</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>0.8699647607821035</v>
+        <v>0.9889609201898324</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>0.9568877043462649</v>
+        <v>1.075818371883891</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>1.068798587995765</v>
+        <v>1.18760337944861</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.7012</t>
+          <t>X &gt; 0.7011</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1443</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.450532333861389</v>
+        <v>1.483806626180218</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.7690964314054369</v>
+        <v>0.8027694400187784</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.7836895961281556</v>
+        <v>0.8190440197966424</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.9701732912452528</v>
+        <v>1.006367008664157</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.020415971595163</v>
+        <v>1.086089001490841</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.8613201967903166</v>
+        <v>0.9267947997765873</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1.47349561598282</v>
+        <v>1.539887667132767</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.264193048026591</v>
+        <v>1.330928299942023</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.236457035486893</v>
+        <v>1.303163404294395</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.432150710590044</v>
+        <v>1.499776814130485</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>1.331982456363455</v>
+        <v>1.35832399091845</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>1.468688968688966</v>
+        <v>1.495087052844411</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.9678983739024503</v>
+        <v>0.9951936840492337</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1.300942117268654</v>
+        <v>1.328131428101265</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>1.265711501931975</v>
+        <v>1.33577750822144</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>0.959870650652455</v>
+        <v>1.029263529263531</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.9643770951036714</v>
+        <v>1.033946530886197</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>1.41379423340895</v>
+        <v>1.483506381465574</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>0.7983165647399346</v>
+        <v>0.8677969307890692</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>1.1239604989605</v>
+        <v>1.193242879357229</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>1.204460713663174</v>
+        <v>1.274397335091827</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>1.336405865920767</v>
+        <v>1.406451581582928</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>1.403280824502694</v>
+        <v>1.473026086164779</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>1.327339485234226</v>
+        <v>1.397193832941504</v>
       </c>
     </row>
     <row r="27">
@@ -4906,571 +4906,571 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.495507027205591</v>
+        <v>1.564964024582558</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.160331512561264</v>
+        <v>1.230187226232744</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.6899363796544407</v>
+        <v>0.7606911796230591</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.7838975091107159</v>
+        <v>0.8548396621980743</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1.226382166736101</v>
+        <v>1.326151691668564</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.4442414485635737</v>
+        <v>0.5445948753446359</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.125333313278531</v>
+        <v>1.225430695086239</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.008329556289851</v>
+        <v>1.027929500534938</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.4036420671929335</v>
+        <v>0.4237346808354445</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.326090985987321</v>
+        <v>1.345734259036234</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.277348476042889</v>
+        <v>1.296952900391055</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.644458126687532</v>
+        <v>1.663885498557271</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>1.004619573790045</v>
+        <v>1.024984932911799</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>1.752568093935018</v>
+        <v>1.772429058886516</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>1.578289520487374</v>
+        <v>1.598547262516618</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>1.688696904519098</v>
+        <v>1.708672683248949</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>1.312276877575343</v>
+        <v>1.332624795666156</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>2.095823348394447</v>
+        <v>2.115596844064505</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>1.181090291617046</v>
+        <v>1.201544722163973</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>1.287358642972535</v>
+        <v>1.307680281930224</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>1.471137232359069</v>
+        <v>1.491526365780167</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>1.960610286571061</v>
+        <v>1.980652155783503</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>2.154610008788261</v>
+        <v>2.174416618063781</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>2.240219558049674</v>
+        <v>2.260004865244056</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.7849</t>
+          <t>X &gt; 0.7848</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>1016</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.06603607456416682</v>
+        <v>0.09931036688299599</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.616687331573381</v>
+        <v>0.6503603401867224</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.9486404107943329</v>
+        <v>0.9839948344628198</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.03799670390038301</v>
+        <v>0.07419042131928677</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.7554040842306691</v>
+        <v>0.8210771141263464</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.2535923192846994</v>
+        <v>0.3190669222709701</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.760253746285791</v>
+        <v>0.826645797435738</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.6785494944680153</v>
+        <v>0.7452847463834473</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.7200655594906493</v>
+        <v>0.7867719282981511</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>1.521033298327524</v>
+        <v>1.588659401867965</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>1.007990990639705</v>
+        <v>1.075317469226732</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>1.713149055668751</v>
+        <v>1.780820034282684</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.9823586245831777</v>
+        <v>1.051358754828136</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.745253782052757</v>
+        <v>1.81453184688548</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>1.676873724117819</v>
+        <v>1.746939730407284</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>1.484532198936051</v>
+        <v>1.553925077547127</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>0.9567377173855576</v>
+        <v>1.026307153168084</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>1.737581072943819</v>
+        <v>1.807293221000442</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>0.9694522673717003</v>
+        <v>1.038932633420835</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>1.254921259842526</v>
+        <v>1.324203640239254</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>1.302272031946927</v>
+        <v>1.37220865337558</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>1.521592566855503</v>
+        <v>1.591638282517664</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>2.288493717589596</v>
+        <v>2.358238979251681</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>1.720426394069165</v>
+        <v>1.790280741776442</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.8267</t>
+          <t>X &gt; 0.8266</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>798</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.7919158919663332</v>
+        <v>-0.758641599647504</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-1.001778123402644</v>
+        <v>-0.9681051147893029</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.06052620653639451</v>
+        <v>-0.02517178286790767</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.150259369353613</v>
+        <v>-1.114065651934709</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.2623963222974552</v>
+        <v>-0.1967232924017779</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.7017981253307823</v>
+        <v>-0.6363235223445116</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.3468447085126201</v>
+        <v>-0.2804526573626731</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.1264803452169332</v>
+        <v>0.1932155971323652</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.04268312703155175</v>
+        <v>0.1093894958390536</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.3966672651343046</v>
+        <v>0.4642933686747455</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.2950866826255734</v>
+        <v>0.3624131612126007</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.6425591951907847</v>
+        <v>0.7102301738047174</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.1059921736723126</v>
+        <v>-0.03699204342735385</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>1.552350263413636</v>
+        <v>1.621628328246359</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>1.645298723624464</v>
+        <v>1.715364729913929</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>1.9897322068298</v>
+        <v>2.059125085440876</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>1.479698663056816</v>
+        <v>1.549268098839342</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>2.126594946209657</v>
+        <v>2.196307094266281</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>1.465525126685328</v>
+        <v>1.535005492734463</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>1.527255639097746</v>
+        <v>1.596538019494474</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>2.111874778971973</v>
+        <v>2.181811400400626</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>2.16123300653738</v>
+        <v>2.231278722199541</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>2.81194802264357</v>
+        <v>2.881693284305655</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>2.234753550543026</v>
+        <v>2.304607898250303</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.8686</t>
+          <t>X &gt; 0.8685</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>567</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.9404353387313904</v>
+        <v>-0.9071610464125612</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.04104295214115439</v>
+        <v>-0.00736994352781295</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.9883923862418413</v>
+        <v>1.023746809910328</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-1.665436200319917</v>
+        <v>-1.629242482901013</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.08569613105814966</v>
+        <v>0.151369160953827</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.4326066280691023</v>
+        <v>-0.3671320250828316</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.205472760123129</v>
+        <v>-1.139080708973182</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-2.189494777775728</v>
+        <v>-2.122759525860296</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-3.382546613987664</v>
+        <v>-3.315840245180162</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-2.569080437455504</v>
+        <v>-2.501454333915063</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.060153269105605</v>
+        <v>-0.9928267905185777</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.4244212577545881</v>
+        <v>0.4920922363685207</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.8764368037660546</v>
+        <v>-0.8074366735210958</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.3131411294676667</v>
+        <v>0.3824191943003896</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>0.7124109486314225</v>
+        <v>0.7824769549208881</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>1.13110415521929</v>
+        <v>1.200497033830366</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.6442767750033482</v>
+        <v>0.7138462107858743</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>1.421127574075619</v>
+        <v>1.490839722132243</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>0.2263159927393588</v>
+        <v>0.2957963587884933</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>0.2369929453262785</v>
+        <v>0.3062753257230071</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>2.33929518183097</v>
+        <v>2.409231803259622</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>2.439706969221866</v>
+        <v>2.509752684884027</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>2.185381606603471</v>
+        <v>2.255126868265556</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>2.462173953402022</v>
+        <v>2.5320283011093</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.9104</t>
+          <t>X &gt; 0.9103</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>388</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.1918579756924998</v>
+        <v>0.225132268011329</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.6298783373368337</v>
+        <v>0.6635513459501752</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1.252033543353789</v>
+        <v>1.287387967022276</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-1.008151522416682</v>
+        <v>-0.9719578049977784</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-1.373421307440729</v>
+        <v>-1.307748277545052</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1.959452570722611</v>
+        <v>-1.89397796773634</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-2.474586744013749</v>
+        <v>-2.408194692863802</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-2.237677472006531</v>
+        <v>-2.170942220091099</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-3.742553159561218</v>
+        <v>-3.675846790753717</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-3.227728776516209</v>
+        <v>-3.160102672975768</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.664709715586447</v>
+        <v>-1.59738323699942</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>1.406711844856176</v>
+        <v>1.474382823470108</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.7976845438948033</v>
+        <v>0.866684674139762</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>1.607255567912006</v>
+        <v>1.676533632744729</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>0.175128452586037</v>
+        <v>0.2451944588755026</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>0.2547245846816466</v>
+        <v>0.3241174632927226</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>0.3783628492956055</v>
+        <v>0.4479322850781315</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>1.046575309488986</v>
+        <v>1.11628745754561</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.0259613213936305</v>
+        <v>0.04351904465550405</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>0.6765463917525736</v>
+        <v>0.7458287721493022</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>2.71066557038349</v>
+        <v>2.780602191812143</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>3.665638349792424</v>
+        <v>3.735684065454585</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>2.909485681223011</v>
+        <v>2.979230942885096</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>3.606740218243196</v>
+        <v>3.676594565950474</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.9522</t>
+          <t>X &gt; 0.9521</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>268</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.4303562061895008</v>
+        <v>0.4636304985083299</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>1.214583676619803</v>
+        <v>1.248256685233144</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.9713854441827507</v>
+        <v>-0.9360310205142639</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-3.923984727525166</v>
+        <v>-3.887791010106262</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-4.289254512549213</v>
+        <v>-4.223581482653536</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-6.340895869691678</v>
+        <v>-6.275421266705408</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-5.621224688312864</v>
+        <v>-5.554832637162917</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-5.153510677115015</v>
+        <v>-5.086775425199583</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-6.23139759716701</v>
+        <v>-6.164691228359509</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-8.497770321369273</v>
+        <v>-8.430144217828833</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-5.984605084104679</v>
+        <v>-5.917278605517652</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-2.532355703997496</v>
+        <v>-2.464684725383563</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-1.418040952335389</v>
+        <v>-1.34904082209043</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.2262738784213028</v>
+        <v>0.2955519432540257</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-1.55206034569062</v>
+        <v>-1.481994339401155</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-1.330134624427444</v>
+        <v>-1.260741745816368</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-1.091093990218162</v>
+        <v>-1.021524554435636</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.8229430779552303</v>
+        <v>-0.7532309298986064</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-2.099357228456256</v>
+        <v>-2.029876862407122</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.04664179104477739</v>
+        <v>0.02264058935195123</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>1.275829441748314</v>
+        <v>1.345766063176967</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>2.692411699538546</v>
+        <v>2.762457415200707</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>2.967186866020675</v>
+        <v>3.036932127682761</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>2.891245526752208</v>
+        <v>2.961099874459485</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.9941</t>
+          <t>X &gt; 0.994</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>171</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-1.627337780019801</v>
+        <v>-1.594063487700971</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>1.546258635160434</v>
+        <v>1.579931643773776</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.4782371505631318</v>
+        <v>-0.4428827268946449</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-2.946416428668563</v>
+        <v>-2.910222711249659</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-5.066072178604898</v>
+        <v>-5.000399148709221</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-6.048498208872971</v>
+        <v>-5.9830236058867</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-7.990954984201849</v>
+        <v>-7.924562933051902</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-4.760737699895849</v>
+        <v>-4.694002447980417</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-6.473607599785488</v>
+        <v>-6.406901230977986</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-9.586624297104635</v>
+        <v>-9.518998193564194</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-7.557879065077017</v>
+        <v>-7.49055258648999</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-6.082587003639631</v>
+        <v>-6.014916025025698</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-3.698306292302213</v>
+        <v>-3.629306162057254</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.7586994697628455</v>
+        <v>0.8279775345955684</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-1.654617734186736</v>
+        <v>-1.584551727897271</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-1.059557684565355</v>
+        <v>-0.9901648059542794</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-1.778446700351701</v>
+        <v>-1.708877264569175</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.1290441515347069</v>
+        <v>-0.0593320034780831</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-1.667306953515165</v>
+        <v>-1.597826587466031</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>0.274122807017541</v>
+        <v>0.3434051874142696</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>2.654899006206726</v>
+        <v>2.724835627635379</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>4.91812523711382</v>
+        <v>4.988170952775981</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>2.853719117046246</v>
+        <v>2.923464378708331</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>2.777777777777779</v>
+        <v>2.847632125485056</v>
       </c>
     </row>
     <row r="34">
@@ -5483,76 +5483,76 @@
         <v>114</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.466229471442183</v>
+        <v>2.499503763761012</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>2.131053956797857</v>
+        <v>2.164726965411198</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1.568546475167864</v>
+        <v>1.603900898836351</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-2.654018767849855</v>
+        <v>-2.617825050430952</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-4.773674517786176</v>
+        <v>-4.708001487890499</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-6.340895869691678</v>
+        <v>-6.275421266705408</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-7.113762001745705</v>
+        <v>-7.047369950595758</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-3.006351734983561</v>
+        <v>-2.939616483068129</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-3.842028652417071</v>
+        <v>-3.775322283609569</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-6.370250028098773</v>
+        <v>-6.302623924558333</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-4.341504796071163</v>
+        <v>-4.274178317484136</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-3.743405717089921</v>
+        <v>-3.675734738475988</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.4819320232963591</v>
+        <v>-0.4129318930514003</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>2.805483095493848</v>
+        <v>2.874761160326571</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>0.3921658915442592</v>
+        <v>0.4622318978337248</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>0.9872259411656401</v>
+        <v>1.056618819776716</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.02406073543942711</v>
+        <v>0.04550870034309895</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>1.625341813377581</v>
+        <v>1.695053961434205</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-2.544499935971309</v>
+        <v>-2.475019569922175</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>1.151315789473685</v>
+        <v>1.220598169870414</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>2.362501345388019</v>
+        <v>2.432437966816671</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>7.549704184482245</v>
+        <v>7.619749900144406</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>5.192900403595949</v>
+        <v>5.262645665258034</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>4.239766081871345</v>
+        <v>4.309620429578622</v>
       </c>
     </row>
     <row r="35">
@@ -5565,76 +5565,76 @@
         <v>69</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.05093299995368739</v>
+        <v>-0.01765870763485822</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>1.063166847720822</v>
+        <v>1.096839856334164</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.3765336163653146</v>
+        <v>-0.3411791926968277</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-3.988877654196159</v>
+        <v>-3.952683936777255</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-5.803422801539043</v>
+        <v>-5.737749771643365</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-11.41335963780762</v>
+        <v>-11.34788503482135</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-9.287675045223963</v>
+        <v>-9.221282994074016</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-6.667678966104845</v>
+        <v>-6.600943714189413</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-3.727612176444524</v>
+        <v>-3.660905807637022</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-5.950722949532803</v>
+        <v>-5.883096845992362</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-5.676363682417467</v>
+        <v>-5.609037203830439</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-8.854008310530041</v>
+        <v>-8.786337331916108</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-9.978499529017185</v>
+        <v>-9.909499398772226</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-2.953479528457343</v>
+        <v>-2.88420146362462</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-5.061686129813481</v>
+        <v>-4.991620123524015</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-4.4666260801921</v>
+        <v>-4.397233201581024</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-3.151444412022187</v>
+        <v>-3.081874976239661</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.3578771034797867</v>
+        <v>-0.2881649554231629</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-3.040304665185651</v>
+        <v>-2.970824299136517</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-1.403985507246375</v>
+        <v>-1.334703126849647</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.4979105539254931</v>
+        <v>-0.4279739324968403</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>5.223235839707264</v>
+        <v>5.293281555369425</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>2.599460281551707</v>
+        <v>2.669205543213792</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.3750317823544407</v>
+        <v>-0.3051774346471632</v>
       </c>
     </row>
   </sheetData>
@@ -5831,76 +5831,76 @@
         <v>66</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-4.398759086910211</v>
+        <v>-4.365484794591382</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-6.950473390983362</v>
+        <v>-6.149536955260039</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-12.16541529492903</v>
+        <v>-11.93538209124755</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-14.37174592155502</v>
+        <v>-14.09761147300914</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-10.25940376628056</v>
+        <v>-11.53485122091873</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-4.102089899542428</v>
+        <v>-4.804833031411292</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>4.080267849000563</v>
+        <v>4.14665990015051</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>8.279325143780511</v>
+        <v>8.346060395695943</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>3.843229268504636</v>
+        <v>3.909935637312138</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>1.576856544302366</v>
+        <v>1.644482647842807</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-1.133858815447965</v>
+        <v>-1.066532336860938</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-5.890564659221376</v>
+        <v>-5.822893680607443</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-7.015055877708519</v>
+        <v>-6.946055747463561</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-4.251338061877199</v>
+        <v>-4.182059997044476</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-4.9102693009145</v>
+        <v>-4.840203294625034</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-8.792821191591628</v>
+        <v>-8.723428312980552</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-2.956765632009208</v>
+        <v>-2.887196196226682</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-4.554286361537322</v>
+        <v>-4.484574213480698</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-5.016589250165893</v>
+        <v>-5.761220145989206</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-4.82954545454546</v>
+        <v>-5.574374336021179</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-8.403048893846439</v>
+        <v>-9.101995130852885</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-5.448700919186024</v>
+        <v>-6.192766465396311</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-6.689077267855403</v>
+        <v>-6.619332006193318</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-2.219564061669324</v>
+        <v>-2.149709713962046</v>
       </c>
     </row>
     <row r="7">
@@ -5913,158 +5913,158 @@
         <v>92</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-7.840788072417467</v>
+        <v>-7.807513780098638</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-6.640875867763548</v>
+        <v>-6.05895724511511</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-11.83197610788551</v>
+        <v>-11.66364296081277</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-9.354280059376542</v>
+        <v>-9.251596980255513</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-4.400400908230374</v>
+        <v>-5.420720786136123</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.04208285371257148</v>
+        <v>-0.4859475824948873</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>5.652195445062802</v>
+        <v>5.718587496212749</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>6.437470586778289</v>
+        <v>6.504205838693721</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>5.415156864566875</v>
+        <v>5.481863233374376</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>2.513661879329369</v>
+        <v>2.58128798286981</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.4034682152574192</v>
+        <v>-0.3361417366703918</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-4.937881267668502</v>
+        <v>-4.870210289054569</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-4.998542698921604</v>
+        <v>-4.929542568676645</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-2.028410148253819</v>
+        <v>-1.959132083421096</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-3.751171174525176</v>
+        <v>-3.68110516823571</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-6.34760048660592</v>
+        <v>-6.278207607994844</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-1.162545244584628</v>
+        <v>-1.092975808802102</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-3.864188463928599</v>
+        <v>-4.389305874325409</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-4.127261186924777</v>
+        <v>-5.237244280635132</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-3.940217391304344</v>
+        <v>-5.050398470667105</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-6.657330843780557</v>
+        <v>-7.720604213101211</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-5.646329377684047</v>
+        <v>-6.160668888763354</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-5.371554211201918</v>
+        <v>-5.301808949539833</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-2.186625985252988</v>
+        <v>-2.11677163754571</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.05186</t>
+          <t>X &lt; -0.05187</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>137</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-2.610291618516754</v>
+        <v>-2.577017326197925</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-6.152154063252262</v>
+        <v>-5.748673557171855</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-6.52813407512874</v>
+        <v>-6.477472748046814</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-5.083654007026929</v>
+        <v>-5.062767193021472</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-2.571225950324369</v>
+        <v>-3.270898091100662</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.4936365044090394</v>
+        <v>0.1531501618660229</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>3.317892674513288</v>
+        <v>3.384284725663235</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>3.039338028994727</v>
+        <v>3.106073280910159</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.9225807127224002</v>
+        <v>0.989287081529902</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-1.290103618910344</v>
+        <v>-1.222477515369903</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-5.332291114384937</v>
+        <v>-5.264964635797909</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-6.330809478291492</v>
+        <v>-6.263138499677559</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-6.016451775915321</v>
+        <v>-5.947451645670363</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-3.360110745223068</v>
+        <v>-3.290832680390345</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-5.457890905123669</v>
+        <v>-5.387824898834204</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-7.021104236797257</v>
+        <v>-6.951711358186181</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-4.277500089219558</v>
+        <v>-4.207930653437032</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-6.879616233914568</v>
+        <v>-7.190469198984836</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-6.277372262773717</v>
+        <v>-6.97457781806051</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-6.090328467153284</v>
+        <v>-6.787732008092483</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-8.093382890749773</v>
+        <v>-8.769127096921814</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-7.439410939093115</v>
+        <v>-7.750196705500144</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-7.164635772610985</v>
+        <v>-7.0948905109489</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-5.780723097280919</v>
+        <v>-5.710868749573642</v>
       </c>
     </row>
     <row r="9">
@@ -6077,240 +6077,240 @@
         <v>181</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-3.944391676021063</v>
+        <v>-3.911117383702233</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-6.726688224742951</v>
+        <v>-6.408056344214209</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-6.268669515628801</v>
+        <v>-6.22445377162358</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-5.343118566526876</v>
+        <v>-5.315786169444699</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-5.161940264119231</v>
+        <v>-5.651576641991973</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-1.149639039090587</v>
+        <v>-1.384116918879322</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.8097352660138526</v>
+        <v>0.8761273171637995</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.5311806204952916</v>
+        <v>0.5979158724107236</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.5201994893454582</v>
+        <v>-0.4534931205379564</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-3.479827249841655</v>
+        <v>-3.412201146301214</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-6.484156507316492</v>
+        <v>-6.416830028729464</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-8.402594673086476</v>
+        <v>-8.334923694472543</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-5.701949279551755</v>
+        <v>-5.632949149306796</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-4.830409915722718</v>
+        <v>-4.761131850889996</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-7.675133504486801</v>
+        <v>-7.605067498197336</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-9.265865804592195</v>
+        <v>-9.196472925981119</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-6.667719061582645</v>
+        <v>-6.598149625800119</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-8.129815310200591</v>
+        <v>-8.342334591916391</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-8.180828326007173</v>
+        <v>-8.672891298423757</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-7.441298342541437</v>
+        <v>-7.939597401024038</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-9.089471127229992</v>
+        <v>-9.575039743853452</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-8.060453807182</v>
+        <v>-8.275758100626746</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-7.785678640699871</v>
+        <v>-7.715933379037786</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-6.756647604277731</v>
+        <v>-6.686793256570454</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; 0.03181</t>
+          <t>X &lt; 0.0318</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>244</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-5.69025043800886</v>
+        <v>-5.656976145690031</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-7.855450766548969</v>
+        <v>-7.604656169846301</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-6.26200551456256</v>
+        <v>-6.220094573715997</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-3.723766307430516</v>
+        <v>-3.707242141545841</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-4.089036092454563</v>
+        <v>-4.446258420544723</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.6498389591225759</v>
+        <v>-0.8098342221709913</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.6096969610952954</v>
+        <v>-0.5433049099453484</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-2.107763801735807</v>
+        <v>-2.041028549820375</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-3.28575993183513</v>
+        <v>-3.219053563027629</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-5.68561160276716</v>
+        <v>-5.61798549922672</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-7.850276725895725</v>
+        <v>-7.782950247308698</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-7.316362499289319</v>
+        <v>-7.248691520675386</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-4.375813067369961</v>
+        <v>-4.306812937125002</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-4.597169878404316</v>
+        <v>-4.527891813571593</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-7.695125507685525</v>
+        <v>-7.625059501396059</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-8.726081718226737</v>
+        <v>-8.656688839615661</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-6.014646957091109</v>
+        <v>-5.945077521308583</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-7.125105734062451</v>
+        <v>-7.269430420251723</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-6.283355271030267</v>
+        <v>-6.647034974286747</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-6.506147540983612</v>
+        <v>-6.86669322935937</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-7.049347949981566</v>
+        <v>-7.4092393973254</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-5.895794808902856</v>
+        <v>-6.04655872857024</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-6.440691773568268</v>
+        <v>-6.370946511906183</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-4.877288850541653</v>
+        <v>-4.807434502834376</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; 0.07365</t>
+          <t>X &lt; 0.07363</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>312</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-4.939944190560922</v>
+        <v>-4.898708748652091</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-3.533106444204648</v>
+        <v>-3.661158502976747</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-3.85664069658317</v>
+        <v>-3.994084601191318</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-2.022663309139389</v>
+        <v>-2.183379314640376</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-3.024875769322669</v>
+        <v>-3.297830490777478</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.2899404556789378</v>
+        <v>-0.4024053936895342</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.7443352501533482</v>
+        <v>-0.6779431990034013</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.978303908410766</v>
+        <v>-1.911568656495334</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-3.847615868865837</v>
+        <v>-3.780909500058335</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-5.576865292374116</v>
+        <v>-5.509239188833675</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-6.576391375577252</v>
+        <v>-6.509064896990225</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-4.944657253574448</v>
+        <v>-4.876986274960515</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-2.884435096265413</v>
+        <v>-2.815434966020455</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-3.742734582459008</v>
+        <v>-3.673456517626285</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-5.357079834235158</v>
+        <v>-5.287013827945692</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-5.717433797352633</v>
+        <v>-5.648040918741557</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-3.303756790864611</v>
+        <v>-3.234187355082085</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-4.826090281235949</v>
+        <v>-4.931384746801356</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-4.754351487928119</v>
+        <v>-5.033964703456647</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-5.528846153846153</v>
+        <v>-5.802532906227476</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-5.431020921818472</v>
+        <v>-5.708136399034274</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-5.18646315694825</v>
+        <v>-5.291521889553486</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-5.232200810978952</v>
+        <v>-5.162455549316867</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-3.705578047683311</v>
+        <v>-3.635723699976033</v>
       </c>
     </row>
     <row r="12">
@@ -6323,76 +6323,76 @@
         <v>393</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-2.28873097753921</v>
+        <v>-2.518652599716255</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-2.494145405243607</v>
+        <v>-2.725623911781788</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.803427764228097</v>
+        <v>-4.035196845524553</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.479246393876949</v>
+        <v>-1.603983914928882</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-2.857174406749103</v>
+        <v>-3.061883674465257</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.3679648898019963</v>
+        <v>0.2902352989511527</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.9112303561760839</v>
+        <v>-0.844838305026137</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.455607786504771</v>
+        <v>-2.388872534589339</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-3.426749949330244</v>
+        <v>-3.360043580522742</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-4.4537499170617</v>
+        <v>-4.386123813521259</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-4.938884320832429</v>
+        <v>-4.871557842245402</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-2.939497211649105</v>
+        <v>-2.871826233035172</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-3.304494759250176</v>
+        <v>-3.235494629005217</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-3.272687013322503</v>
+        <v>-3.203408948489781</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-3.931618252359804</v>
+        <v>-3.861552246070339</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-4.855545544510576</v>
+        <v>-4.7861526658995</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-3.9769810108114</v>
+        <v>-3.907411575028874</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-4.194410613374586</v>
+        <v>-4.265416835812083</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-4.345758808343078</v>
+        <v>-4.555854568811803</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-3.649809160305338</v>
+        <v>-3.86267964491973</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-3.175197864468693</v>
+        <v>-3.392567585037654</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-3.251152920111302</v>
+        <v>-3.325124977404798</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-2.976377753629173</v>
+        <v>-2.906632491967088</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-1.525601535645727</v>
+        <v>-1.455747187938449</v>
       </c>
     </row>
     <row r="13">
@@ -6405,158 +6405,158 @@
         <v>495</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.970714592123542</v>
+        <v>-2.149793435499561</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.800461579029658</v>
+        <v>-1.983592039271826</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-3.537528571604</v>
+        <v>-3.717036174385626</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.635627719807211</v>
+        <v>-1.726596980255508</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-2.604519235213559</v>
+        <v>-2.754972623143473</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.00286770067759079</v>
+        <v>-0.05052166831183058</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.9769410761923822</v>
+        <v>-0.9105490250424353</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.060324695554009</v>
+        <v>-1.993589443638577</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.415186900149074</v>
+        <v>-1.348480531341572</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.384193337075445</v>
+        <v>-1.316567233535004</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.914663043803166</v>
+        <v>-1.847336565216139</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.7853062430527231</v>
+        <v>-0.7176352644387904</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.3001395138537504</v>
+        <v>-0.2311393836087916</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.3202890814273402</v>
+        <v>-0.2510110165946173</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-1.180427563925406</v>
+        <v>-1.11036155763594</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-1.591403731607841</v>
+        <v>-1.522010852996765</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-1.121875695374477</v>
+        <v>-1.052306259591951</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.9071992166167604</v>
+        <v>-0.9559397199523687</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.7741650077416438</v>
+        <v>-0.9412555824888074</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.3851010101010104</v>
+        <v>-0.553202529060016</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>0.0817995910020457</v>
+        <v>-0.08971247972221619</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>0.2078647373796372</v>
+        <v>0.1565354123119249</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>0.4826399038617666</v>
+        <v>0.5523851655238516</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>1.416799574694302</v>
+        <v>1.48665392240158</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; 0.1992</t>
+          <t>X &lt; 0.1991</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>607</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.5695462423521036</v>
+        <v>-0.7187691913540419</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.963470406483502</v>
+        <v>-2.105705212594792</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-3.317849843497655</v>
+        <v>-3.459245566675968</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.080823484559659</v>
+        <v>-1.151066800810163</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.610027695813216</v>
+        <v>-1.723825361299511</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.1113876729703662</v>
+        <v>-0.1379417249705526</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.048188231253903</v>
+        <v>-0.9817961801039559</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.654611729231483</v>
+        <v>-1.587876477316051</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.12129238552032</v>
+        <v>-1.054586016712818</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.075455665142208</v>
+        <v>-1.007829561601767</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.948637381633425</v>
+        <v>-1.881310903046398</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.899862432649314</v>
+        <v>-1.832191454035382</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.5653372576938338</v>
+        <v>-0.496337127448875</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.6227596424986785</v>
+        <v>-0.5534815776659556</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-1.117756455306477</v>
+        <v>-1.047690449017011</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-2.162040667980179</v>
+        <v>-2.092647789369103</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-1.804331083440573</v>
+        <v>-1.734761647658047</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-1.814291753297738</v>
+        <v>-1.839602351479229</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-1.502833269304645</v>
+        <v>-1.623710970554903</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.725906095551899</v>
+        <v>-0.9450618818983543</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.1158939839567665</v>
+        <v>-0.3400670662578236</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.02710439380037144</v>
+        <v>-0.1539948064496599</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.08181851891625769</v>
+        <v>-0.1101613522858145</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>0.3364740792123087</v>
+        <v>0.4063284269195861</v>
       </c>
     </row>
     <row r="15">
@@ -6569,76 +6569,76 @@
         <v>720</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.712582944212336</v>
+        <v>-2.821174982284425</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.977660056571189</v>
+        <v>-3.08643102532487</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-3.933845869329744</v>
+        <v>-4.043779947114139</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.443782433211609</v>
+        <v>-2.491480382175958</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-3.286681172353639</v>
+        <v>-3.440409430824765</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.030551042105465</v>
+        <v>-1.117236947585731</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.527555105193976</v>
+        <v>-1.537728077317524</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.591211674888577</v>
+        <v>-1.678198475238645</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.195890485422822</v>
+        <v>-1.284094213434123</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.8632252046293232</v>
+        <v>-0.9535616136085565</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.557054042631549</v>
+        <v>-1.645019212825943</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.559522773215718</v>
+        <v>-1.569986943574378</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.8859503679130896</v>
+        <v>-0.8169502376681308</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.6923694196113459</v>
+        <v>-0.623091354778623</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.9363628993125488</v>
+        <v>-0.8662968930230832</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-1.724428714144828</v>
+        <v>-1.655035835533752</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-1.858522408293751</v>
+        <v>-1.788952972511225</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-1.60642180619768</v>
+        <v>-1.617168503441675</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-1.587009121556633</v>
+        <v>-1.677902295408082</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.9027777777777715</v>
+        <v>-1.076118726103957</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.75153374233129</v>
+        <v>-0.9271019618431566</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.1330443535294563</v>
+        <v>-0.2288188902526471</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.1360469648250984</v>
+        <v>-0.1489415552203468</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>0.06578947368420529</v>
+        <v>0.1356438213914828</v>
       </c>
     </row>
     <row r="16">
@@ -6648,161 +6648,161 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.714888791841915</v>
+        <v>-2.744789765761716</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-2.028504603468349</v>
+        <v>-2.061748313695659</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-3.165343538327413</v>
+        <v>-3.198074098537319</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.890829205496317</v>
+        <v>-1.929954294404197</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.793120723662312</v>
+        <v>-2.920970886176136</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.160172978125409</v>
+        <v>-1.227344343628481</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.348985162179964</v>
+        <v>-2.414397628092757</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.44062582600823</v>
+        <v>-2.506304286915096</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.090824766038487</v>
+        <v>-2.157435588584917</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.018227286844194</v>
+        <v>-2.085960432293298</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.59030090969258</v>
+        <v>-2.589713532332851</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.385718876045352</v>
+        <v>-2.31804789743142</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.575506346043987</v>
+        <v>-1.436677698242349</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.434106204236741</v>
+        <v>-1.294560448780956</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-1.367523537590856</v>
+        <v>-1.226311494545527</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-2.223491299335855</v>
+        <v>-2.084709076234503</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-2.478503977765314</v>
+        <v>-2.33969158851464</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-2.272113689787112</v>
+        <v>-2.202401541730488</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-1.74386197743862</v>
+        <v>-1.744379410200835</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-1.122572815533985</v>
+        <v>-1.194337474324826</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.9376178847261158</v>
+        <v>-1.010491390474868</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.5281360471648426</v>
+        <v>-0.5301703550390044</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.2533608806827132</v>
+        <v>-0.1836156190206282</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>0.1561346732527085</v>
+        <v>0.2988340468538908</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 0.3247</t>
+          <t>X &lt; 0.3246</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>942</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.152610387912389</v>
+        <v>-2.230188806221932</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-2.328624651487551</v>
+        <v>-2.406586254878007</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-3.29337172727832</v>
+        <v>-3.371758144058845</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-2.373317013463883</v>
+        <v>-2.457833877530142</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-3.524899260359163</v>
+        <v>-3.681694902960189</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.546375321746474</v>
+        <v>-1.653572527209612</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-2.683382254910263</v>
+        <v>-2.788694871731408</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-2.693267016852445</v>
+        <v>-2.799265605875142</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.853971829598933</v>
+        <v>-1.962703275604838</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.20497425939584</v>
+        <v>-2.314122639734059</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.670572708982405</v>
+        <v>-2.719659108068186</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.632541876727927</v>
+        <v>-2.623473673987952</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.065701171324996</v>
+        <v>-1.996701041080037</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.864225001386842</v>
+        <v>-1.794946936554119</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-2.100323259451621</v>
+        <v>-2.030257253162155</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-2.773762152747793</v>
+        <v>-2.704369274136717</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-2.953606822880253</v>
+        <v>-2.943994656357319</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-2.362912721264109</v>
+        <v>-2.414585888719721</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-2.085903816829337</v>
+        <v>-2.198694507795395</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-1.307059447983015</v>
+        <v>-1.483307471611731</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-1.531788519401353</v>
+        <v>-1.647205586511106</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.6523295623051055</v>
+        <v>-0.7080080540631428</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.3775543958229761</v>
+        <v>-0.3707378996988879</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.3473386225649051</v>
+        <v>-0.2774842748576276</v>
       </c>
     </row>
     <row r="18">
@@ -6815,76 +6815,76 @@
         <v>1047</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-2.259027066128148</v>
+        <v>-2.325057639747754</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.884651028043848</v>
+        <v>-1.953046301245564</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.613458632118309</v>
+        <v>-2.682946162319368</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.141977074211788</v>
+        <v>-2.21519264472299</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-3.308363513001495</v>
+        <v>-3.443519528274486</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.554166011871772</v>
+        <v>-1.695629009859324</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.275052324326353</v>
+        <v>-2.415989988402941</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.931727853342139</v>
+        <v>-2.074871840003524</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.457264460568631</v>
+        <v>-1.602276031615951</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.850871734455922</v>
+        <v>-1.943265813641233</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.861683570002185</v>
+        <v>-1.900597306132227</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.950663405036025</v>
+        <v>-1.936343525400567</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.649299110215189</v>
+        <v>-1.58029897997023</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.395370750146874</v>
+        <v>-1.326092685314151</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-1.388902749640458</v>
+        <v>-1.318836743350992</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-1.784570343074932</v>
+        <v>-1.770077197833849</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-2.054135923409355</v>
+        <v>-2.094108403252392</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-1.436889551497913</v>
+        <v>-1.53354986752985</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-1.165097230734936</v>
+        <v>-1.317658486605524</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.3492120343839531</v>
+        <v>-0.5045758498601671</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.6058794920925052</v>
+        <v>-0.7054066447121627</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.3953015964457194</v>
+        <v>-0.4388857260994641</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.02501544620046303</v>
+        <v>-0.01223045634367281</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.1009567854689308</v>
+        <v>-0.03110243776165333</v>
       </c>
     </row>
     <row r="19">
@@ -6894,161 +6894,161 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.322205029444177</v>
+        <v>-1.383902668987524</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.35018619676827</v>
+        <v>-1.412635206308281</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.394896162840766</v>
+        <v>-2.457121221682335</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.276327815578355</v>
+        <v>-2.340696196965695</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-3.293794748432738</v>
+        <v>-3.413606964997904</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.39776376120524</v>
+        <v>-1.523895547437753</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.859821546404199</v>
+        <v>-1.986287926162952</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.82702304516085</v>
+        <v>-1.954402356047524</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.210449705048653</v>
+        <v>-1.340038269378184</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.808846519326856</v>
+        <v>-1.889030886845951</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.973083743439588</v>
+        <v>-2.003615746433042</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.638142559195188</v>
+        <v>-1.619981859345657</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.095967111015661</v>
+        <v>-1.026966980770702</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.7032888343307135</v>
+        <v>-0.6340107694979906</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.8359042838943438</v>
+        <v>-0.7658382776048782</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-1.242338311872579</v>
+        <v>-1.224082934609243</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-1.325204632087896</v>
+        <v>-1.358000071586716</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.9391168266261332</v>
+        <v>-1.024244284179829</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.3190860491415606</v>
+        <v>-0.4574757102730587</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.07984581497797194</v>
+        <v>-0.218799270173939</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.3943908851884288</v>
+        <v>-0.5336767928417103</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.117612254764019</v>
+        <v>-0.2055521412387407</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.1073873528321556</v>
+        <v>-0.1425927829752212</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.09514527058386335</v>
+        <v>-0.07789019720861035</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 0.4502</t>
+          <t>X &lt; 0.4501</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.368874982857314</v>
+        <v>-1.42214663799615</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.9464488694802426</v>
+        <v>-1.001793618363855</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.866194836710555</v>
+        <v>-1.921579468749279</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.501436116001109</v>
+        <v>-1.559480220922715</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-2.221840387004683</v>
+        <v>-2.32884214278689</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.7942079207690895</v>
+        <v>-0.9054928657507588</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.283091075228135</v>
+        <v>-1.394503708557544</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.517016887072423</v>
+        <v>-1.628370239970344</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.270800582241634</v>
+        <v>-1.382977786001909</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.439287714388165</v>
+        <v>-1.552620424187296</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.64531275471878</v>
+        <v>-1.712662707372594</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.44402235074773</v>
+        <v>-1.466975430133189</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.9672325444150189</v>
+        <v>-0.9448617176128096</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.3078847917984504</v>
+        <v>-0.2386067269657275</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.3585088722884038</v>
+        <v>-0.3363016658593381</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.5976303455013081</v>
+        <v>-0.6226193075672697</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.6041626756832841</v>
+        <v>-0.6764723933037402</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.2600946693956132</v>
+        <v>-0.3809928409199657</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.1646443072734556</v>
+        <v>0.04269298068511063</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.3997385358004877</v>
+        <v>0.2772815784721132</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.3368799581122843</v>
+        <v>-0.4582156334762004</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>0.1507720715913194</v>
+        <v>0.07589025102159752</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.009468936353435708</v>
+        <v>-0.08371863778252475</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.4883111620038534</v>
+        <v>-0.5138824144179281</v>
       </c>
     </row>
     <row r="21">
@@ -7058,243 +7058,243 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1339</v>
+        <v>1342</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.573900329848065</v>
+        <v>-1.620274005423148</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.428175976442326</v>
+        <v>-1.475623911781781</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.238665281160223</v>
+        <v>-2.28634347589739</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.174607536669981</v>
+        <v>-2.223798747560373</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.426064917288265</v>
+        <v>-2.519867187511707</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.311310070875109</v>
+        <v>-1.408164629537268</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.043443718992187</v>
+        <v>-2.139620873104981</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.76268701763464</v>
+        <v>-1.860293359898314</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.531675304257938</v>
+        <v>-1.629992217868725</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.596446082031832</v>
+        <v>-1.696063143908489</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.989742601266641</v>
+        <v>-2.046458759521876</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.046284575958161</v>
+        <v>-2.061699650756687</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.687096269222756</v>
+        <v>-1.66076979767211</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.166613317645833</v>
+        <v>-1.09733525281311</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-1.114105354499586</v>
+        <v>-1.087822764043516</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-1.143844677431368</v>
+        <v>-1.161091628450677</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-1.160172390040607</v>
+        <v>-1.220824789167018</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-1.147214577599861</v>
+        <v>-1.251481516727083</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.9618948752928134</v>
+        <v>-1.066431284062766</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.8057004470938907</v>
+        <v>-0.9104724487265941</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-1.379796233009884</v>
+        <v>-1.483951519911308</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-1.038931584043546</v>
+        <v>-1.144347844216497</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-1.018857519965756</v>
+        <v>-1.123946279981091</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-1.244164057143102</v>
+        <v>-1.305199033385797</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.5339</t>
+          <t>X &lt; 0.5338</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1437</v>
+        <v>1440</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.545000526629913</v>
+        <v>-1.586052592884023</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.431977332766252</v>
+        <v>-1.473910409382874</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.285311002087866</v>
+        <v>-2.327223207726348</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.136637910337875</v>
+        <v>-2.180131640516322</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.326958554323816</v>
+        <v>-2.410189650604991</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.206505793881888</v>
+        <v>-1.292603397289597</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.148244760366389</v>
+        <v>-2.233064586084062</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.76774797921734</v>
+        <v>-1.854142992045325</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.549695609865942</v>
+        <v>-1.636711293323941</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.662991210702835</v>
+        <v>-1.751014024549875</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.010608446697383</v>
+        <v>-2.058812316274221</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.082376849135663</v>
+        <v>-2.092065420252901</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.439200713694554</v>
+        <v>-1.450055087778559</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.107307178947444</v>
+        <v>-1.078366302421529</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.826191420420777</v>
+        <v>-0.8380990955100316</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-0.8133280754548551</v>
+        <v>-0.8656886766769318</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-0.7681246373980599</v>
+        <v>-0.8207648673936632</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-0.970954753281795</v>
+        <v>-1.063918157660211</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-0.6446253362172385</v>
+        <v>-0.7382381700557232</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.625</v>
+        <v>-0.718460001874746</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-1.127373445829093</v>
+        <v>-1.220405159710673</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.9538216677003746</v>
+        <v>-1.047549416107394</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.9163183635724934</v>
+        <v>-1.009801587502601</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-1.061849125248749</v>
+        <v>-1.11435617860851</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.5757</t>
+          <t>X &lt; 0.5756</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1552</v>
+        <v>1556</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-2.022278966106583</v>
+        <v>-2.056563209756426</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.943181217915779</v>
+        <v>-1.978160373417793</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-2.268335806873111</v>
+        <v>-2.304505904975208</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.99347179251847</v>
+        <v>-2.031358885017418</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.515321629195277</v>
+        <v>-2.586910959791354</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.911322893273571</v>
+        <v>-1.984257884632939</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-2.458149756847753</v>
+        <v>-2.5308305103922</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.936030750646523</v>
+        <v>-2.01049546282178</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.412103264233977</v>
+        <v>-1.487915869485086</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.766808516972723</v>
+        <v>-1.842860749891273</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.811938067748756</v>
+        <v>-1.851827798329111</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.863385974639165</v>
+        <v>-1.903435451650118</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.672287951504607</v>
+        <v>-1.713597349796721</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.600698812541289</v>
+        <v>-1.642362319299018</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-1.38975527909534</v>
+        <v>-1.469834690361999</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-1.333961643179833</v>
+        <v>-1.41343098504224</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-1.366576743226695</v>
+        <v>-1.446224471357738</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-1.626690706947628</v>
+        <v>-1.705893991033399</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-1.116314829660254</v>
+        <v>-1.196599304010761</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-1.020244215938305</v>
+        <v>-1.10058941447506</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-1.397300087454539</v>
+        <v>-1.477513306491687</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-1.242546713031814</v>
+        <v>-1.323339530749912</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-1.251898005821019</v>
+        <v>-1.332358222109704</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-1.161301018870198</v>
+        <v>-1.242176801287755</v>
       </c>
     </row>
     <row r="24">
@@ -7304,243 +7304,243 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1681</v>
+        <v>1684</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.941884177330365</v>
+        <v>-1.999580993854011</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.894138283497362</v>
+        <v>-1.952163501224597</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.83347710229431</v>
+        <v>-1.892516200249396</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.633378932968533</v>
+        <v>-1.693244073620164</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-2.260844473281153</v>
+        <v>-2.349578992168247</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.688363478643389</v>
+        <v>-1.778066769350907</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-2.193314152600159</v>
+        <v>-2.282664068242823</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.967788345377478</v>
+        <v>-2.057776804412988</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.480594092566122</v>
+        <v>-1.571491151007748</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.749193253931956</v>
+        <v>-1.840156618993305</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.769993372885097</v>
+        <v>-1.827761568063416</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.897828987315101</v>
+        <v>-1.955504960491204</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.570646717834123</v>
+        <v>-1.628781434259807</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.75789163346338</v>
+        <v>-1.815863807290349</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-1.25841025295901</v>
+        <v>-1.351738941846691</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-1.27976480390307</v>
+        <v>-1.372770255748975</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-1.379344679897727</v>
+        <v>-1.472330842333818</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-1.805434297022899</v>
+        <v>-1.897803922921661</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-1.139742490756852</v>
+        <v>-1.233238385166324</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-1.096068249258167</v>
+        <v>-1.189603875527446</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-1.129601834176107</v>
+        <v>-1.223486075654655</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-1.0517906399228</v>
+        <v>-1.145936557993821</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-1.098690642986028</v>
+        <v>-1.192661742727807</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-1.080271072287111</v>
+        <v>-1.174398406109177</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.6594</t>
+          <t>X &lt; 0.6593</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1804</v>
+        <v>1806</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-2.085950540471494</v>
+        <v>-2.163823043410083</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.954502399847179</v>
+        <v>-2.032547830774668</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.940225454656698</v>
+        <v>-2.018243179870815</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.69213792751534</v>
+        <v>-1.770432596693865</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-2.082396377319768</v>
+        <v>-2.186071663329102</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.535843700553841</v>
+        <v>-1.640204590896303</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-2.003871891855589</v>
+        <v>-2.107743166841644</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.812327642316497</v>
+        <v>-1.916465524947952</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.575223024485858</v>
+        <v>-1.624753554093466</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.043183048597193</v>
+        <v>-2.092194056595417</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.768823781481856</v>
+        <v>-1.787350687352699</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.741705431132736</v>
+        <v>-1.760103613332362</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.567911434634631</v>
+        <v>-1.64080885417669</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.647214248748796</v>
+        <v>-1.719990180836263</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-1.336576814642058</v>
+        <v>-1.441494359959528</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-1.205756514974709</v>
+        <v>-1.31093180982927</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-1.252421532517701</v>
+        <v>-1.357613003530481</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-1.656619997226287</v>
+        <v>-1.761434942945961</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-1.131971932712752</v>
+        <v>-1.237455754253787</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-1.244469026548678</v>
+        <v>-1.349916514630898</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-1.368117398483292</v>
+        <v>-1.473471084418385</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-1.190168753677114</v>
+        <v>-1.295791164907612</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-1.270626835554559</v>
+        <v>-1.376253741532317</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-1.369601016584333</v>
+        <v>-1.475190434791607</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.7012</t>
+          <t>X &lt; 0.7011</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1958</v>
+        <v>1962</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.300384032013426</v>
+        <v>-1.322298726335191</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.901666804174809</v>
+        <v>-0.9246909818775961</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.9495029456541602</v>
+        <v>-0.9736833240822023</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.129912599545939</v>
+        <v>-1.154360735934468</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.163688013062838</v>
+        <v>-1.209862200277534</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.049756629185353</v>
+        <v>-1.096037739671551</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.490661697794337</v>
+        <v>-1.536753165964818</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.33555030159777</v>
+        <v>-1.382232887508671</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.316317823620949</v>
+        <v>-1.363041581855178</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.45289575962699</v>
+        <v>-1.500047864154162</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.38147916120775</v>
+        <v>-1.399971523904448</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.479624436477224</v>
+        <v>-1.4980909330679</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.102515987014705</v>
+        <v>-1.121981393069206</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.345137358079114</v>
+        <v>-1.364337346976704</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-1.313611006216156</v>
+        <v>-1.362916971294958</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-1.095549665195129</v>
+        <v>-1.14482387325026</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-1.098119929225419</v>
+        <v>-1.147545036080231</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-1.427861459570579</v>
+        <v>-1.476747493422458</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.9782434899658199</v>
+        <v>-1.027896423979023</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-1.220056065239547</v>
+        <v>-1.269095035676514</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-1.274651199411011</v>
+        <v>-1.324090759579477</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-1.371706485048726</v>
+        <v>-1.421054759161699</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-1.424331804028782</v>
+        <v>-1.473374211228901</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-1.368355345292073</v>
+        <v>-1.417618156182421</v>
       </c>
     </row>
     <row r="27">
@@ -7550,571 +7550,571 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2163</v>
+        <v>2166</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.06661911846809</v>
+        <v>-1.105442819233701</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.9658186595255529</v>
+        <v>-1.004874368820175</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.7328801683640407</v>
+        <v>-0.7725821469124483</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.8260980728461931</v>
+        <v>-0.8658467515272434</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.074348292047681</v>
+        <v>-1.130579672482426</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.6325052231992458</v>
+        <v>-0.6893406806248166</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.012844570553042</v>
+        <v>-1.069358040380457</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.9444047610779478</v>
+        <v>-0.9552789205550667</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.6014892874757933</v>
+        <v>-0.6128424940393558</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.119583168022551</v>
+        <v>-1.130404384883462</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.094762020013377</v>
+        <v>-1.10557530467446</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.301784422474071</v>
+        <v>-1.312388355990855</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.9281948745367075</v>
+        <v>-0.9395700318066531</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.352807246098749</v>
+        <v>-1.363661182294692</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-1.248330376750786</v>
+        <v>-1.259486190490527</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-1.317072344853422</v>
+        <v>-1.328022636670283</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-1.101754971028392</v>
+        <v>-1.113048068938596</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-1.548568065052933</v>
+        <v>-1.55928353977739</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-1.02883346351711</v>
+        <v>-1.040237312574519</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-1.091658975542217</v>
+        <v>-1.102952642644752</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-1.192438636144765</v>
+        <v>-1.203727134733889</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-1.47221551082994</v>
+        <v>-1.483150339384309</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-1.586293422003166</v>
+        <v>-1.597027745310371</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-1.635358623094952</v>
+        <v>-1.646058240781493</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.7849</t>
+          <t>X &lt; 0.7848</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2385</v>
+        <v>2389</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.2272775519301931</v>
+        <v>-0.2411787883905063</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.540248312169112</v>
+        <v>-0.5538072382023529</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.7108427710149243</v>
+        <v>-0.7248462803148428</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.3623748972586114</v>
+        <v>-0.3773234227627711</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.6628358570745121</v>
+        <v>-0.6899622036333568</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.4524231272863517</v>
+        <v>-0.4798250888906992</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.6608061316374574</v>
+        <v>-0.6882677062067302</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.6243033194841772</v>
+        <v>-0.6519847217521644</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.6424672489082965</v>
+        <v>-0.6701175079432744</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.9758239880089832</v>
+        <v>-1.0033269930911</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.7610356917005632</v>
+        <v>-0.7887787235784813</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.058031455403167</v>
+        <v>-1.085439759044903</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.7396715306624486</v>
+        <v>-0.7681950509461473</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.06185748978983</v>
+        <v>-1.089975608648814</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-1.02805131814663</v>
+        <v>-1.056577636427278</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.9515428361893683</v>
+        <v>-0.9799180794174518</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.7266952481425903</v>
+        <v>-0.7555339731185171</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-1.057966205729166</v>
+        <v>-1.086325374169945</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.7335919127752462</v>
+        <v>-0.7624046994125635</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.8567915445793304</v>
+        <v>-0.8853248072338573</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.8729742783446923</v>
+        <v>-0.9017754932549238</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.9660867591525033</v>
+        <v>-0.9947914721068045</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-1.295239476699933</v>
+        <v>-1.323275203860362</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-1.053183272647033</v>
+        <v>-1.081683279673584</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.8267</t>
+          <t>X &lt; 0.8266</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2603</v>
+        <v>2607</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.05779024695294055</v>
+        <v>0.04736581432468512</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.04784593674773419</v>
+        <v>0.03730876223875867</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.2660705552129627</v>
+        <v>-0.2766566594429136</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.03240564239420252</v>
+        <v>0.02110001251190141</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.2351543042087627</v>
+        <v>-0.2552282753465747</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.1028187998709953</v>
+        <v>-0.1230403143244558</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.2053650551808204</v>
+        <v>-0.2257236091323449</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.3476431077453697</v>
+        <v>-0.3678993518871465</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.3225347304463639</v>
+        <v>-0.3428280044333647</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.4249798982460646</v>
+        <v>-0.4454112629921738</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.3961482855287528</v>
+        <v>-0.4165380335682372</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.5003075318562793</v>
+        <v>-0.5206534499166793</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.2638082900918945</v>
+        <v>-0.2849381118068521</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.7687509972005842</v>
+        <v>-0.7892038726226431</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.7926491322326399</v>
+        <v>-0.8133193656460804</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.9025521232984701</v>
+        <v>-0.9228518454139802</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.7459804773228669</v>
+        <v>-0.7665827371258587</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.9433643521896542</v>
+        <v>-0.9637169612801699</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.7430253907124609</v>
+        <v>-0.7636200911333191</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.7635692366705058</v>
+        <v>-0.784078400913117</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.9389218211238131</v>
+        <v>-0.9593748986804087</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.9538483629131136</v>
+        <v>-0.9743205577173839</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-1.155632218281326</v>
+        <v>-1.175708656128251</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.9785717334699271</v>
+        <v>-0.9989617277710181</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.8686</t>
+          <t>X &lt; 0.8685</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2834</v>
+        <v>2838</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.01856322848091452</v>
+        <v>0.01172191837509473</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.2277843153531052</v>
+        <v>-0.2343651705230343</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.4577539519068239</v>
+        <v>-0.4643599947407182</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.03903130653021236</v>
+        <v>0.03155557397821696</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.3065392769501258</v>
+        <v>-0.3195803124457655</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.2048509889062586</v>
+        <v>-0.217998297517731</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.04606645632304662</v>
+        <v>-0.05962914499155403</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.151543001858542</v>
+        <v>0.1376281351346904</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.3887571573160997</v>
+        <v>0.3745107637828369</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.2321055800226475</v>
+        <v>0.2178849211885634</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.07015730194068226</v>
+        <v>-0.0838972834363787</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.3640860193917064</v>
+        <v>-0.3774891244408991</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.09744708511612288</v>
+        <v>-0.1115026442537328</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.3331652130412053</v>
+        <v>-0.3469518300144614</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.4085079703880936</v>
+        <v>-0.4223557567611351</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.4961623324741211</v>
+        <v>-0.509753188952061</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.3982803393594736</v>
+        <v>-0.4120499590470246</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.5528148458761919</v>
+        <v>-0.5664013646447046</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.3158303401783797</v>
+        <v>-0.3297072916887842</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.3193269908386185</v>
+        <v>-0.3331630805462709</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.7359656539750432</v>
+        <v>-0.7493549526520198</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.7557915718337966</v>
+        <v>-0.7691801715136179</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.7070346191460857</v>
+        <v>-0.7204346138123014</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.7621529712307122</v>
+        <v>-0.7755025258013717</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.9104</t>
+          <t>X &lt; 0.9103</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3013</v>
+        <v>3017</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.1826853056190458</v>
+        <v>-0.1868997450109191</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.3025423899173632</v>
+        <v>-0.3066538558423204</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.4061496587067026</v>
+        <v>-0.4103513215764352</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.1456459564940715</v>
+        <v>-0.1503045864458343</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.09666206581191972</v>
+        <v>-0.1053387044496858</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.02284902046699955</v>
+        <v>-0.03159919092287566</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.04795416987145273</v>
+        <v>0.03898469673450222</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.01937037815666542</v>
+        <v>0.0103895904737783</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.211947106001432</v>
+        <v>0.2027131744286592</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.1508843241346298</v>
+        <v>0.1416044292360752</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.05120203984152738</v>
+        <v>-0.06017797008097858</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.4434202161474872</v>
+        <v>-0.4519274487098102</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.3583592023551176</v>
+        <v>-0.3671602645084562</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.4609943783760784</v>
+        <v>-0.4697000919120597</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.2731307053417282</v>
+        <v>-0.2821936074363975</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.2871865050442253</v>
+        <v>-0.2961432506887007</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.3023226153046537</v>
+        <v>-0.3112860643463975</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.3876402940938135</v>
+        <v>-0.3965130308065739</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.2512419400869632</v>
+        <v>-0.260266937182152</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.3428488564799466</v>
+        <v>-0.3517288741547446</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.6012242816769984</v>
+        <v>-0.6098531915428111</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.723840373429951</v>
+        <v>-0.7323243895878804</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.6284712072493406</v>
+        <v>-0.6370439165493593</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.717990074200884</v>
+        <v>-0.7264616549831331</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.9522</t>
+          <t>X &lt; 0.9521</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3133</v>
+        <v>3137</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.1886968176646135</v>
+        <v>-0.1914800248243793</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.316745414848377</v>
+        <v>-0.3194035888947866</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.1541337192941938</v>
+        <v>-0.1571515105277754</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.06936915008961364</v>
+        <v>0.06599091964946524</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.1026501772000117</v>
+        <v>0.096547908413946</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.2760511312604024</v>
+        <v>0.2697451358302558</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.2195713315876304</v>
+        <v>0.2132514825050649</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.1815163155810851</v>
+        <v>0.1752115003060908</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.2730876007316851</v>
+        <v>0.2666672078856678</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.4708517731154132</v>
+        <v>0.4640945218273771</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.2552541069078416</v>
+        <v>0.2487957844373341</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.03716077245488236</v>
+        <v>-0.04328110518666506</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.125363120122401</v>
+        <v>-0.1314945003319963</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.264273701844715</v>
+        <v>-0.270255814904651</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.1086884084322932</v>
+        <v>-0.1149421243163715</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.1312579476394689</v>
+        <v>-0.1374235197764548</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.1508905488263892</v>
+        <v>-0.1570492211782621</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.1731972229676728</v>
+        <v>-0.1793424974189435</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.06554921308377715</v>
+        <v>-0.07181231563113499</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.2420704494740207</v>
+        <v>-0.2480926593995108</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.3518738783857103</v>
+        <v>-0.3578179276966935</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.4726243641621011</v>
+        <v>-0.4784264103355156</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.497938051827866</v>
+        <v>-0.5036822002949535</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.4911403415443587</v>
+        <v>-0.4969049690310641</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.9941</t>
+          <t>X &lt; 0.994</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3230</v>
+        <v>3234</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.06207099074926248</v>
+        <v>-0.06393584539389252</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.2885097125230445</v>
+        <v>-0.2901202262780913</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.2044572429863365</v>
+        <v>-0.2062696889233706</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.1012522361359558</v>
+        <v>-0.1032411105566808</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.01241350929907981</v>
+        <v>0.008562439604219207</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.0630450170078305</v>
+        <v>0.05914207892805479</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.169884441124637</v>
+        <v>0.1657952293488805</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.00139869469506948</v>
+        <v>-0.002504472271915859</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.09141821590937127</v>
+        <v>0.08740470931132904</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.2600742412676098</v>
+        <v>0.2557979923027744</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.1515734128646784</v>
+        <v>0.1474470424972836</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.07544121516977498</v>
+        <v>0.07138722539857412</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.04374151462728548</v>
+        <v>-0.04772766522452798</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.277687794694593</v>
+        <v>-0.2814029861679117</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.146499388512936</v>
+        <v>-0.1504237004589513</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.1814616827737652</v>
+        <v>-0.1853046192959837</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.1427541325094879</v>
+        <v>-0.1466563775784806</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.2293412477982315</v>
+        <v>-0.2331461685203138</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.1493699161768447</v>
+        <v>-0.153261175789261</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.2531694495980261</v>
+        <v>-0.256922066792896</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.3759795614879025</v>
+        <v>-0.3796199815760986</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.4953930884029418</v>
+        <v>-0.4988934325383454</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.3879039750386539</v>
+        <v>-0.391520662462348</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.3835569315445468</v>
+        <v>-0.3871865228674309</v>
       </c>
     </row>
     <row r="34">
@@ -8124,79 +8124,79 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3287</v>
+        <v>3291</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.2300126444214925</v>
+        <v>-0.2310704085436086</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.2770515290382178</v>
+        <v>-0.2780688257570318</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2797108064885094</v>
+        <v>-0.2807927192668771</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.1603715866976998</v>
+        <v>-0.1616317129646703</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.08522926672750941</v>
+        <v>-0.08776509630732221</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.03227257165840314</v>
+        <v>-0.03486520747301114</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.001171202714225217</v>
+        <v>-0.00383911625476685</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.1413326932830401</v>
+        <v>-0.1438456832230415</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.1127630292434532</v>
+        <v>-0.1153101843960229</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.02103102481960661</v>
+        <v>-0.02372698478075819</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.09270096831996</v>
+        <v>-0.0952989155895736</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.1117895441933001</v>
+        <v>-0.1143790331363448</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.2180825877000956</v>
+        <v>-0.2205976352384909</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.3305416798202359</v>
+        <v>-0.3329324147198065</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.2433731989003007</v>
+        <v>-0.2459020734581472</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.2674661760773915</v>
+        <v>-0.2699394674235478</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.2317749207204756</v>
+        <v>-0.2342993704706799</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.2883400529950038</v>
+        <v>-0.2908023992126374</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.1452758733847048</v>
+        <v>-0.1479032353965408</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.2744226678820993</v>
+        <v>-0.276886056629067</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.3133371871134543</v>
+        <v>-0.3157804845941996</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.4927872676201943</v>
+        <v>-0.4950177356167274</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.4128109550927377</v>
+        <v>-0.4151271385619637</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.3794408951086723</v>
+        <v>-0.3818027500660293</v>
       </c>
     </row>
     <row r="35">
@@ -8206,79 +8206,79 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3332</v>
+        <v>3336</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.1420796769877626</v>
+        <v>-0.1427822131640255</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.2227733664297062</v>
+        <v>-0.2233904394768373</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.214878684809328</v>
+        <v>-0.2155494249176328</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.1663706499417188</v>
+        <v>-0.1671214141053383</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.126986176521207</v>
+        <v>-0.1285573484808822</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.01253766073645579</v>
+        <v>-0.01424058692008145</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.05195250637395077</v>
+        <v>-0.05363299861245707</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.1043835528795611</v>
+        <v>-0.1060109896209056</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.1652612933261892</v>
+        <v>-0.1668157890831949</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.1150723349118365</v>
+        <v>-0.1167113820079351</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.1223245584816723</v>
+        <v>-0.1239475599393316</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.05520794994479417</v>
+        <v>-0.05692067823578384</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.02562373837526621</v>
+        <v>-0.02740728080372179</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.16941375165095</v>
+        <v>-0.1710332419972431</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.1221774345950948</v>
+        <v>-0.1238746240764357</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.1378922435176193</v>
+        <v>-0.1395534290271172</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.1643485619238731</v>
+        <v>-0.1659832361988194</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.2215462275756224</v>
+        <v>-0.2231166896099239</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.1673779280747283</v>
+        <v>-0.1690076079609995</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.202338129496404</v>
+        <v>-0.2039212124176473</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.2180504839604751</v>
+        <v>-0.2196324608247693</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.3360870783178243</v>
+        <v>-0.337530959283967</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.2834367037990049</v>
+        <v>-0.2849362052107622</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.2214921056141748</v>
+        <v>-0.2230692081848531</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/nasdaq_hourly_24hrs/volatility/bb_pct_20.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/volatility/bb_pct_20.xlsx
@@ -618,2379 +618,2379 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.1146</t>
+          <t>X ≈ -0.1145</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>26</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-17.14235713645416</v>
+        <v>-14.97783265949234</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-6.016460799248158</v>
+        <v>-3.763335308168251</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-11.33369272804691</v>
+        <v>-12.65489611130221</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>3.236126155127472</v>
+        <v>2.045739726860496</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>10.54930494527892</v>
+        <v>9.42071167649236</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>10.74734686010741</v>
+        <v>9.578586433809015</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>9.955260487614545</v>
+        <v>8.789454442131159</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>2.013525574744527</v>
+        <v>0.832718404337534</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>9.716372495034292</v>
+        <v>8.619041128476361</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>5.085650897801301</v>
+        <v>3.999064731230668</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>1.535653723154994</v>
+        <v>0.4405555687349363</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-2.590412483729445</v>
+        <v>-3.666819702557952</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.08035052610105708</v>
+        <v>-0.9454875024275964</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>3.690207461436891</v>
+        <v>2.641257476198298</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.8293086111613377</v>
+        <v>-1.873997924571533</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.2161070480006018</v>
+        <v>-1.314491620232616</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>3.489629993834619</v>
+        <v>2.41908673071655</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-4.302250570928855</v>
+        <v>-5.391358184358118</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-4.080426437924999</v>
+        <v>-5.178704282557888</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-3.887524379042716</v>
+        <v>-4.9660804018419</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-4.45471970262367</v>
+        <v>-5.534439023251537</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-6.076153185432965</v>
+        <v>-9.455230307034569</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-1.956766514221407</v>
+        <v>-5.369540323102207</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-2.033159597411057</v>
+        <v>-5.533376452482564</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.07279</t>
+          <t>X ≈ -0.07272</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>45</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>8.53223792019655</v>
+        <v>8.62005986375366</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-5.059023598115481</v>
+        <v>-4.86652327805313</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4.563201463520066</v>
+        <v>4.926894035682309</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3.854611233540162</v>
+        <v>4.339249365672501</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1.30895907853872</v>
+        <v>1.856433652358042</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1.494415081055756</v>
+        <v>2.012041262324637</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-1.486856721672552</v>
+        <v>-0.9900468644394778</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-3.977041839296177</v>
+        <v>-3.50526806145696</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-8.363522496244244</v>
+        <v>-7.802638935859903</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-9.135722932239787</v>
+        <v>-8.59725760529178</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-15.50930438044887</v>
+        <v>-14.96865862196789</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-9.145139053193546</v>
+        <v>-8.605767898087869</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-8.051834774393313</v>
+        <v>-7.504664502757073</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-6.058209667285908</v>
+        <v>-5.53915738388995</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-8.934102388017223</v>
+        <v>-8.437112163984175</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-8.343367088614556</v>
+        <v>-7.879635205102687</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-10.69866294145762</v>
+        <v>-10.20372414280499</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-13.02597471671612</v>
+        <v>-12.55755742544009</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-10.59402608070526</v>
+        <v>-10.12826894606016</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-10.41051264668559</v>
+        <v>-9.917190436351042</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-10.95602581148946</v>
+        <v>-10.48707275537893</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-11.0318625422418</v>
+        <v>-10.56554114422231</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-10.75748013632182</v>
+        <v>-10.32526188780001</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-13.05880062305346</v>
+        <v>-12.71286363197112</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.03095</t>
+          <t>X ≈ -0.03096</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>44</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-8.138549347387794</v>
+        <v>-6.984718096338597</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-8.473538377731849</v>
+        <v>-7.239363092878257</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-5.384981457255577</v>
+        <v>-3.999867482864133</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-6.096522244537844</v>
+        <v>-5.600179653780316</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-13.21958248314956</v>
+        <v>-12.65483864655054</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-6.247561560755749</v>
+        <v>-5.723144394215119</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-7.016547946797431</v>
+        <v>-6.516547616306781</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-7.295545024238983</v>
+        <v>-6.821819220850905</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-4.992402718296695</v>
+        <v>-4.433420295914317</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-10.29214044675414</v>
+        <v>-9.752894215382199</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-10.02155800250219</v>
+        <v>-9.483955323135255</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-14.8338011365347</v>
+        <v>-14.29093530695919</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-4.626448525899228</v>
+        <v>-4.081217186707804</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-9.382895707152116</v>
+        <v>-8.861775344808891</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-14.57789323043008</v>
+        <v>-14.07738223446314</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-16.2575113404757</v>
+        <v>-15.78888187515284</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-14.1272456883554</v>
+        <v>-13.63007380073817</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-11.96624691795224</v>
+        <v>-11.49827249019186</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-14.02491065442186</v>
+        <v>-13.55689480081254</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-11.57123439918951</v>
+        <v>-11.07703846164961</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-12.11718935762563</v>
+        <v>-11.64734467655063</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-9.921003282548668</v>
+        <v>-9.454933636403773</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-9.646623424002705</v>
+        <v>-9.214404228367087</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-9.725467289719624</v>
+        <v>-9.379530298637285</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ 0.01089</t>
+          <t>X ≈ 0.0108</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>63</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-10.7188261125012</v>
+        <v>-10.61153229888867</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-11.05463394925863</v>
+        <v>-10.85806118304448</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-6.173421790121964</v>
+        <v>-5.798921191375975</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1.011374962039724</v>
+        <v>1.499247142322858</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.9022306491816465</v>
+        <v>-0.3520560289039523</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.8624990239767243</v>
+        <v>1.380574417986537</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-4.64580221928027</v>
+        <v>-4.147151280826272</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-9.664986468170909</v>
+        <v>-9.189774083080437</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-11.20718297379227</v>
+        <v>-10.64444407088479</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-11.97998697559382</v>
+        <v>-11.43958045066772</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-11.71005393446568</v>
+        <v>-11.17127985930539</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-4.079826328431338</v>
+        <v>-3.543216530579294</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.4531877994014408</v>
+        <v>0.08957141948508252</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-3.840586804025989</v>
+        <v>-3.322683227123825</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-7.665722039934728</v>
+        <v>-7.169166841254778</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-7.074779253220939</v>
+        <v>-6.611475816168593</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-4.041450367313828</v>
+        <v>-3.550230496327302</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-4.147352736946694</v>
+        <v>-3.683987158558253</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.7614416128556698</v>
+        <v>-0.3013852641655888</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-3.747657559805148</v>
+        <v>-3.258110190973106</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-1.117654431214767</v>
+        <v>-0.654444655006813</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>0.393299201765501</v>
+        <v>0.856250594297812</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-2.505923338263813</v>
+        <v>-2.073690736158838</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>0.591993027740692</v>
+        <v>0.9379300188230317</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ 0.05271</t>
+          <t>X ≈ 0.05256</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>68</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-2.271790997385814</v>
+        <v>-4.418518835151218</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>10.54951875795764</v>
+        <v>9.267758074023256</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4.042271562170207</v>
+        <v>2.949750146491958</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3.325734663168483</v>
+        <v>6.738618356105995</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.8866742700550674</v>
+        <v>2.896248822445493</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.071361053684051</v>
+        <v>3.051251855610104</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-1.160431387982726</v>
+        <v>-0.6638734671347777</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.437163468907883</v>
+        <v>-0.966807700321155</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-5.789199851510013</v>
+        <v>-5.229575844888053</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-5.095349417172656</v>
+        <v>-4.558936485203219</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.892619057631386</v>
+        <v>-2.824125820535542</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>3.692075026930766</v>
+        <v>2.759002924376119</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.572619045011528</v>
+        <v>1.648068428333517</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.5806297882339351</v>
+        <v>-1.530564075981921</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>3.164845583375779</v>
+        <v>0.7221120347432048</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>5.226878656528854</v>
+        <v>2.748999005185894</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>6.56260252750802</v>
+        <v>5.57994255427473</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>3.522701498251593</v>
+        <v>2.513555231358666</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.8010425907335517</v>
+        <v>-0.2081028909855362</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-1.951327409387197</v>
+        <v>-2.931532351199991</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>0.4458180839764196</v>
+        <v>-0.5611108894851142</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-2.570263963108687</v>
+        <v>-3.576017847628556</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.825758091177164</v>
+        <v>-1.863638675358459</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>0.5686503573391946</v>
+        <v>-0.5560008868725745</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ 0.09457</t>
+          <t>X ≈ 0.09432</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>6.722776782166214</v>
+        <v>8.037353118013606</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.9078842198335408</v>
+        <v>3.170082599915531</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-4.226093412260084</v>
+        <v>-2.698810067927624</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.6600128869627397</v>
+        <v>-0.9779430223791366</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2.130445666285318</v>
+        <v>-4.717533614151456</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2.967929403800852</v>
+        <v>0.05854947140340983</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.485383640343962</v>
+        <v>-4.200630544433913</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-4.219862437751701</v>
+        <v>-6.817983747994205</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.720590535314315</v>
+        <v>-4.377473142370057</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.03099791015738163</v>
+        <v>-2.855692693019051</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.472392715141552</v>
+        <v>-0.2693895606384231</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>4.885828030671092</v>
+        <v>2.928901625988772</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-4.849279612939036</v>
+        <v>-6.291849341099038</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.377263824707555</v>
+        <v>-3.064164218979691</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>1.661126375631341</v>
+        <v>0.8926039880716914</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-1.44148912974304</v>
+        <v>-2.026600015094139</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-6.506260897955251</v>
+        <v>-7.932489217655757</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-1.681195068562225</v>
+        <v>-3.425615982780428</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-2.699490322525477</v>
+        <v>-4.373521519625733</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>3.655043369293239</v>
+        <v>1.64541538696723</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>5.582092162299837</v>
+        <v>3.402192916566747</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>4.272098773775461</v>
+        <v>2.165878683667344</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>5.78063509692285</v>
+        <v>4.734770658425369</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>6.941199376947033</v>
+        <v>5.736748771129889</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ 0.1364</t>
+          <t>X ≈ 0.1361</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.695186116701251</v>
+        <v>-0.2067640953230878</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.9222908333897024</v>
+        <v>1.4414852759448</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-2.45832528445488</v>
+        <v>-2.642573798185055</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-2.194051229369038</v>
+        <v>-3.233068424779376</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.551766550227306</v>
+        <v>-2.559005031774319</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.368019257339064</v>
+        <v>-3.353515069260283</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.159859804355186</v>
+        <v>-3.197203439432776</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.4604101435532257</v>
+        <v>-1.606047530148317</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>6.413506047085249</v>
+        <v>5.154313736365154</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>10.52830125985761</v>
+        <v>9.103545613099556</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>9.828359866702392</v>
+        <v>7.481560849043618</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>7.598845819981506</v>
+        <v>5.310530732456698</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>11.36872703873046</v>
+        <v>9.894664346006088</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>11.1520857929433</v>
+        <v>10.59971254479908</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>9.521466136481031</v>
+        <v>8.97400040983306</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>11.09642457746628</v>
+        <v>11.4364798285427</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>9.987510241087804</v>
+        <v>10.38592203887328</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>11.84431078070261</v>
+        <v>13.10796075835036</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>13.04336157777009</v>
+        <v>14.2772892003949</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>12.2546589939077</v>
+        <v>13.54488379823266</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>12.69645860550477</v>
+        <v>13.93384688320475</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>13.60069081499731</v>
+        <v>14.81496561903874</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>13.87505151335328</v>
+        <v>15.06337633603626</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>12.82355231812351</v>
+        <v>13.95380303469627</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ 0.1782</t>
+          <t>X ≈ 0.1779</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>5.672456936714276</v>
+        <v>6.133351384317884</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.658961674066788</v>
+        <v>-2.533513096853028</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-2.326832900318557</v>
+        <v>-2.107365004716648</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.400937422278773</v>
+        <v>1.509877759856025</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2.839967967973735</v>
+        <v>2.917385438724629</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.5241766009867064</v>
+        <v>0.1766555185526784</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.299730321377176</v>
+        <v>-0.6125036422089281</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.1971178757177796</v>
+        <v>0.7702254563575863</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.2393528756466168</v>
+        <v>0.8975165178688158</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.3520551615677903</v>
+        <v>0.9489166882342204</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.041784793073965</v>
+        <v>-2.153345282427736</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-6.771750468986539</v>
+        <v>-5.805721644998393</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.671431177334391</v>
+        <v>-1.853824818669835</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.894472956347002</v>
+        <v>-2.101876466748919</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.77679476188964</v>
+        <v>-0.2478265235109376</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-4.635217063121431</v>
+        <v>-3.913492138828211</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-4.771196430078518</v>
+        <v>-4.019046195722851</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-5.770310363043748</v>
+        <v>-4.153352460155133</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-4.662420404287225</v>
+        <v>-3.094706234138755</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-2.689947883355003</v>
+        <v>-1.189341741470734</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-1.451848711748717</v>
+        <v>-0.06356511285713395</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-1.528001391516462</v>
+        <v>-0.1388255061003179</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-3.036173781159576</v>
+        <v>-1.589675651392639</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-4.368324432576763</v>
+        <v>-2.599869281688129</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ 0.22</t>
+          <t>X ≈ 0.2196</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-14.29809497354682</v>
+        <v>-14.4630470042086</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-8.476179327405106</v>
+        <v>-6.286998810878657</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-7.308331541637095</v>
+        <v>-6.68926721074358</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-9.787951475687493</v>
+        <v>-8.122544886761553</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-12.778114265265</v>
+        <v>-12.60413044502808</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-6.40980530764103</v>
+        <v>-6.558004153199974</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-4.559188548095491</v>
+        <v>-3.98061830303417</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.203406191329847</v>
+        <v>-0.07244595272965171</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.535479456451014</v>
+        <v>-2.473781514379823</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.6742974292686625</v>
+        <v>-0.73749997297314</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.399199256237452</v>
+        <v>1.221217374595696</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.1686088637491423</v>
+        <v>0.9460776398931046</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.540625695437704</v>
+        <v>-1.009110974274208</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.9966656282919004</v>
+        <v>0.4317973522598209</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.1125603398560955</v>
+        <v>1.441618530839172</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.7063153395712192</v>
+        <v>2.002193298355778</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-2.078239594799072</v>
+        <v>-0.6370783632263723</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.415812562332448</v>
+        <v>0.9208855640911153</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-1.96891418803402</v>
+        <v>0.2893625381096072</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-1.782955856350846</v>
+        <v>0.5032258787426969</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-4.096051398188571</v>
+        <v>-1.756566943191352</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.6320743507483115</v>
+        <v>0.7080164094738208</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.3575996382662581</v>
+        <v>0.9518038226774195</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-1.318387643701925</v>
+        <v>-0.05749640033220516</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ 0.2619</t>
+          <t>X ≈ 0.2614</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.256728442464151</v>
+        <v>-2.147440920916765</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>5.143205918488619</v>
+        <v>3.985679943316441</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.7111854383771</v>
+        <v>2.742264390251528</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.994109191222783</v>
+        <v>0.3290039258600501</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.6813950881120832</v>
+        <v>0.969129696983309</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-2.021187340369316</v>
+        <v>-1.612785849720709</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-8.612277751182049</v>
+        <v>-7.871162944170649</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-8.339449859893435</v>
+        <v>-8.177759946528568</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-8.297042239889457</v>
+        <v>-7.141284016510397</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-10.04559677307758</v>
+        <v>-8.8487993308405</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-9.210274758391861</v>
+        <v>-8.580362607706981</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-7.552471382577863</v>
+        <v>-7.032799240762976</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-5.769141167105694</v>
+        <v>-5.405985032811031</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-5.991960741920764</v>
+        <v>-5.655648128272773</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-3.744816525543875</v>
+        <v>-4.508977723575356</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-5.090600027983676</v>
+        <v>-5.779954141541246</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-6.195654657650842</v>
+        <v>-6.801081758106584</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-6.302898794780205</v>
+        <v>-6.936840272027332</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-2.209170977859685</v>
+        <v>-3.978492949650466</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-2.023379875018627</v>
+        <v>-3.766346107930197</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-1.595836603103287</v>
+        <v>-3.418257387027538</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-2.642556350920152</v>
+        <v>-3.494951285953917</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.4263340656225694</v>
+        <v>-1.418629178566619</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>1.439581253969692</v>
+        <v>1.17092841695905</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ 0.3037</t>
+          <t>X ≈ 0.3032</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.362534326896238</v>
+        <v>0.1201223634841</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-4.835749292602621</v>
+        <v>-5.775698782720838</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-4.607660290231635</v>
+        <v>-4.596784573805834</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-6.159618083753266</v>
+        <v>-5.994314689473427</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-9.011626578754026</v>
+        <v>-7.879287529743934</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-4.632814721395889</v>
+        <v>-3.692228293852288</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-5.410713153664233</v>
+        <v>-4.480839293417375</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-4.852895698527412</v>
+        <v>-4.786221661224722</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.6225377195409578</v>
+        <v>-1.42878351674414</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-3.913913543809329</v>
+        <v>-4.646389705478803</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-3.639211561332367</v>
+        <v>-3.567881602542059</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-4.756986147015766</v>
+        <v>-5.463338483868895</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-5.884858709515719</v>
+        <v>-6.576900397483875</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-5.271147538309251</v>
+        <v>-6.017463083984254</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-7.612819141540868</v>
+        <v>-7.509706905413779</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-7.019360631299541</v>
+        <v>-6.142388399225709</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-7.157827080159549</v>
+        <v>-6.248823152713143</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-3.907606703392517</v>
+        <v>-3.95155026727425</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-5.370549087667783</v>
+        <v>-5.362193241905601</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-3.502258024382797</v>
+        <v>-3.527468022620326</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-6.066751182527284</v>
+        <v>-6.531820272861445</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-1.940916471667471</v>
+        <v>-1.735847947223988</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-1.666441759185417</v>
+        <v>-2.30580741843557</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-4.263282415770043</v>
+        <v>-4.907985583190133</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ 0.3456</t>
+          <t>X ≈ 0.3449</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-3.23681296414594</v>
+        <v>-3.965366772224122</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>2.122863282235905</v>
+        <v>1.253247810547428</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3.505423723970985</v>
+        <v>1.832068705597472</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.0627509273176301</v>
+        <v>-1.489207370860726</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.361828657507004</v>
+        <v>-1.758915529125346</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-2.108837994291392</v>
+        <v>-1.609371373865145</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.8990830154859353</v>
+        <v>1.246858271421303</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>4.416063307570717</v>
+        <v>3.677505228359529</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.613654846069224</v>
+        <v>1.981738322437984</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.382594588338584</v>
+        <v>3.015827840041176</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>5.457354732242834</v>
+        <v>5.113144663050484</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>4.226950518203154</v>
+        <v>4.839813295690853</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2.147624124090143</v>
+        <v>2.817604025727981</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2.876553004269489</v>
+        <v>3.484483139753642</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>5.065884530583013</v>
+        <v>5.548237997535999</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>6.616192774196293</v>
+        <v>6.110169225314138</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>5.531228960000917</v>
+        <v>5.093987923740634</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>6.381247457396</v>
+        <v>6.792587982142564</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>6.602442754720521</v>
+        <v>7.009163063716201</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>8.313329999444349</v>
+        <v>8.141193479260565</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>7.770783831478319</v>
+        <v>7.577927198288876</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>1.980652155783503</v>
+        <v>2.00543351375827</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>3.207507820646725</v>
+        <v>3.166712227841792</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>2.179294615042281</v>
+        <v>2.088359609619594</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 0.3874</t>
+          <t>X ≈ 0.3866</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>88</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>9.971388830261176</v>
+        <v>11.1487304079691</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>5.10336326039576</v>
+        <v>6.393317261352728</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.2698124572936678</v>
+        <v>1.769540628154104</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-3.842018752598541</v>
+        <v>-2.201311323821756</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-3.042099469529312</v>
+        <v>-2.470513134801728</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.5424057324663849</v>
+        <v>1.060521157071349</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>3.173460277226553</v>
+        <v>3.657643659441412</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.5045204743441971</v>
+        <v>1.098237251161216</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.803033520598397</v>
+        <v>3.482786224751024</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.234164735730609</v>
+        <v>-0.6945131666525768</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-3.227621595693535</v>
+        <v>-1.553896243080601</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>2.161249353438656</v>
+        <v>3.821899605110467</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>5.574123921746484</v>
+        <v>7.236521780225253</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>7.623303965866853</v>
+        <v>9.254468273949861</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>5.835193715270769</v>
+        <v>7.446994318540696</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>5.296641616051588</v>
+        <v>6.877466246043824</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>7.435824954503005</v>
+        <v>9.042369174722317</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>5.062200730869634</v>
+        <v>6.645715445002182</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>9.825618388610529</v>
+        <v>11.39782111580328</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>3.194282380396729</v>
+        <v>4.809859045407016</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>1.515372576067065</v>
+        <v>3.110627565000037</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>2.575890251021598</v>
+        <v>4.171863535398288</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-1.695089581951159</v>
+        <v>-0.1263476126357261</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.6345581988105309</v>
+        <v>0.847742428635442</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 0.4292</t>
+          <t>X ≈ 0.4284</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.861129273763865</v>
+        <v>-2.607133948516605</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>3.34500390640634</v>
+        <v>2.5576365384958</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>3.723252780288888</v>
+        <v>2.219813831546162</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>6.696928729876831</v>
+        <v>6.140204070353327</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>9.11916621828648</v>
+        <v>8.576191719829836</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>5.628274455331528</v>
+        <v>5.117122397745121</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>4.839512733148176</v>
+        <v>4.332252208384688</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.784267284151134</v>
+        <v>1.323641895825574</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.865261512954447</v>
+        <v>-2.161291837671072</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.965358761475912</v>
+        <v>1.56438401368986</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.318857413877033</v>
+        <v>1.83600862169714</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.1144300090147325</v>
+        <v>0.6563822395731052</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.09840509138970788</v>
+        <v>-0.454219323651202</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>3.9257880377614</v>
+        <v>2.916880051402465</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>4.188374625525931</v>
+        <v>3.144401691661429</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>5.7128206571806</v>
+        <v>5.516968373179282</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>6.505136111282113</v>
+        <v>6.321670696027702</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>6.403716365524247</v>
+        <v>6.190973836166791</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>5.322251385243511</v>
+        <v>4.593292117810492</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>5.509097195211751</v>
+        <v>3.901713940382535</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>0.3369213976158818</v>
+        <v>-0.2940317041109779</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>3.038853213984559</v>
+        <v>1.446807846176213</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>0.5355501486888343</v>
+        <v>-0.126335211072572</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-5.095837660089998</v>
+        <v>-5.743166662273858</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.471</t>
+          <t>X ≈ 0.4702</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>99</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-4.136700692962968</v>
+        <v>-5.007595843212833</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-7.495916364808522</v>
+        <v>-7.256916316679217</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-6.913890420920218</v>
+        <v>-6.492517065134052</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-10.65038988276581</v>
+        <v>-10.08521519268601</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-4.935783775464877</v>
+        <v>-4.346511979581386</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-7.775222011266408</v>
+        <v>-7.202739710060243</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-11.56955467713949</v>
+        <v>-9.996118868695291</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-4.789937995753093</v>
+        <v>-3.287217775766706</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-4.74880818627522</v>
+        <v>-4.164829334304535</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-3.503733760906108</v>
+        <v>-2.950644004661491</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-6.254470364676301</v>
+        <v>-6.696201977539388</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-9.557390612292359</v>
+        <v>-9.988216584962963</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-10.67894450318191</v>
+        <v>-9.094135591680597</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-11.90852704323028</v>
+        <v>-10.35285908629584</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-10.55401435058354</v>
+        <v>-9.025473881334875</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-7.946837903681612</v>
+        <v>-7.46446459156558</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-8.084526429593829</v>
+        <v>-7.572123608292259</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-12.23370733574838</v>
+        <v>-11.73796622913812</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-15.04811898512686</v>
+        <v>-14.55293294667246</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-15.87137418526029</v>
+        <v>-14.34621953054779</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-14.39371833302385</v>
+        <v>-13.91036518078035</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-16.48976631463496</v>
+        <v>-13.9927954724398</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-14.19508958195112</v>
+        <v>-12.74642369776431</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-11.24061880487114</v>
+        <v>-10.8946818137888</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.5129</t>
+          <t>X ≈ 0.512</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.132488199758185</v>
+        <v>-0.5447155619325486</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.468522492503013</v>
+        <v>-2.793364613901851</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.923308133476986</v>
+        <v>-2.047903496004629</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.604005969267874</v>
+        <v>-1.639730585596183</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.9255545915831362</v>
+        <v>-0.9145809499926472</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.2882283887033807</v>
+        <v>2.247792645263267</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-3.55117656899877</v>
+        <v>-2.977605466953605</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.792521017316083</v>
+        <v>-1.280265752910985</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.749357176207177</v>
+        <v>-0.1516157955663928</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.529398653818987</v>
+        <v>-0.9421931107971346</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.254919846858577</v>
+        <v>-0.6708008451824199</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.536184239097764</v>
+        <v>-0.9464746549819978</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.42737204275393</v>
+        <v>0.9555183156342295</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.8301546653299141</v>
+        <v>-1.303064476715697</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>2.582548580280637</v>
+        <v>2.038783501190345</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>3.183422566846652</v>
+        <v>2.598418394296651</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>4.67993504957991</v>
+        <v>3.502007046907032</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>1.516034985422976</v>
+        <v>1.356584816625507</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>3.772742692877685</v>
+        <v>3.585992763277069</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>1.918772176315329</v>
+        <v>1.785124872639642</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>2.396634171614608</v>
+        <v>2.228549379565671</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0.2799718836746621</v>
+        <v>-0.873548439209948</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>0.5544465961569429</v>
+        <v>-0.6307828866583662</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>1.499022506198742</v>
+        <v>1.226530307423559</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.5547</t>
+          <t>X ≈ 0.5537</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-8.025195191535154</v>
+        <v>-8.325768760343188</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-8.362516428773276</v>
+        <v>-7.702066733803008</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.080034489010146</v>
+        <v>-3.739179901121148</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.2175091708314199</v>
+        <v>-0.8531553196206403</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-4.869796017801889</v>
+        <v>-5.476812672495122</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-10.69708778183283</v>
+        <v>-13.14634437891377</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-6.324014814551226</v>
+        <v>-7.854210588329039</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-4.017417312426517</v>
+        <v>-5.046475578595334</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.3354773661353505</v>
+        <v>-0.5724328699940671</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-3.036665743811049</v>
+        <v>-3.103716914044213</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.6846539738173121</v>
+        <v>0.6505116056645619</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.4008156925932909</v>
+        <v>1.247154388427276</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-5.04138718757364</v>
+        <v>-5.095280714061985</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-8.70802984689518</v>
+        <v>-7.091628279380352</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-9.379512603313565</v>
+        <v>-7.775506014187236</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-8.260344880736255</v>
+        <v>-8.094773577198964</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-9.25720796081572</v>
+        <v>-9.951278186956287</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-9.708454810495425</v>
+        <v>-11.83816762574503</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-6.906356533019576</v>
+        <v>-9.00681850919279</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-5.857441757534311</v>
+        <v>-7.047598363853375</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-4.675849994466056</v>
+        <v>-6.741579119773448</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-4.751695955874958</v>
+        <v>-7.697399872946328</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-5.339290208910143</v>
+        <v>-7.458449744512166</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-2.828915565581688</v>
+        <v>-5.870758368812723</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.5966</t>
+          <t>X ≈ 0.5955</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.29547609999684</v>
+        <v>-1.57450316461982</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.630158727520765</v>
+        <v>-1.819908589479056</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3.179165821401384</v>
+        <v>4.620893534390525</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2.466462924161235</v>
+        <v>4.032001211495562</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.5695506808886677</v>
+        <v>2.99546757426549</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.7561087934069377</v>
+        <v>3.145381428436785</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.7656783982756181</v>
+        <v>3.129827114591187</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.635812467012776</v>
+        <v>-0.2490799680259173</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.594607797575662</v>
+        <v>-0.1256345475775262</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.805303043251683</v>
+        <v>-0.1449524472414936</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.531400352466186</v>
+        <v>0.1249609114490866</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.590757726689731</v>
+        <v>-1.689897110466376</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.5901695188811544</v>
+        <v>1.82183704291986</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-3.934339474211278</v>
+        <v>-3.820178856576007</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>0.0921661083600398</v>
+        <v>0.1243743866964948</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.8759469696969688</v>
+        <v>-0.0892421629907787</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-1.791114106674264</v>
+        <v>-0.1936053008280325</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-4.239704810495802</v>
+        <v>-1.871460658771738</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-1.680063429571298</v>
+        <v>-0.1144089127621299</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-2.274467619603449</v>
+        <v>-2.221805760219262</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>1.870486212430876</v>
+        <v>1.853854449170996</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>1.013390251021775</v>
+        <v>1.778736913770707</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>0.506614963503651</v>
+        <v>0.4730888045977011</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-0.3504672897196244</v>
+        <v>0.3103921819830404</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.6384</t>
+          <t>X ≈ 0.6372</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-4.456667808963303</v>
+        <v>-3.581813164410832</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-3.153016050164581</v>
+        <v>-3.828139106385244</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-3.771040477996436</v>
+        <v>-4.292252534370277</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2.845384465261674</v>
+        <v>-3.288824665894353</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.0960814215521637</v>
+        <v>-1.172523683285036</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.2825757725740985</v>
+        <v>-1.009722589498644</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.3305854148771488</v>
+        <v>-1.01464303409562</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.05241026512982216</v>
+        <v>-1.319563477504239</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.363908716204648</v>
+        <v>-3.122917657117476</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-5.593650590333041</v>
+        <v>-5.843897592508185</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.223973242872368</v>
+        <v>-1.578509176149701</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.9550109269171401</v>
+        <v>1.347746234949547</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.805962681988916</v>
+        <v>-1.363346838957114</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.3884678212637453</v>
+        <v>0.794271548075308</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-2.687034711312094</v>
+        <v>-1.490816672599038</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.45330352707402</v>
+        <v>0.6706840156231451</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>0.2324514670957711</v>
+        <v>1.369623204640106</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>0.1276107632748662</v>
+        <v>-0.3686655560686134</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-1.295842118095976</v>
+        <v>-0.9613282859764922</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-3.568012701570304</v>
+        <v>-2.357803304177814</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-4.930231000684238</v>
+        <v>-2.925879153702368</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-3.366732699798355</v>
+        <v>-1.393137096391825</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-3.911930118463566</v>
+        <v>-1.957144830391691</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-5.627106633982017</v>
+        <v>-2.927917395411662</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.6802</t>
+          <t>X ≈ 0.679</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>8.534230795155331</v>
+        <v>8.033108145916934</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>12.04298758406304</v>
+        <v>10.43004304926211</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>11.24650246855015</v>
+        <v>9.839007149283965</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>6.049736122237661</v>
+        <v>4.622639371862341</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>10.19858034498112</v>
+        <v>9.6342572501907</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>5.260330118336228</v>
+        <v>4.503716329695138</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>5.129872085415379</v>
+        <v>3.711768652154696</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>4.851703923210763</v>
+        <v>2.746175087492006</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1.69002282257712</v>
+        <v>0.2306652419950126</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>5.402088102219139</v>
+        <v>5.383806172754241</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>3.113388049090155</v>
+        <v>3.402867773358189</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>1.55364834093298</v>
+        <v>3.129197372840302</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4.915250817013238</v>
+        <v>5.992652910789651</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.772643200954448</v>
+        <v>3.102029806220862</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.448699276255347</v>
+        <v>1.098261298594338</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>0.7867132867132867</v>
+        <v>1.655193741802925</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>1.293821790761527</v>
+        <v>2.215020090845499</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>1.830006727965838</v>
+        <v>2.748811706128095</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>1.404872467864593</v>
+        <v>2.297487508154639</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.3313586452442934</v>
+        <v>0.5176121985910243</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>0.4081464688408829</v>
+        <v>1.281966079413166</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-2.872827697696273</v>
+        <v>-1.45691934748011</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-2.598352985214369</v>
+        <v>-1.881511586668985</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.7511083153606464</v>
+        <v>-0.7128636319706203</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.722</t>
+          <t>X ≈ 0.7208</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.9908947800012697</v>
+        <v>0.8731756453519068</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.793165055663138</v>
+        <v>-1.325128830693913</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.173451710850877</v>
+        <v>2.304975332182416</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.926672804112528</v>
+        <v>3.667947945474211</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.371938807970885</v>
+        <v>0.4666051181887525</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>3.248097281988315</v>
+        <v>3.548661817648991</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>3.449751335591792</v>
+        <v>4.224080476835141</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>3.171200419870289</v>
+        <v>4.407342142727565</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>6.644399621773026</v>
+        <v>7.46204813018381</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>2.435358803158778</v>
+        <v>2.767155697796255</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>1.731063114268657</v>
+        <v>2.549885415651673</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.4698847281472069</v>
+        <v>0.6120836023988261</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.8142556578692108</v>
+        <v>1.455784852502298</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.370323300050323</v>
+        <v>0.2362992261183763</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.2601623230125085</v>
+        <v>0.04623732038761119</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-3.097147950089074</v>
+        <v>-1.356636787587597</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.780084694909732</v>
+        <v>0.4963089170615191</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-2.355513634024987</v>
+        <v>-1.105376413722325</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-1.159230096237906</v>
+        <v>0.08563072210573353</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>0.4982039490241803</v>
+        <v>1.772106412525808</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.04434221894174328</v>
+        <v>0.7155367949016025</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-2.080972494076434</v>
+        <v>-1.819682992089845</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-2.78688993845708</v>
+        <v>-2.563313512469911</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-3.843114348543097</v>
+        <v>-3.714505668095413</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.7639</t>
+          <t>X ≈ 0.7625</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>8.242560958316915</v>
+        <v>8.453758460228222</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>3.871909720505215</v>
+        <v>4.527307155836532</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.2566922881670308</v>
+        <v>0.0561402350029212</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>4.411519611672738</v>
+        <v>3.148717252013064</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3.627298645851916</v>
+        <v>2.878086608725695</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.572112365581589</v>
+        <v>1.18858860936497</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.042316148058944</v>
+        <v>2.242894700578248</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.315674210032327</v>
+        <v>1.937974257169628</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.230282554241313</v>
+        <v>-1.158453646987446</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.2389542360899171</v>
+        <v>0.816127765193734</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>2.306735851346005</v>
+        <v>2.926910390257675</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.131125461350877</v>
+        <v>2.193648031258689</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.904824381041891</v>
+        <v>1.081785359494951</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>1.580606491142348</v>
+        <v>2.040745944741374</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>0.9224631935618319</v>
+        <v>1.363953347313434</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>2.413711102051856</v>
+        <v>1.919961525969271</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>2.728224458347924</v>
+        <v>2.275527209108219</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>3.520244741073888</v>
+        <v>3.535578769506913</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>1.942414148903985</v>
+        <v>1.895842742482536</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>1.23239897232493</v>
+        <v>1.183044517222598</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>2.035144284179523</v>
+        <v>2.937214669581913</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>3.753020295864644</v>
+        <v>4.25622640776605</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>1.336912048705443</v>
+        <v>1.249378007801525</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>4.400093248396963</v>
+        <v>3.876283654851086</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.8057</t>
+          <t>X ≈ 0.8043</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3.239886831522163</v>
+        <v>4.274076606497104</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>6.574834803814554</v>
+        <v>6.704236740299294</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>4.678100158453276</v>
+        <v>5.462025900109893</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>4.423861735340822</v>
+        <v>5.759305412901227</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>4.546786859123799</v>
+        <v>5.491549311365723</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>3.816321852560677</v>
+        <v>4.307718719113439</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>4.879235553991393</v>
+        <v>4.858082128269466</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>2.766161723917214</v>
+        <v>2.328957405862027</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>3.266364502162205</v>
+        <v>2.90172717134589</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>5.704458000437633</v>
+        <v>4.785643664914474</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>3.684939660948217</v>
+        <v>2.827432769668988</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>5.699768239151595</v>
+        <v>4.781296725047511</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>5.035321768625742</v>
+        <v>5.272981033928062</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>2.520664910527749</v>
+        <v>2.812692254593252</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>1.86252161294717</v>
+        <v>2.585179274777218</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.2953850430914642</v>
+        <v>0.4641134216386149</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.8880177763991668</v>
+        <v>-0.09279356411201434</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>0.3832883087704246</v>
+        <v>1.119306953646593</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.7769670992960229</v>
+        <v>0.4335267784026655</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>0.3273099033325622</v>
+        <v>1.54239862093759</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-1.591383053624355</v>
+        <v>-0.3682324580003424</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.7497978223728978</v>
+        <v>-0.4458626886390959</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>0.4421080827696997</v>
+        <v>1.595546948766788</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.09243976678384769</v>
+        <v>0.5303796112726218</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.8476</t>
+          <t>X ≈ 0.846</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.3940938666787446</v>
+        <v>-3.283094428160339</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-3.326273262431137</v>
+        <v>-4.892524286885084</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-2.599790146959961</v>
+        <v>-3.390583751853079</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.1504592968007685</v>
+        <v>-2.162265381401767</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-1.051132041547355</v>
+        <v>-2.424374162009386</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-1.297066288350457</v>
+        <v>-2.73001784604665</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>1.827088923863123</v>
+        <v>2.415778370924592</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>5.877881808114374</v>
+        <v>6.676108710156576</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>8.516771587431677</v>
+        <v>9.537808345628342</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>7.743855911395187</v>
+        <v>8.296663727712939</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>3.688911224552768</v>
+        <v>4.006337831574989</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>1.245659656602641</v>
+        <v>0.9986750232144033</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>1.854099321348201</v>
+        <v>2.622933375348005</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>4.663323475204663</v>
+        <v>5.585841625178766</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>4.005180177624133</v>
+        <v>4.737519694886167</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>4.166666666666664</v>
+        <v>4.387835586168627</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>3.599849096788766</v>
+        <v>4.280766425672233</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>3.927908825868009</v>
+        <v>4.158141734523973</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>4.576700639692767</v>
+        <v>5.289210934207546</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>4.763546449660794</v>
+        <v>5.506754504515058</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>1.623597684292164</v>
+        <v>2.650644302106429</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>1.547751722883064</v>
+        <v>2.576361256885228</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>4.419629032767716</v>
+        <v>6.056397744041796</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>1.746394182141842</v>
+        <v>3.583432664325677</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.8894</t>
+          <t>X ≈ 0.8878</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-3.361517504493385</v>
+        <v>-1.175110442159962</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-1.461657431334856</v>
+        <v>1.704829192692515</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.4522788268967233</v>
+        <v>-0.05708549591155787</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-3.053971281931489</v>
+        <v>-0.1372657170811635</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>3.314148860046373</v>
+        <v>4.277196196385631</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>2.942455828266674</v>
+        <v>3.389680283401852</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>1.611847926499216</v>
+        <v>-0.006522744433212324</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-2.018318825516431</v>
+        <v>-3.436039310666708</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-2.535490861478827</v>
+        <v>-3.31686283510335</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.073769666006946</v>
+        <v>-2.022764944627426</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.3176084119091485</v>
+        <v>-0.1826053038187538</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.637118645170098</v>
+        <v>-2.526830384817679</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-4.436258365657508</v>
+        <v>-5.724369801574575</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-2.422700370595727</v>
+        <v>-3.883704825043942</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>1.947089292717578</v>
+        <v>0.6401338674703467</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>3.10013543253767</v>
+        <v>2.557032879601437</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>1.290240641928904</v>
+        <v>0.6763132383851556</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>2.302718373861914</v>
+        <v>2.118215515158539</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>0.8426321011549618</v>
+        <v>-0.2914999875900719</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.646499742508297</v>
+        <v>-1.656242363887579</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>1.604250178911144</v>
+        <v>0.4186719063854056</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.1475734361292425</v>
+        <v>-0.713195228324139</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>0.6855604942299109</v>
+        <v>0.0491982052567721</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>0.05106902312955697</v>
+        <v>-0.6493715684785712</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.9312</t>
+          <t>X ≈ 0.9295</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.3075137800986312</v>
+        <v>0.6310685267462688</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.6422905784484456</v>
+        <v>-2.080842892609269</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>6.253023705853899</v>
+        <v>7.388351179871279</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5.540069686411158</v>
+        <v>5.127847908643318</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>5.204279213863884</v>
+        <v>5.677733870235294</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>7.891245399961235</v>
+        <v>7.471785384386273</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>4.619296716070892</v>
+        <v>4.221026509924194</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>4.341085271317837</v>
+        <v>3.097547112439159</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>1.882572453232562</v>
+        <v>0.7353734218196308</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>8.609656777196065</v>
+        <v>7.354548546592326</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>8.050383086024631</v>
+        <v>5.996550800658625</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>10.27163368257666</v>
+        <v>9.052728417219427</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>5.815138282387217</v>
+        <v>4.653272762040565</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>4.760726072607312</v>
+        <v>3.596807467953219</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>4.102582775026711</v>
+        <v>2.904325364645963</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>3.863636363636338</v>
+        <v>2.636742707966889</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>3.729719226658887</v>
+        <v>2.529419722434412</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>5.291545189504376</v>
+        <v>4.542599765128564</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>4.674103237095373</v>
+        <v>4.762930502881936</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>2.3609490470634</v>
+        <v>2.505671309300517</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>5.985069545764027</v>
+        <v>6.131341056514017</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>5.909223584354926</v>
+        <v>6.906780487014437</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>2.850364963503651</v>
+        <v>3.809562979222193</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>5.274532710280361</v>
+        <v>6.166688188757696</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.973</t>
+          <t>X ≈ 0.9713</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>4.091111649454625</v>
+        <v>4.448361875122885</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.6635513459501752</v>
+        <v>1.214381888080595</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-1.805395538132359</v>
+        <v>-1.039517090566918</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-5.611133062729756</v>
+        <v>-4.628473755317358</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-2.854140030122373</v>
+        <v>-2.909862799206785</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-6.790885184231165</v>
+        <v>-4.751338946720495</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-1.377266857812231</v>
+        <v>1.439531863734317</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-5.77918964277152</v>
+        <v>-2.851606443443188</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-5.737702460856838</v>
+        <v>-3.72500273916593</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-6.510618136893285</v>
+        <v>-4.525294891687132</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-3.14377498957672</v>
+        <v>-1.255445246815114</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>3.793970452336062</v>
+        <v>4.46002156627258</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>2.670808385479944</v>
+        <v>4.347514818554131</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.6430539961212887</v>
+        <v>1.113327934433528</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-1.301197293701811</v>
+        <v>0.4279930595720174</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-1.737738206810342</v>
+        <v>-0.008847634038765761</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>0.1902003263152494</v>
+        <v>0.8832963380157466</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-1.976496047609032</v>
+        <v>-1.24481702768125</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-2.791532501736249</v>
+        <v>-2.443785999159608</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.5428310216651226</v>
+        <v>-0.227115628892733</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-1.085377189631153</v>
+        <v>0.21329431443705</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-1.161223151040254</v>
+        <v>-1.244958610669592</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>3.236962901647978</v>
+        <v>3.035988083583085</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>3.161130648424702</v>
+        <v>2.86536766054639</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 1.015</t>
+          <t>X ≈ 1.013</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-9.781197990624953</v>
+        <v>-2.771036736181621</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.4103410004989243</v>
+        <v>4.167882901076581</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-4.536449978356629</v>
+        <v>2.939823181751635</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-3.49501803288706</v>
+        <v>2.400689748076523</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-5.585194470346657</v>
+        <v>0.3422421810199481</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-5.398228284249285</v>
+        <v>-1.283713639939144</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-9.678948897964183</v>
+        <v>-5.72447765378611</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-8.202774377804978</v>
+        <v>-4.353046200503833</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-11.67005912571484</v>
+        <v>-7.817530527300747</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-15.95174673157592</v>
+        <v>-10.34320268434417</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-13.92330112450171</v>
+        <v>-10.15087081743955</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-10.69327859812512</v>
+        <v>-6.835039535429829</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-10.06205470006898</v>
+        <v>-8.056469183146952</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-3.265589716866444</v>
+        <v>-1.173145536751164</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-5.678118979359255</v>
+        <v>-3.611554963026876</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-5.083732057416263</v>
+        <v>-3.050250944207214</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-5.217649194393736</v>
+        <v>-4.937020782889441</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-3.568103933302666</v>
+        <v>-6.932697462708028</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>0.1565593774462428</v>
+        <v>0.6263975327993663</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-1.410980777498004</v>
+        <v>-3.585936137548046</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>3.30963094927278</v>
+        <v>3.095404126891324</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.2749869419608615</v>
+        <v>-0.7690968664834301</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-1.754898194391082</v>
+        <v>0.6986293674868378</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.07634448270208338</v>
+        <v>1.731580812473851</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 1.057</t>
+          <t>X ≈ 1.055</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>6.359152886568019</v>
+        <v>0.625048816683595</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>3.80215386599599</v>
+        <v>2.456926484611664</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>4.586357039187227</v>
+        <v>-0.8634455833816119</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.5710414246999562</v>
+        <v>-3.533632285821767</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-3.129054119469444</v>
+        <v>-3.821296963451367</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.502356511072364</v>
+        <v>0.4306729621592922</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-3.714036617262423</v>
+        <v>-2.405873941114571</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>2.674418604651166</v>
+        <v>3.510452588842412</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-3.950760880100809</v>
+        <v>-2.534439324718029</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-6.945898778359492</v>
+        <v>-7.473953289671016</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-2.22739469175314</v>
+        <v>-1.004684376761624</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>4.160522571465506</v>
+        <v>4.891554492011629</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>14.14847161572055</v>
+        <v>12.03937423896763</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>11.70517051705174</v>
+        <v>9.785994899084166</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>8.824804997248926</v>
+        <v>7.026056013567164</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>9.419191919191917</v>
+        <v>7.587360032386826</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>4.840830337770001</v>
+        <v>5.417801654560115</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>4.735989633948847</v>
+        <v>7.362702053030503</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-1.714785651793527</v>
+        <v>1.368023844340883</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>5.138726824841171</v>
+        <v>7.779644187704974</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>6.818402879097398</v>
+        <v>9.364136732329058</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>11.18700136213271</v>
+        <v>13.45564087704046</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>9.239253852392537</v>
+        <v>11.61594202898549</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>11.38564382139149</v>
+        <v>13.53713636802936</v>
       </c>
     </row>
   </sheetData>
@@ -3180,2461 +3180,2461 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.1355</t>
+          <t>X &gt; -0.1354</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3339</v>
+        <v>3360</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.05346991783804356</v>
+        <v>-0.01025900715286809</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.07449228581394607</v>
+        <v>0.05534579751019919</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.02275858818931908</v>
+        <v>0.1475442952522457</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.041460230709923</v>
+        <v>0.2223583011662029</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.009332311223055001</v>
+        <v>0.1704929660877781</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.1502349775846952</v>
+        <v>-0.01121117777478275</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.326058475185917</v>
+        <v>-0.1975448799036101</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.4084675014907475</v>
+        <v>-0.2784274703706018</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.3201812996255953</v>
+        <v>-0.1041057223505319</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.2706137080863726</v>
+        <v>-0.05349977174230247</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.2180442490992078</v>
+        <v>0.02824276722256513</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.1214011432940083</v>
+        <v>0.1541751624524537</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.09259536944917812</v>
+        <v>0.2133206900749798</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.1466813348001494</v>
+        <v>0.1902661358190798</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.1298143965697491</v>
+        <v>0.2380257102101808</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.05547102827437556</v>
+        <v>0.3123374584391811</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.1716260648209271</v>
+        <v>0.1369759182259145</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.1390768200650001</v>
+        <v>0.140530184796809</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.1147590622365655</v>
+        <v>0.2537704201515822</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.1196015214584492</v>
+        <v>0.1887155975623713</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.04580943258576298</v>
+        <v>0.3227302500216211</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.1037504675412748</v>
+        <v>0.2058391717063444</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.09873683290353341</v>
+        <v>0.2887080708381404</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.1866832226336683</v>
+        <v>0.1442792251722409</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.0937</t>
+          <t>X &gt; -0.0936</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3313</v>
+        <v>3334</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.08064148200620735</v>
+        <v>0.1064647225894291</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.02786047737770048</v>
+        <v>0.0851255541831506</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.1118825647127508</v>
+        <v>0.2473833626099022</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.01638890139061999</v>
+        <v>0.2081387699520363</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.09219514511047322</v>
+        <v>0.09835568760231439</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.2357578051669478</v>
+        <v>-0.08599664205227953</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.4067449505957583</v>
+        <v>-0.2676294576999254</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.4274749931847168</v>
+        <v>-0.2870926751523797</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.3989468893210812</v>
+        <v>-0.1721326623989725</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.3126489872149776</v>
+        <v>-0.08510345412900477</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.2318070463459989</v>
+        <v>0.02502737045012537</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.1020246582800226</v>
+        <v>0.1839729628394551</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.09395262670371807</v>
+        <v>0.2223575865971981</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.1767927470253738</v>
+        <v>0.171152226146063</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.1243248554953809</v>
+        <v>0.2544962004634286</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.05421037734988232</v>
+        <v>0.3250241879069264</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.2003591337992106</v>
+        <v>0.1191790132694805</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.1064047652740356</v>
+        <v>0.183670286055964</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.08363701220097397</v>
+        <v>0.2961352498667722</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.09003134509346467</v>
+        <v>0.2289149664839414</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.01120886904184459</v>
+        <v>0.368407034996153</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.05687981536343756</v>
+        <v>0.281180445385786</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.08415525375645672</v>
+        <v>0.3328335832084051</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.1721923123577227</v>
+        <v>0.1885560840861658</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.05187</t>
+          <t>X &gt; -0.05184</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3268</v>
+        <v>3289</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.03573606992725331</v>
+        <v>-0.01001803245842581</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.04141808456636653</v>
+        <v>0.1528738659650486</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.05058839382954261</v>
+        <v>0.1833584370129842</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.03646299730789337</v>
+        <v>0.1516170378731587</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.1114888844202113</v>
+        <v>0.07430171727273205</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2595820952159187</v>
+        <v>-0.1147019341462112</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.3918719304921936</v>
+        <v>-0.2577453642662704</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.3785978487309194</v>
+        <v>-0.243061695406638</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.289275560584386</v>
+        <v>-0.06773230292625954</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.1911562309340411</v>
+        <v>0.03135958533658112</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.02143759101104337</v>
+        <v>0.2301705354421628</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.02249803075642376</v>
+        <v>0.3042339353969936</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.01562653383668788</v>
+        <v>0.3280784725871442</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.09580628392509283</v>
+        <v>0.2492805120845247</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.003015189349881098</v>
+        <v>0.3734145271281051</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>0.05993039743803763</v>
+        <v>0.4372800932536691</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.05579864685164893</v>
+        <v>0.2604166666666643</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>0.07149628974887889</v>
+        <v>0.3579953839633276</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.06108988745713617</v>
+        <v>0.4387616374668681</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.05208054553433783</v>
+        <v>0.3677336782892269</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>0.1395000545842606</v>
+        <v>0.5169313860350329</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>0.09424448779125072</v>
+        <v>0.4295849669827305</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>0.06281525411240807</v>
+        <v>0.4786573278710264</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>0.005254864503143608</v>
+        <v>0.3650729242268085</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.01003</t>
+          <t>X &gt; -0.01008</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3224</v>
+        <v>3245</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.07484823038548427</v>
+        <v>0.08455417179757774</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.1576271677987222</v>
+        <v>0.2531075874408941</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.1247711089187931</v>
+        <v>0.2400801444011478</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.04624252591732869</v>
+        <v>0.2296075014887933</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.0674056932299365</v>
+        <v>0.2469002306805095</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.1778602910956479</v>
+        <v>-0.03865525672155457</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.3014607193515531</v>
+        <v>-0.1728802489843559</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.2841978252438366</v>
+        <v>-0.1538582035362168</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.2250889616577894</v>
+        <v>-0.008536533529813539</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.05330160764120961</v>
+        <v>0.1640274334819196</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.1150404791209709</v>
+        <v>0.3618874962364345</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.2252514933373106</v>
+        <v>0.5021345352933508</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.07897991554523998</v>
+        <v>0.3878655323741995</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.03094059405940186</v>
+        <v>0.3728202525169806</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.1958975382579098</v>
+        <v>0.5693575340649417</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.282625011727184</v>
+        <v>0.6572958487574851</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.1362434343599404</v>
+        <v>0.4487623001230006</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.235783107719989</v>
+        <v>0.5187583381891656</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.2533305896415854</v>
+        <v>0.6285332501892995</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.2107113946558741</v>
+        <v>0.5229170293392471</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>0.3067749721206283</v>
+        <v>0.681870722476873</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>0.2309290107115274</v>
+        <v>0.5636123378761084</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>0.1953262038137282</v>
+        <v>0.6100886710064586</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>0.1380562834813688</v>
+        <v>0.4972031374181896</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; 0.0318</t>
+          <t>X &gt; 0.03168</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3161</v>
+        <v>3182</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.2899704966309287</v>
+        <v>0.2963245827508274</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.3810920366296671</v>
+        <v>0.4730961583210274</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.2502966238316588</v>
+        <v>0.3596455385413009</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.02700704870262172</v>
+        <v>0.2044700730247655</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.08673093510653729</v>
+        <v>0.2587588869827755</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1985950702318604</v>
+        <v>-0.06675439861552235</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.2148762478249751</v>
+        <v>-0.09419417890075721</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.09723493865592303</v>
+        <v>0.02504270796953278</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.006211415702559009</v>
+        <v>0.2020424026277468</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.1844020235454522</v>
+        <v>0.3937657416847529</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.3507193617707429</v>
+        <v>0.5902311616667077</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.3110534239831324</v>
+        <v>0.5822279096333745</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.08958623191399795</v>
+        <v>0.3937714183302035</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.1081016905729726</v>
+        <v>0.4459870404545612</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>0.3525827750267041</v>
+        <v>0.7225715616089872</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0.4292610347236163</v>
+        <v>0.8012093040970072</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.2195065503059794</v>
+        <v>0.5279378331765443</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.3231407661236574</v>
+        <v>0.6019679441901289</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.2735554073439985</v>
+        <v>0.6469445846972732</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>0.2896032782784843</v>
+        <v>0.5977770905836408</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>0.3351644224243699</v>
+        <v>0.7083282550920416</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>0.2276929075680911</v>
+        <v>0.5578184314793262</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>0.2491631924726576</v>
+        <v>0.6632244669371303</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>0.1290091417893962</v>
+        <v>0.4884772437888643</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; 0.07363</t>
+          <t>X &gt; 0.07344</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3093</v>
+        <v>3114</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.3462911502336254</v>
+        <v>0.3992819855823484</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.157537876574608</v>
+        <v>0.2810483065972775</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.1669295705477865</v>
+        <v>0.3030857718936986</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.04551589917442556</v>
+        <v>0.06178475406217387</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.06914407872874762</v>
+        <v>0.201164373298937</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.2265152177993599</v>
+        <v>-0.1348418826512798</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.1940880973139016</v>
+        <v>-0.08175416875305785</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.06777643879910755</v>
+        <v>0.04670161219682001</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.1209283235909737</v>
+        <v>0.3206519211990582</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.3004780332346897</v>
+        <v>0.5019172353997234</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.4000394434129575</v>
+        <v>0.6647900167693876</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.2367212322597396</v>
+        <v>0.5346939658303924</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.03499643841556122</v>
+        <v>0.366381502890178</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.1232435400908685</v>
+        <v>0.4891487218667905</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.2907548180374562</v>
+        <v>0.7225815962354716</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.3237847986153923</v>
+        <v>0.7586756818509954</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.08005277518482501</v>
+        <v>0.4176178842251446</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.2527980148191986</v>
+        <v>0.5602248691973699</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.2619585342529902</v>
+        <v>0.6656161416485986</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.3388704256309794</v>
+        <v>0.6748461471158507</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>0.33273168754382</v>
+        <v>0.736048827292187</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>0.2892063466906336</v>
+        <v>0.648088459411035</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>0.272795474169456</v>
+        <v>0.7184032381882943</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>0.1193435735199486</v>
+        <v>0.511285372525208</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; 0.1155</t>
+          <t>X &gt; 0.1152</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3012</v>
+        <v>3028</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.1748119549525669</v>
+        <v>0.1823486575146092</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.1373592398535024</v>
+        <v>0.1989951529561296</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.2850686348264801</v>
+        <v>0.3883443723641804</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.0644892828653596</v>
+        <v>0.09131467109452274</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.1282963925886875</v>
+        <v>0.3408631932859691</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.3124215970654944</v>
+        <v>-0.1403345036713333</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.159362021953541</v>
+        <v>0.03522844957869609</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.04388324443966951</v>
+        <v>0.2416695583581259</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.1704512411113299</v>
+        <v>0.4540861204946154</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.309392226931493</v>
+        <v>0.5972786798660366</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.3712012578186616</v>
+        <v>0.6913221976336814</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.1116954518243745</v>
+        <v>0.4666946729725225</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.1663464915894437</v>
+        <v>0.5554858135186791</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.1635958297816629</v>
+        <v>0.5900684421153954</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.2539021964686867</v>
+        <v>0.7177526907870231</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.3712573046569076</v>
+        <v>0.8377819268765236</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.2571747564346083</v>
+        <v>0.6547741625480441</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.3048077889738749</v>
+        <v>0.6734290677674153</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.3415990911583862</v>
+        <v>0.8087356392937721</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.2496904759508141</v>
+        <v>0.6472804421530896</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>0.1915636269677066</v>
+        <v>0.6603261087725016</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>0.1820966897869525</v>
+        <v>0.6049808110338759</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>0.1246762811272788</v>
+        <v>0.6043320366888238</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.06411270804631641</v>
+        <v>0.3628739285754037</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; 0.1573</t>
+          <t>X &gt; 0.157</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2910</v>
+        <v>2923</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.2053067327218798</v>
+        <v>0.1963263650233245</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.109846173688311</v>
+        <v>0.1543624253085696</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.3812288340590229</v>
+        <v>0.4972210086651287</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.01015515649662291</v>
+        <v>0.210733153840593</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.1871851967698674</v>
+        <v>0.4450322537140678</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.2754212667054006</v>
+        <v>-0.02491063798988336</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.1242930275188385</v>
+        <v>0.1513438612605995</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.06155950752394546</v>
+        <v>0.3080432478186736</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.04837748404651165</v>
+        <v>0.2852445537254056</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.04879633710922349</v>
+        <v>0.2917165765511172</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.03971322410520628</v>
+        <v>0.4474032587359531</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.1507407466471022</v>
+        <v>0.2926944039866086</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.2263142698567293</v>
+        <v>0.2200038614450506</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.2215677359373984</v>
+        <v>0.2305020272054463</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.07094025091318201</v>
+        <v>0.4211717771709189</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.004676393565283377</v>
+        <v>0.4570555226086626</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.0838885492130288</v>
+        <v>0.3052118885096746</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.0996696354784703</v>
+        <v>0.2267558459024741</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.1036173258981066</v>
+        <v>0.3249182859185993</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.1711022349878846</v>
+        <v>0.1839727608707307</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.2467522794964765</v>
+        <v>0.1835147227597105</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.2882457847049551</v>
+        <v>0.09452976592935158</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.3572956342290894</v>
+        <v>0.08493427704753032</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.5158452965924738</v>
+        <v>-0.1253393988767684</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; 0.1991</t>
+          <t>X &gt; 0.1987</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2798</v>
+        <v>2805</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.01353559138360794</v>
+        <v>-0.05343083721438546</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.2206776529408359</v>
+        <v>0.2674352636740167</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.489628731932612</v>
+        <v>0.6067900459482161</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.04551589917442556</v>
+        <v>0.1560810812880717</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.08099803795113303</v>
+        <v>0.3410259521699501</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.265463940958611</v>
+        <v>-0.03339006988721849</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.07724192783615536</v>
+        <v>0.1834771965224178</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.05613329693149183</v>
+        <v>0.2886002886002785</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.0598949251779004</v>
+        <v>0.2594876582641206</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.06484185814274923</v>
+        <v>0.2640696556318218</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.1230326586742123</v>
+        <v>0.5568108622501455</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.1142889491720567</v>
+        <v>0.5492409614840099</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.1684682749898627</v>
+        <v>0.3072451392538085</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.1546036956636812</v>
+        <v>0.3286199103735825</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.04268588878689172</v>
+        <v>0.4493150211924757</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.1806776289473362</v>
+        <v>0.640914568615635</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.1037377848316225</v>
+        <v>0.487123636794685</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0.1273181277407218</v>
+        <v>0.4110170865851117</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.07886514185727833</v>
+        <v>0.4687741480814438</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.07027639059290891</v>
+        <v>0.2417449930547875</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.198513966268365</v>
+        <v>0.1939088121011636</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.2386201135245116</v>
+        <v>0.1043464939505654</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.2500639142661853</v>
+        <v>0.1553813257305876</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.3616359816424293</v>
+        <v>-0.02124152858380768</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; 0.241</t>
+          <t>X &gt; 0.2405</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2685</v>
+        <v>2687</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.587639533452311</v>
+        <v>0.5793695750317269</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.5866906282775588</v>
+        <v>0.5552741995866413</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.8178110451219496</v>
+        <v>0.9271974729261174</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.3645009425931534</v>
+        <v>0.5196381576668756</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.6221822801349006</v>
+        <v>0.9095143983438874</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.006875272640129992</v>
+        <v>0.2531393167264326</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.1113837586030613</v>
+        <v>0.3663440625245329</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.1512275100315037</v>
+        <v>0.3044556873635642</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.04429168638034042</v>
+        <v>0.3795195757825383</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.0391925175329817</v>
+        <v>0.3080537331068456</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.1450111340503852</v>
+        <v>0.5276333525900156</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.1261948906469428</v>
+        <v>0.5318138204150529</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.06863446176431154</v>
+        <v>0.3650531114891322</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.1191649625586564</v>
+        <v>0.3240888578456449</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.04921952894951431</v>
+        <v>0.40573786669367</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.1585558184071161</v>
+        <v>0.5811338130855574</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.1955677453151523</v>
+        <v>0.5364931328878981</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.150176141885332</v>
+        <v>0.3886261374426851</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.1650472887018708</v>
+        <v>0.4766530353075993</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.001802856941779396</v>
+        <v>0.2302620215210425</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.03448352686166345</v>
+        <v>0.2795642416227651</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.2220613318461915</v>
+        <v>0.07783624086841456</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.2455382022319199</v>
+        <v>0.1204063146997925</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.3213704554551953</v>
+        <v>-0.01964939056136217</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; 0.2828</t>
+          <t>X &gt; 0.2823</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2582</v>
+        <v>2578</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.7011058005008763</v>
+        <v>0.6946614074826201</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.4049241391637963</v>
+        <v>0.4102337705460855</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.7422813927186738</v>
+        <v>0.8504549228917995</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.2994933323651026</v>
+        <v>0.5276983327122338</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.6198201890343356</v>
+        <v>0.9069938135682136</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.07347877188973229</v>
+        <v>0.3320321961456472</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.4593841983814642</v>
+        <v>0.7146327606353822</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.489933849730285</v>
+        <v>0.6630908712635701</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.377040483594044</v>
+        <v>0.697505453036193</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.3599785275177965</v>
+        <v>0.6952131528005054</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.5182080538495981</v>
+        <v>0.9127270530059874</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.4325088434518065</v>
+        <v>0.8516519987193263</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.1587676260165338</v>
+        <v>0.6090574395452606</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.1151100046273541</v>
+        <v>0.5769171477940063</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.09820358904010362</v>
+        <v>0.6135361596879747</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.367952817701557</v>
+        <v>0.8500859415007227</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.4505235576720423</v>
+        <v>0.846731947130877</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.4075993481117237</v>
+        <v>0.698352994941601</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.2597585518528547</v>
+        <v>0.6650203403349195</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.08259054919270881</v>
+        <v>0.3992419618275562</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>0.02780127827113432</v>
+        <v>0.435911238334505</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.1255040169876978</v>
+        <v>0.2288966909939489</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.2383259737542929</v>
+        <v>0.1854780248495373</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.3916175608272923</v>
+        <v>-0.06998801779942454</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 0.3246</t>
+          <t>X &gt; 0.324</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2463</v>
+        <v>2455</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.6691488396234817</v>
+        <v>0.723446866713509</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.658127605822429</v>
+        <v>0.7201603302413346</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.000764161809649</v>
+        <v>1.123371606433061</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.6115657069156768</v>
+        <v>0.8544631399337703</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.085164145740315</v>
+        <v>1.347202614068159</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.3008636381913945</v>
+        <v>0.5336550231394313</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.7429983213589182</v>
+        <v>0.9749354338119502</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.7480729955860141</v>
+        <v>0.9361114176978163</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.425335167383345</v>
+        <v>0.8040364278968823</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.5664718919058984</v>
+        <v>0.9628372471256981</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.7190740441892771</v>
+        <v>1.137213759577236</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.6832396204983624</v>
+        <v>1.168044597235962</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.4507658127515626</v>
+        <v>0.9690870989972353</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.3753473767789899</v>
+        <v>0.9073076848647759</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.4707621375334554</v>
+        <v>1.020525527104475</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.7248713318838966</v>
+        <v>1.200421723133857</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.8181214975429114</v>
+        <v>1.202232263742211</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.6160888000520401</v>
+        <v>0.9313216716228965</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.5317872197793463</v>
+        <v>0.9669947886508368</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.2557927336245029</v>
+        <v>0.595977329683798</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>0.3222599639532291</v>
+        <v>0.7850073588547133</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.03779224999343</v>
+        <v>0.327333998733593</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.1693264697078831</v>
+        <v>0.310295992069122</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.2045578297115043</v>
+        <v>0.1724045282466307</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 0.3665</t>
+          <t>X &gt; 0.3658</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2358</v>
+        <v>2346</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.8430784364834381</v>
+        <v>0.9412988218048071</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.5929040069999445</v>
+        <v>0.6953919861009368</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.8892335197286769</v>
+        <v>1.090444077102752</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.6415925290507545</v>
+        <v>0.9633549070593332</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.194126929599925</v>
+        <v>1.491519271190114</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.408165873734518</v>
+        <v>0.6332244507922553</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.7360479851064383</v>
+        <v>0.9623013377763954</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.5847400936528615</v>
+        <v>0.808740605522992</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.3724201689685813</v>
+        <v>0.7493179681760864</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.5301305504616991</v>
+        <v>0.8674510686824846</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.5080819015914741</v>
+        <v>0.9524838071140636</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.5254407891756259</v>
+        <v>0.9974466483307722</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.37520596428228</v>
+        <v>0.8832011889317499</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.2639705358601958</v>
+        <v>0.7875667962957777</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>0.2661447281737566</v>
+        <v>0.8101586646675472</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.4625351353432734</v>
+        <v>0.9723047249507246</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.6082503001052189</v>
+        <v>1.021413266751658</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>0.3593705392288342</v>
+        <v>0.6589951465390769</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.2614654084270072</v>
+        <v>0.686263185077884</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.1030034550570491</v>
+        <v>0.2454110209438696</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.009417307501450978</v>
+        <v>0.4693942887360691</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.1276720899453281</v>
+        <v>0.2493660332017384</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.3196944088458054</v>
+        <v>0.1775810007224834</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.3107090199995213</v>
+        <v>0.08338530238572872</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 0.4083</t>
+          <t>X &gt; 0.4075</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2270</v>
+        <v>2258</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.4892056106453566</v>
+        <v>0.5434892648595238</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.4180491989387818</v>
+        <v>0.4733293535844822</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.9132463186248359</v>
+        <v>1.06397795819553</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.8154065346829782</v>
+        <v>1.086689994888189</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.35835068427982</v>
+        <v>1.645929745825761</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.4029618615898443</v>
+        <v>0.6165716119292952</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.6415579931652218</v>
+        <v>0.8572569957451677</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.6269669350553855</v>
+        <v>0.7974581853209699</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.3169602681124459</v>
+        <v>0.6427877615425146</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.5985261386488858</v>
+        <v>0.9283247855600223</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.6529021252747782</v>
+        <v>1.050163809070277</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.4620261840411999</v>
+        <v>0.8873705366405105</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.1736620082219886</v>
+        <v>0.6355961348866543</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.02132520944402216</v>
+        <v>0.4575901222330856</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>0.05025208021579886</v>
+        <v>0.5515043079178383</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.2751336506285895</v>
+        <v>0.7421655691242393</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.3435689919171097</v>
+        <v>0.7088162251655561</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>0.1770581793766794</v>
+        <v>0.4256774378301529</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.1093035176770272</v>
+        <v>0.2688065429592825</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.2308277517618649</v>
+        <v>0.06752287827215753</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.0685281047499231</v>
+        <v>0.3664587137532394</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.232479793031267</v>
+        <v>0.09649633426760573</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.266375124602078</v>
+        <v>0.1894258713936594</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.2981545143892248</v>
+        <v>0.05359636212445196</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 0.4501</t>
+          <t>X &gt; 0.4493</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2162</v>
+        <v>2148</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.6066136437240814</v>
+        <v>0.7048340290454504</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.271836845374267</v>
+        <v>0.3665910899251514</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.772875968088421</v>
+        <v>1.004787108070495</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.5216024657278666</v>
+        <v>0.8278973746362439</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.9706688722202941</v>
+        <v>1.291028061868388</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.1419379207368863</v>
+        <v>0.386096478577457</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.431854426135537</v>
+        <v>0.6793010025466799</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.569155446756433</v>
+        <v>0.7705120921387021</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.4259704218382652</v>
+        <v>0.7863858788206812</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.5302477282579048</v>
+        <v>0.8957519200599009</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.6196351635869632</v>
+        <v>1.009920359634087</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.4793899152636172</v>
+        <v>0.8991995462668712</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.1872527791554219</v>
+        <v>0.691406051292212</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.2184983041240329</v>
+        <v>0.331648831633153</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.1564626445267976</v>
+        <v>0.4187209223443773</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.003500812188434566</v>
+        <v>0.4976458724547541</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.03577562980267146</v>
+        <v>0.4213795436968226</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.1339867253892422</v>
+        <v>0.1304341399637465</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.3806300345666713</v>
+        <v>0.04734778447062382</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.5175585076698823</v>
+        <v>-0.1288276882232609</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.08878182642221333</v>
+        <v>0.4002827109436851</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.3958951328821954</v>
+        <v>0.02734630339706001</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.3064342964408482</v>
+        <v>0.2055961316689263</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.05849226659289286</v>
+        <v>0.3504510793887903</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.492</t>
+          <t>X &gt; 0.4911</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2063</v>
+        <v>2049</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.8342375503319417</v>
+        <v>0.9808372293156253</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.6445986329690712</v>
+        <v>0.7349303936117551</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.141751330430573</v>
+        <v>1.36702874455036</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.057728128597894</v>
+        <v>1.355178069689885</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.25410988633606</v>
+        <v>1.563412866213682</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.521869492849504</v>
+        <v>0.7527605989655157</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.007782444179277</v>
+        <v>1.195097277438308</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.8263295867508305</v>
+        <v>0.966566390295192</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.6742995940162828</v>
+        <v>1.025610039923372</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.723831910239106</v>
+        <v>1.081595354197241</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.9495122587387144</v>
+        <v>1.382251307110984</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.9610386172645988</v>
+        <v>1.425238685843134</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.708703836330109</v>
+        <v>1.164206745608624</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.3424870788965677</v>
+        <v>0.8478842068771684</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.3424988769950801</v>
+        <v>0.8750290168120429</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.3850245799398309</v>
+        <v>0.8823452067339161</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.4254556607674118</v>
+        <v>0.8075956549935128</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.4466591012833447</v>
+        <v>0.7038707610184431</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.3232388001911843</v>
+        <v>0.7527786250675845</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.2192460255736606</v>
+        <v>0.5581033963985718</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>0.5976887087952178</v>
+        <v>1.091719578332984</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0.3764234550933381</v>
+        <v>0.7047470041329476</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>0.360059582989841</v>
+        <v>0.8313891834570555</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.478119719490266</v>
+        <v>0.8937737521191877</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.5338</t>
+          <t>X &gt; 0.5328</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1965</v>
+        <v>1950</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.9323236182753547</v>
+        <v>1.058288371025142</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.7499858443157805</v>
+        <v>0.9140592170701254</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.344487120488047</v>
+        <v>1.540402227532383</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.19047619047619</v>
+        <v>1.507227278342867</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.362815799229736</v>
+        <v>1.689218706113387</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.5335218227254899</v>
+        <v>0.6768589719996285</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.2351503746075</v>
+        <v>1.406942185999746</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.9569389298544237</v>
+        <v>1.08063632987335</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.7951740792487954</v>
+        <v>1.08537689003284</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.8860795414236904</v>
+        <v>1.184341537804649</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.109326175455529</v>
+        <v>1.486483185612038</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.13545482078802</v>
+        <v>1.545648747761945</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.6728618596229623</v>
+        <v>1.174801696668858</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.4009699750462872</v>
+        <v>0.9570862169672694</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.230781385431726</v>
+        <v>0.8159460968359156</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.2454607108727203</v>
+        <v>0.79522149105766</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.2132729736917796</v>
+        <v>0.6708024612502115</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>0.3933263599878387</v>
+        <v>0.6707329705030176</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0.1512024737365891</v>
+        <v>0.608938522666179</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.1344859427376974</v>
+        <v>0.4958084599124888</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.5079703091228041</v>
+        <v>1.034003603808863</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>0.3812337624719788</v>
+        <v>0.7848758497180555</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>0.350364963503651</v>
+        <v>0.9056225347090745</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>0.4272044660055698</v>
+        <v>0.8768799577729709</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.5756</t>
+          <t>X &gt; 0.5746</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1849</v>
+        <v>1836</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.49428802170317</v>
+        <v>1.640958585064347</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.321673385515517</v>
+        <v>1.449047429706049</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.559330012160196</v>
+        <v>1.868219418527211</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.278808425149897</v>
+        <v>1.653786982137994</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.753828763413438</v>
+        <v>2.134168366876672</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.238092246808108</v>
+        <v>1.535162448036743</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.709386806161</v>
+        <v>1.981981083752189</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.269013199245762</v>
+        <v>1.46107791896128</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.8240138946739748</v>
+        <v>1.188312790165227</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.132179299718565</v>
+        <v>1.450593533180879</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.135968671610222</v>
+        <v>1.538389917700286</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.181543592486555</v>
+        <v>1.564182711250041</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.031354498603399</v>
+        <v>1.564120539165216</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.9724377843189842</v>
+        <v>1.456842999420225</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>0.8336986935412227</v>
+        <v>1.349402273664147</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.7790861563170921</v>
+        <v>1.347214648890592</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.8074188841314012</v>
+        <v>1.330343416531015</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>1.027077909893769</v>
+        <v>1.447429412753714</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.5939698316509876</v>
+        <v>1.20599533183389</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.510399200299382</v>
+        <v>0.9641899293619929</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>0.8331856445561741</v>
+        <v>1.516801223900586</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>0.7032563948831481</v>
+        <v>1.311553100471727</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>0.7073146660455691</v>
+        <v>1.424960355967912</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>0.6314824128222938</v>
+        <v>1.295850964979273</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.6175</t>
+          <t>X &gt; 0.6164</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1721</v>
+        <v>1707</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.701777741388007</v>
+        <v>1.883954815708321</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.541216970912757</v>
+        <v>1.696086285285936</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.438854135586759</v>
+        <v>1.660196594305553</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.19047619047619</v>
+        <v>1.474062532467734</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.841909875884781</v>
+        <v>2.069078971590692</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.273939941192388</v>
+        <v>1.413476303647975</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.77957546171551</v>
+        <v>1.895237007607939</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.559436026253955</v>
+        <v>1.59031656419932</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.078275124544959</v>
+        <v>1.287609337657216</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.350655615755862</v>
+        <v>1.571170821683801</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1.334355211460178</v>
+        <v>1.645204412021549</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.462109873052832</v>
+        <v>1.81009735507044</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>1.151955936278014</v>
+        <v>1.544644599514157</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1.337381124872074</v>
+        <v>1.855633754794283</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>0.8888504488597491</v>
+        <v>1.441979073558024</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>0.9021798461077921</v>
+        <v>1.455769381598671</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>1.000685719008295</v>
+        <v>1.445510015558149</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>1.418796787412568</v>
+        <v>1.698241843466533</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>0.7631018812944816</v>
+        <v>1.305779835379809</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.717524681384532</v>
+        <v>1.204959375147574</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>0.7560360381134359</v>
+        <v>1.49132971478523</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>0.680190076704335</v>
+        <v>1.27624746958972</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>0.7222417793084119</v>
+        <v>1.496894409937887</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>0.7045152785546307</v>
+        <v>1.370323245592353</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.6593</t>
+          <t>X &gt; 0.6581</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1599</v>
+        <v>1583</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.171652886568033</v>
+        <v>2.312100886166171</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.899376088218219</v>
+        <v>2.128811458101616</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.836357039187227</v>
+        <v>2.126465508996517</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.498403019744494</v>
+        <v>1.847150348384915</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.975112547197213</v>
+        <v>2.323001099957459</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.349578733294599</v>
+        <v>1.603290999005011</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1.890130049404242</v>
+        <v>2.123174547198104</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.674418604651166</v>
+        <v>1.818254103789485</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1.340905786565877</v>
+        <v>1.633095975276966</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>1.880490110529379</v>
+        <v>2.152010040483425</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1.529549752691302</v>
+        <v>1.897725248997702</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>1.500800349243299</v>
+        <v>1.846314372692042</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.377638282387188</v>
+        <v>1.772434200506233</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1.469059405940598</v>
+        <v>1.938772676861966</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>1.161682212174924</v>
+        <v>1.671711652536835</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>1.005600090965942</v>
+        <v>1.517266908687084</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>1.059300214776471</v>
+        <v>1.451454402515715</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>1.51731129331926</v>
+        <v>1.860147413613312</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.9201945441622925</v>
+        <v>1.483367584620609</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>1.044501267200978</v>
+        <v>1.484038700628531</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>1.189885055457594</v>
+        <v>1.837339758810799</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>0.9889609201898324</v>
+        <v>1.48534645012144</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>1.075818371883891</v>
+        <v>1.767457180500664</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>1.18760337944861</v>
+        <v>1.707014237054437</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.7011</t>
+          <t>X &gt; 0.6999</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1443</v>
+        <v>1433</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.483806626180218</v>
+        <v>1.713251556813333</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.8027694400187784</v>
+        <v>1.259875841441414</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.8190440197966424</v>
+        <v>1.319151310780811</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.006367008664157</v>
+        <v>1.556624630644784</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.086089001490841</v>
+        <v>1.557691663436181</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.9267947997765873</v>
+        <v>1.299687510098167</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1.539887667132767</v>
+        <v>1.956887655541806</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.330928299942023</v>
+        <v>1.72112350535587</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.303163404294395</v>
+        <v>1.779896121817295</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.499776814130485</v>
+        <v>1.813720145270153</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>1.35832399091845</v>
+        <v>1.740173693761072</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>1.495087052844411</v>
+        <v>1.712027945600461</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.9951936840492337</v>
+        <v>1.330680671865252</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1.328131428101265</v>
+        <v>1.817008148317775</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>1.33577750822144</v>
+        <v>1.731737858462438</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>1.029263529263531</v>
+        <v>1.50282934764914</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>1.033946530886197</v>
+        <v>1.371527777777771</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>1.483506381465574</v>
+        <v>1.767126029190962</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>0.8677969307890692</v>
+        <v>1.398149169735674</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>1.193242879357229</v>
+        <v>1.585199883675031</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>1.274397335091827</v>
+        <v>1.895473779682845</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>1.406451581582928</v>
+        <v>1.793329611070668</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>1.473026086164779</v>
+        <v>2.149414832332795</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>1.397193832941504</v>
+        <v>1.960316177287346</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.743</t>
+          <t>X &gt; 0.7416</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1239</v>
+        <v>1230</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.564964024582558</v>
+        <v>1.851898231631758</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.230187226232744</v>
+        <v>1.686506693834488</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.7606911796230591</v>
+        <v>1.15645027310233</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.8548396621980743</v>
+        <v>1.20817045754692</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1.326151691668564</v>
+        <v>1.737765296513608</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.5445948753446359</v>
+        <v>0.9285153276324607</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.225430695086239</v>
+        <v>1.582708677718593</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.027929500534938</v>
+        <v>1.277788234309973</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.4237346808354445</v>
+        <v>0.8421100586478616</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.345734259036234</v>
+        <v>1.656364521560562</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.296952900391055</v>
+        <v>1.606538344538485</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.663885498557271</v>
+        <v>1.893563475413409</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>1.024984932911799</v>
+        <v>1.310033396524339</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>1.772429058886516</v>
+        <v>2.077889376940931</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>1.598547262516618</v>
+        <v>2.009913963526813</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>1.708672683248949</v>
+        <v>1.974757498423983</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>1.332624795666156</v>
+        <v>1.515974467798429</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>2.115596844064505</v>
+        <v>2.241205700663642</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>1.201544722163973</v>
+        <v>1.614768068003059</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>1.307680281930224</v>
+        <v>1.554352708588262</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>1.491526365780167</v>
+        <v>2.090211347089834</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>1.980652155783503</v>
+        <v>2.389623561023157</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>2.174416618063781</v>
+        <v>2.927206583548205</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>2.260004865244056</v>
+        <v>2.896892465590362</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.7848</t>
+          <t>X &gt; 0.7834</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.09931036688299599</v>
+        <v>0.4534746364118192</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.6503603401867224</v>
+        <v>1.084760783164093</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.9839948344628198</v>
+        <v>1.389520872305653</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.07419042131928677</v>
+        <v>0.7971186734974296</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.8210771141263464</v>
+        <v>1.496219402793798</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.3190669222709701</v>
+        <v>0.8734259132753124</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.826645797435738</v>
+        <v>1.4428663181966</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.7452847463834473</v>
+        <v>1.137945874787981</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.7867719282981511</v>
+        <v>1.265874784472089</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>1.588659401867965</v>
+        <v>1.834345706406737</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>1.075317469226732</v>
+        <v>1.326853625494508</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>1.780820034282684</v>
+        <v>1.829998766539774</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>1.051358754828136</v>
+        <v>1.358381502890175</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.81453184688548</v>
+        <v>2.085757197554628</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>1.746939730407284</v>
+        <v>2.14674305957201</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>1.553925077547127</v>
+        <v>1.986364527072027</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>1.026307153168084</v>
+        <v>1.355083985649053</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>1.807293221000442</v>
+        <v>1.967028154061381</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>1.038932633420835</v>
+        <v>1.555230082768482</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>1.324203640239254</v>
+        <v>1.633004197399714</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>1.37220865337558</v>
+        <v>1.910796850207277</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>1.591638282517664</v>
+        <v>1.994234780678617</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>2.358238979251681</v>
+        <v>3.282608695652179</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>1.790280741776442</v>
+        <v>2.689435218604096</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.8266</t>
+          <t>X &gt; 0.8252</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.758641599647504</v>
+        <v>-0.6161011988453424</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.9681051147893029</v>
+        <v>-0.488409030813223</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.02517178286790767</v>
+        <v>0.2494248872204778</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.114065651934709</v>
+        <v>-0.5920433140784098</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.1967232924017779</v>
+        <v>0.3777285582755638</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.6363235223445116</v>
+        <v>-0.08800284195300634</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.2804526573626731</v>
+        <v>0.4867781595129017</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.1932155971323652</v>
+        <v>0.8045227223309297</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.1093894958390536</v>
+        <v>0.8079186307697128</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.4642933686747455</v>
+        <v>1.008131145513019</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.3624131612126007</v>
+        <v>0.9067671563813562</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.7102301738047174</v>
+        <v>1.003784205646056</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.03699204342735385</v>
+        <v>0.262491091931274</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>1.621628328246359</v>
+        <v>1.882252049178113</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>1.715364729913929</v>
+        <v>2.024003034634362</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>2.059125085440876</v>
+        <v>2.412518052174441</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>1.549268098839342</v>
+        <v>1.760416666666664</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>2.196307094266281</v>
+        <v>2.204347329965643</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>1.535005492734463</v>
+        <v>1.869250427748582</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>1.596538019494474</v>
+        <v>1.658369188540433</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>2.181811400400626</v>
+        <v>2.548810099163255</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>2.231278722199541</v>
+        <v>2.67733899024801</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>2.881693284305655</v>
+        <v>3.754900887087942</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>2.304607898250303</v>
+        <v>3.293861882951617</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.8685</t>
+          <t>X &gt; 0.8669</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>567</v>
+        <v>577</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.9071610464125612</v>
+        <v>0.3822879476573249</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.00736994352781295</v>
+        <v>1.160271896936379</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.023746809910328</v>
+        <v>1.612062436683026</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-1.629242482901013</v>
+        <v>-0.004230547108136307</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.151369160953827</v>
+        <v>1.426695954430762</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.3671320250828316</v>
+        <v>0.9010357037735517</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.139080708973182</v>
+        <v>-0.2353432367868038</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-2.122759525860296</v>
+        <v>-1.393506001014536</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-3.315840245180162</v>
+        <v>-2.460116340477192</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-2.501454333915063</v>
+        <v>-1.720331658222129</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.9928267905185777</v>
+        <v>-0.2535573944710308</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.4920922363685207</v>
+        <v>1.005696828532081</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.8074366735210958</v>
+        <v>-0.6211406814101679</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.3824191943003896</v>
+        <v>0.4958129704672984</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>0.7824769549208881</v>
+        <v>1.008197837729007</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>1.200497033830366</v>
+        <v>1.673057762152354</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.7138462107858743</v>
+        <v>0.8169235159817276</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>1.490839722132243</v>
+        <v>1.472944225312958</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>0.2957963587884933</v>
+        <v>0.5889879157986044</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>0.3062753257230071</v>
+        <v>0.2177258120230761</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>2.409231803259622</v>
+        <v>2.510688456467015</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>2.509752684884027</v>
+        <v>2.71514001348261</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>2.255126868265556</v>
+        <v>2.89333533925079</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>2.5320283011093</v>
+        <v>3.185461035851453</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.9103</t>
+          <t>X &gt; 0.9087</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>388</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.225132268011329</v>
+        <v>1.140917575686871</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.6635513459501752</v>
+        <v>0.8950107399830003</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1.287387967022276</v>
+        <v>2.425126764673692</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.9719578049977784</v>
+        <v>0.0605726671312965</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-1.307748277545052</v>
+        <v>0.03817908399398817</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1.89397796773634</v>
+        <v>-0.311216423931981</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-2.408194692863802</v>
+        <v>-0.3468047652786197</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-2.170942220091099</v>
+        <v>-0.3985606517252123</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-3.675846790753717</v>
+        <v>-2.042783640775284</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-3.160102672975768</v>
+        <v>-1.573012351184495</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.59738323699942</v>
+        <v>-0.2881191087320545</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>1.474382823470108</v>
+        <v>2.726438177302974</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.866684674139762</v>
+        <v>1.864710616814229</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>1.676533632744729</v>
+        <v>2.629134783229212</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>0.2451944588755026</v>
+        <v>1.18748673045809</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>0.3241174632927226</v>
+        <v>1.242461635353699</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>0.4479322850781315</v>
+        <v>0.8854166666666643</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>1.11628745754561</v>
+        <v>1.158623932063442</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>0.04351904465550405</v>
+        <v>1.017885373892568</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>0.7458287721493022</v>
+        <v>1.13056082554656</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>2.780602191812143</v>
+        <v>3.529737755346986</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>3.735684065454585</v>
+        <v>4.385128056527641</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>2.979230942885096</v>
+        <v>4.278752654521071</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>3.676594565950474</v>
+        <v>5.05345939208437</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.9521</t>
+          <t>X &gt; 0.9504</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.4636304985083299</v>
+        <v>1.366464180980309</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>1.248256685233144</v>
+        <v>2.211466436185539</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.9360310205142639</v>
+        <v>0.229499607021225</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-3.887791010106262</v>
+        <v>-2.181084409968818</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-4.223581482653536</v>
+        <v>-2.456642550068153</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-6.275421266705408</v>
+        <v>-3.754254398615522</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-5.554832637162917</v>
+        <v>-2.367518229030054</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-5.086775425199583</v>
+        <v>-1.945165945165954</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-6.164691228359509</v>
+        <v>-3.271782490027299</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-8.430144217828833</v>
+        <v>-5.52237943979209</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-5.917278605517652</v>
+        <v>-3.068326243369569</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-2.464684725383563</v>
+        <v>-0.07218092511359231</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-1.34904082209043</v>
+        <v>0.6311087756174558</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.2955519432540257</v>
+        <v>2.20105653236616</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-1.481994339401155</v>
+        <v>0.4279930595720103</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-1.260741745816368</v>
+        <v>0.6256607147553055</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-1.021524554435636</v>
+        <v>0.1581439393939448</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.7532309298986064</v>
+        <v>-0.3383765294040231</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-2.029876862407122</v>
+        <v>-0.6388446274075648</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>0.02264058935195123</v>
+        <v>0.5222405743691638</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>1.345766063176967</v>
+        <v>2.378842614682029</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>2.762457415200707</v>
+        <v>3.269601516646873</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>3.036932127682761</v>
+        <v>4.486312399355889</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>2.961099874459485</v>
+        <v>4.560990147459364</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.994</t>
+          <t>X &gt; 0.9922</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>171</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-1.594063487700971</v>
+        <v>-0.399769585253452</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>1.579931643773776</v>
+        <v>2.782895007614101</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.4428827268946449</v>
+        <v>0.9567723342939587</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-2.910222711249659</v>
+        <v>-0.7784870073714103</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-5.000399148709221</v>
+        <v>-2.196902290327891</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-5.9830236058867</v>
+        <v>-3.182825827186953</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-7.924562933051902</v>
+        <v>-4.549336410848241</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-4.694002447980417</v>
+        <v>-1.42568542568543</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-6.406901230977986</v>
+        <v>-3.012042230287037</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-9.518998193564194</v>
+        <v>-6.093808011220666</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-7.49055258648999</v>
+        <v>-4.10728728233061</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-6.014916025025698</v>
+        <v>-2.669583522516191</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-3.629306162057254</v>
+        <v>-1.498761354252686</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.8279775345955684</v>
+        <v>2.824433155742774</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-1.584551727897271</v>
+        <v>0.4279930595720103</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.9901648059542794</v>
+        <v>0.9892970783916724</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-1.708877264569175</v>
+        <v>-0.2574404761904816</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.0593320034780831</v>
+        <v>0.1811039900764939</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-1.597826587466031</v>
+        <v>0.3955662172222674</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>0.3434051874142696</v>
+        <v>0.9516961762385634</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>2.724835627635379</v>
+        <v>3.619917079149893</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>4.988170952775981</v>
+        <v>5.856893285518304</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>2.923464378708331</v>
+        <v>5.317492416582418</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>2.847632125485056</v>
+        <v>5.532750403117099</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 1.036</t>
+          <t>X &gt; 1.034</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.499503763761012</v>
+        <v>0.6946614074826201</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>2.164726965411198</v>
+        <v>2.143669826016037</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1.603900898836351</v>
+        <v>0.0415180970058131</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-2.617825050430952</v>
+        <v>-2.24579935603969</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-4.708001487890499</v>
+        <v>-3.368815123257669</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-6.275421266705408</v>
+        <v>-4.059339144378235</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-7.047369950595758</v>
+        <v>-4.006963529492303</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-2.939616483068129</v>
+        <v>-0.07459583730770447</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-3.775322283609569</v>
+        <v>-0.7941245547422469</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-6.302623924558333</v>
+        <v>-4.132548931317508</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-4.274178317484136</v>
+        <v>-1.317941035357251</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-3.675734738475988</v>
+        <v>-0.7470653627098969</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.4129318930514003</v>
+        <v>1.527873028313898</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>2.874761160326571</v>
+        <v>4.66946947535537</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>0.4622318978337248</v>
+        <v>2.292399839233028</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>1.056618819776716</v>
+        <v>2.85370385805269</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>0.04550870034309895</v>
+        <v>1.902365819209038</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>1.695053961434205</v>
+        <v>3.464396968284724</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-2.475019569922175</v>
+        <v>0.2890286869559162</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>1.220598169870414</v>
+        <v>3.045988013370838</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>2.432437966816671</v>
+        <v>3.86199998019233</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>7.619749900144406</v>
+        <v>8.915042586442176</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>5.262645665258034</v>
+        <v>7.449275362318836</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>4.309620429578622</v>
+        <v>7.287136368029373</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 1.078</t>
+          <t>X &gt; 1.076</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>69</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.01765870763485822</v>
+        <v>0.7430875576036868</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>1.096839856334164</v>
+        <v>1.925752150471247</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.3411791926968277</v>
+        <v>0.6710580485796669</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-3.952683936777255</v>
+        <v>-1.349915578799987</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-5.737749771643365</v>
+        <v>-3.054045147470745</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-11.34788503482135</v>
+        <v>-7.182825827186953</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-9.221282994074016</v>
+        <v>-5.120764982276818</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-6.600943714189413</v>
+        <v>-2.568542568542576</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-3.660905807637022</v>
+        <v>0.4165291982843868</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-5.883096845992362</v>
+        <v>-1.808093725506374</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-5.609037203830439</v>
+        <v>-1.535858710902041</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-8.786337331916108</v>
+        <v>-4.669583522516191</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-9.909499398772226</v>
+        <v>-5.784475639966963</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-2.88420146362462</v>
+        <v>1.110147441457066</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-4.991620123524015</v>
+        <v>-1.000578368999413</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-4.397233201581024</v>
+        <v>-0.4392743501797511</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-3.081874976239661</v>
+        <v>-0.5431547619047592</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.2881649554231629</v>
+        <v>0.7525325615050633</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-2.970824299136517</v>
+        <v>-0.4615766399205867</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-1.334703126849647</v>
+        <v>-0.2469901948616027</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.4279739324968403</v>
+        <v>0.03442658740154769</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>5.293281555369425</v>
+        <v>5.756365514721629</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>2.669205543213792</v>
+        <v>4.550724637681157</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.3051774346471632</v>
+        <v>2.939310281072856</v>
       </c>
     </row>
   </sheetData>
@@ -5824,2461 +5824,2461 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.1355</t>
+          <t>X &lt; -0.1354</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-4.365484794591382</v>
+        <v>-4.971198156682028</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-6.149536955260039</v>
+        <v>-6.645676420957329</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-11.93538209124755</v>
+        <v>-10.75751337999176</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-14.09761147300914</v>
+        <v>-12.77848700737142</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-11.53485122091873</v>
+        <v>-10.19690229032789</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-4.804833031411292</v>
+        <v>-2.897111541472661</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>4.14665990015051</v>
+        <v>4.87923501772319</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>8.346060395695943</v>
+        <v>8.860028860028848</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>3.909935637312138</v>
+        <v>3.273672055427248</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>1.644482647842807</v>
+        <v>1.049049131636487</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-1.066532336860938</v>
+        <v>-1.535858710902041</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-5.822893680607443</v>
+        <v>-6.098154951087629</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-6.946055747463561</v>
+        <v>-7.213047068538401</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-4.182059997044476</v>
+        <v>-4.604138272828649</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-4.840203294625034</v>
+        <v>-5.286292654713705</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-8.723428312980552</v>
+        <v>-9.010702921608328</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-2.887196196226682</v>
+        <v>-3.40029761904762</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-4.484574213480698</v>
+        <v>-4.961753152780652</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-5.761220145989206</v>
+        <v>-6.175862354206302</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-5.574374336021179</v>
+        <v>-5.961275909147318</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-9.101995130852885</v>
+        <v>-9.385863267670914</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-6.192766465396311</v>
+        <v>-6.603882932483337</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-6.619332006193318</v>
+        <v>-7.788819875776397</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-2.149709713962046</v>
+        <v>-3.665244584351569</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.0937</t>
+          <t>X &lt; -0.0936</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-7.807513780098638</v>
+        <v>-7.709293394777269</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-6.05895724511511</v>
+        <v>-5.871866897147797</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-11.66364296081277</v>
+        <v>-11.29322766570605</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-9.251596980255513</v>
+        <v>-8.760629864514272</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-5.420720786136123</v>
+        <v>-4.869521337946942</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.4859475824948873</v>
+        <v>0.4957456013844777</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>5.718587496212749</v>
+        <v>5.950663589151759</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>6.504205838693721</v>
+        <v>6.687409812409804</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>5.481863233374376</v>
+        <v>4.732005388760584</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>2.58128798286981</v>
+        <v>1.85262056020791</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.3361417366703918</v>
+        <v>-1.000144425187756</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-4.870210289054569</v>
+        <v>-5.443393046325717</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-4.929542568676645</v>
+        <v>-5.516618497109825</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-1.959132083421096</v>
+        <v>-2.639852558542934</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-3.68110516823571</v>
+        <v>-4.363673607094654</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-6.278207607994844</v>
+        <v>-6.927369588274992</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-1.092975808802102</v>
+        <v>-1.822916666666671</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-4.389305874325409</v>
+        <v>-5.080800771828272</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-5.237244280635132</v>
+        <v>-5.908005211349163</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-5.050398470667105</v>
+        <v>-5.693418766290179</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-7.720604213101211</v>
+        <v>-8.344196601004249</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-6.160668888763354</v>
+        <v>-7.377692456292863</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-5.301808949539833</v>
+        <v>-7.134057971014485</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-2.11677163754571</v>
+        <v>-4.171196965303949</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.05187</t>
+          <t>X &lt; -0.05184</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-2.577017326197925</v>
+        <v>-2.478796940876556</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-5.748673557171855</v>
+        <v>-5.561583209204542</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-6.477472748046814</v>
+        <v>-6.10705745294009</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-5.062767193021472</v>
+        <v>-4.57180007728023</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-3.270898091100662</v>
+        <v>-2.719698642911482</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.1531501618660229</v>
+        <v>0.9833342538667509</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>3.384284725663235</v>
+        <v>3.734351532414166</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>3.106073280910159</v>
+        <v>3.429431089005547</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.989287081529902</v>
+        <v>0.7204805660655538</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-1.222477515369903</v>
+        <v>-1.494010645465849</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-5.264964635797909</v>
+        <v>-5.477094779797689</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-6.263138499677559</v>
+        <v>-6.462896592425011</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-5.947451645670363</v>
+        <v>-6.159348993563725</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-3.290832680390345</v>
+        <v>-3.570703622372719</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-5.387824898834204</v>
+        <v>-5.671297720569832</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-6.951711358186181</v>
+        <v>-7.237653276218261</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-4.207930653437032</v>
+        <v>-4.504654255319153</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-7.190469198984836</v>
+        <v>-7.47441779310487</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-6.97457781806051</v>
+        <v>-7.259955565959096</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-6.787732008092483</v>
+        <v>-7.045369120900112</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-8.769127096921814</v>
+        <v>-9.031253338592904</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-7.750196705500144</v>
+        <v>-8.397196002392157</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-7.0948905109489</v>
+        <v>-8.153561517113779</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-5.710868749573642</v>
+        <v>-6.897260795091185</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.01003</t>
+          <t>X &lt; -0.01008</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-3.911117383702233</v>
+        <v>-3.542626728110598</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-6.408056344214209</v>
+        <v>-5.939071198223068</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-6.22445377162358</v>
+        <v>-5.5808620743082</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-5.315786169444699</v>
+        <v>-4.824819053703457</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-5.651576641991973</v>
+        <v>-5.100377193802792</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-1.384116918879322</v>
+        <v>-0.6191192634803855</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.8761273171637995</v>
+        <v>1.288501426989598</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.5979158724107236</v>
+        <v>0.9835809835809783</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.4534931205379564</v>
+        <v>-0.5101117283565344</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-3.412201146301214</v>
+        <v>-3.468325385738034</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-6.416830028729464</v>
+        <v>-6.439333614376942</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-8.334923694472543</v>
+        <v>-8.33753719046986</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-5.632949149306796</v>
+        <v>-5.668645524136849</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-4.761131850889996</v>
+        <v>-4.835798504488878</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-7.605067498197336</v>
+        <v>-7.680115048536095</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-9.196472925981119</v>
+        <v>-9.280973191878594</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-6.598149625800119</v>
+        <v>-6.682150900900908</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-8.342334591916391</v>
+        <v>-8.436656627684123</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-8.672891298423757</v>
+        <v>-8.762734941078897</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-7.939597401024038</v>
+        <v>-8.007607955479365</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-9.575039743853452</v>
+        <v>-9.65613353794118</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-8.275758100626746</v>
+        <v>-8.650214978815384</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-7.715933379037786</v>
+        <v>-8.406580493537007</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-6.686793256570454</v>
+        <v>-7.48763840674539</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; 0.0318</t>
+          <t>X &lt; 0.03168</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-5.656976145690031</v>
+        <v>-5.349855643773246</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-7.604656169846301</v>
+        <v>-7.20218818228836</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-6.220094573715997</v>
+        <v>-5.645637304260269</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-3.707242141545841</v>
+        <v>-3.216275025804599</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-4.446258420544723</v>
+        <v>-3.895058972355542</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.8098342221709913</v>
+        <v>-0.1090931082929458</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.5433049099453484</v>
+        <v>-0.0977235076224261</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-2.041028549820375</v>
+        <v>-1.612321370385899</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-3.219053563027629</v>
+        <v>-3.097295686508239</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-5.61798549922672</v>
+        <v>-5.506250407534026</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-7.782950247308698</v>
+        <v>-7.653370231639371</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-7.248691520675386</v>
+        <v>-7.123500573207437</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-4.306812937125002</v>
+        <v>-4.206134626142088</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-4.527891813571593</v>
+        <v>-4.454368687575197</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-7.625059501396059</v>
+        <v>-7.555877908169926</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-8.656688839615661</v>
+        <v>-8.607477115156712</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-5.945077521308583</v>
+        <v>-5.888776881720439</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-7.269430420251723</v>
+        <v>-7.231338406236873</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-6.647034974286747</v>
+        <v>-6.613650372639491</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-6.86669322935937</v>
+        <v>-6.802289734032115</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-7.4092393973254</v>
+        <v>-7.369734235412849</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-6.04655872857024</v>
+        <v>-6.235219338013302</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-6.370946511906183</v>
+        <v>-6.798036465638148</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-4.807434502834376</v>
+        <v>-5.347272234121156</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; 0.07363</t>
+          <t>X &lt; 0.07344</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-4.898708748652091</v>
+        <v>-5.105126728110598</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-3.661158502976747</v>
+        <v>-3.631793751902251</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-3.994084601191318</v>
+        <v>-3.785366030485925</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-2.183379314640376</v>
+        <v>-1.061497372400702</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-3.297830490777478</v>
+        <v>-2.430175346385759</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.4024053936895342</v>
+        <v>0.5748595254351088</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.6779431990034013</v>
+        <v>-0.2202224867976099</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.911568656495334</v>
+        <v>-1.474510018813824</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-3.780909500058335</v>
+        <v>-3.561770982547444</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-5.509239188833675</v>
+        <v>-5.307189566374369</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-6.509064896990225</v>
+        <v>-6.617233032782693</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-4.876986274960515</v>
+        <v>-4.9950808100388</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-2.815434966020455</v>
+        <v>-2.945415965464257</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-3.673456517626285</v>
+        <v>-3.826561419302422</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-5.287013827945692</v>
+        <v>-5.774538585997611</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-5.648040918741557</v>
+        <v>-6.162601655785537</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-3.234187355082085</v>
+        <v>-3.418380801687768</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-4.931384746801356</v>
+        <v>-5.133543387862026</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-5.033964703456647</v>
+        <v>-5.235536856918785</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-5.802532906227476</v>
+        <v>-5.970317500467388</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-5.708136399034274</v>
+        <v>-5.904850609443066</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-5.291521889553486</v>
+        <v>-5.66355743519582</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-5.162455549316867</v>
+        <v>-5.736378646119974</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-3.635723699976033</v>
+        <v>-4.316239159396773</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; 0.1155</t>
+          <t>X &lt; 0.1152</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-2.518652599716255</v>
+        <v>-2.311099634514534</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-2.725623911781788</v>
+        <v>-2.183595292209532</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-4.035196845524553</v>
+        <v>-3.55807915085456</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.603983914928882</v>
+        <v>-1.045059144911292</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-3.061883674465257</v>
+        <v>-2.926113377747939</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.2902352989511527</v>
+        <v>0.4646510740212904</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.844838305026137</v>
+        <v>-1.076699594927845</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.388872534589339</v>
+        <v>-2.625401132863828</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-3.360043580522742</v>
+        <v>-3.741253317707084</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-4.386123813521259</v>
+        <v>-4.786061031831885</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-4.871557842245402</v>
+        <v>-5.260094673943975</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-2.871826233035172</v>
+        <v>-3.297870658266021</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-3.235494629005217</v>
+        <v>-3.666494119000369</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-3.203408948489781</v>
+        <v>-3.665971961528008</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-3.861552246070339</v>
+        <v>-4.348126343413064</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-4.7861526658995</v>
+        <v>-5.279359638026236</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-3.907411575028874</v>
+        <v>-4.388215174129364</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-4.265416835812083</v>
+        <v>-4.769855498196428</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-4.555854568811803</v>
+        <v>-5.052905708861594</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-3.86267964491973</v>
+        <v>-4.34080682599167</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-3.392567585037654</v>
+        <v>-3.913226451750518</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-3.325124977404798</v>
+        <v>-3.988388973705803</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-2.906632491967088</v>
+        <v>-3.495998269521948</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-1.455747187938449</v>
+        <v>-2.165599950378585</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; 0.1573</t>
+          <t>X &lt; 0.157</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-2.149793435499561</v>
+        <v>-1.87922164004798</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.983592039271826</v>
+        <v>-1.435592387343874</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-3.717036174385626</v>
+        <v>-3.373286604802317</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.726596980255508</v>
+        <v>-1.501771596797731</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-2.754972623143473</v>
+        <v>-2.853988793568234</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.05052166831183058</v>
+        <v>-0.3301912822447051</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.9105490250424353</v>
+        <v>-1.519750612031672</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.993589443638577</v>
+        <v>-2.416387031771656</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.348480531341572</v>
+        <v>-1.8939808045333</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.316567233535004</v>
+        <v>-1.901077664644163</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.847336565216139</v>
+        <v>-2.615035943925427</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.7176352644387904</v>
+        <v>-1.510947286956885</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.2311393836087916</v>
+        <v>-0.8506914754135764</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.2510110165946173</v>
+        <v>-0.7044482192924448</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-1.11036155763594</v>
+        <v>-1.583841259954617</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-1.522010852996765</v>
+        <v>-1.81149187624343</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-1.052306259591951</v>
+        <v>-1.323656311637087</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.9559397199523687</v>
+        <v>-1.062063099244448</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.9412555824888074</v>
+        <v>-1.044839530875791</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.553202529060016</v>
+        <v>-0.63301442703969</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.08971247972221619</v>
+        <v>-0.2142656345348186</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>0.1565354123119249</v>
+        <v>-0.09218949771297957</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>0.5523851655238516</v>
+        <v>0.348683646342522</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>1.48665392240158</v>
+        <v>1.17273794593865</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; 0.1991</t>
+          <t>X &lt; 0.1987</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>607</v>
+        <v>625</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.7187691913540419</v>
+        <v>-0.3680235535074203</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-2.105705212594792</v>
+        <v>-1.642269652844675</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-3.459245566675968</v>
+        <v>-3.132399640228343</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.151066800810163</v>
+        <v>-0.9306856858858836</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.723825361299511</v>
+        <v>-1.75783337202575</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.1379417249705526</v>
+        <v>-0.2342543986155192</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.9817961801039559</v>
+        <v>-1.349336410848238</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.587876477316051</v>
+        <v>-1.814256854256861</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.054586016712818</v>
+        <v>-1.366327944572753</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.007829561601767</v>
+        <v>-1.362379439792093</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.881310903046398</v>
+        <v>-2.530144425187757</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.832191454035382</v>
+        <v>-2.32672637965905</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.496337127448875</v>
+        <v>-1.04161849710983</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.5534815776659556</v>
+        <v>-0.9698525585429323</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-1.047690449017011</v>
+        <v>-1.332006940427988</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-2.092647789369103</v>
+        <v>-2.21070292160833</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-1.734761647658047</v>
+        <v>-1.834583333333335</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-1.839602351479229</v>
+        <v>-1.647467438494942</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-1.623710970554903</v>
+        <v>-1.433005211349169</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.9450618818983543</v>
+        <v>-0.7384187662901809</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.3400670662578236</v>
+        <v>-0.1858632676709178</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.1539948064496599</v>
+        <v>-0.101025789626199</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.1101613522858145</v>
+        <v>-0.0173913043478251</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>0.4063284269195861</v>
+        <v>0.4604697013627188</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; 0.241</t>
+          <t>X &lt; 0.2405</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>720</v>
+        <v>743</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.821174982284425</v>
+        <v>-2.606797851105249</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-3.08643102532487</v>
+        <v>-2.382911073854636</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-4.043779947114139</v>
+        <v>-3.702745091979509</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.491480382175958</v>
+        <v>-2.078582884648497</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-3.440409430824765</v>
+        <v>-3.491833165903934</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.117236947585731</v>
+        <v>-1.245506080984292</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.537728077317524</v>
+        <v>-1.771409089179336</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.678198475238645</v>
+        <v>-1.537971524512585</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.284094213434123</v>
+        <v>-1.54463211684731</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.9535616136085565</v>
+        <v>-1.263967595915915</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.645019212825943</v>
+        <v>-1.933859095443481</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.569986943574378</v>
+        <v>-1.806672543858241</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.8169502376681308</v>
+        <v>-1.037311633045221</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.623091354778623</v>
+        <v>-0.7471876864029596</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.8662968930230832</v>
+        <v>-0.8909840602126522</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-1.655035835533752</v>
+        <v>-1.540985559562571</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-1.788952972511225</v>
+        <v>-1.644865971287579</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-1.617168503441675</v>
+        <v>-1.23939206837381</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-1.677902295408082</v>
+        <v>-1.15951934324687</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-1.076118726103957</v>
+        <v>-0.541164392131364</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.9271019618431566</v>
+        <v>-0.4356613834178873</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.2288188902526471</v>
+        <v>0.02753410270219803</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.1489415552203468</v>
+        <v>0.1365790859617277</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>0.1356438213914828</v>
+        <v>0.3782085977288006</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; 0.2828</t>
+          <t>X &lt; 0.2823</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>823</v>
+        <v>852</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.744789765761716</v>
+        <v>-2.550794756115273</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-2.061748313695659</v>
+        <v>-1.568907395590173</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-3.198074098537319</v>
+        <v>-2.879484975647571</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.929954294404197</v>
+        <v>-1.771461246247291</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.920970886176136</v>
+        <v>-2.921739001096611</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.227344343628481</v>
+        <v>-1.294160501901906</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.414397628092757</v>
+        <v>-2.558726082209745</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.506304286915096</v>
+        <v>-2.394162957543244</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.157435588584917</v>
+        <v>-2.266234047859136</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.085960432293298</v>
+        <v>-2.240689298947018</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.589713532332851</v>
+        <v>-2.79005052847414</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.31804789743142</v>
+        <v>-2.479778022851541</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.436677698242349</v>
+        <v>-1.599364975983065</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.294560448780956</v>
+        <v>-1.378115469341061</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-1.226311494545527</v>
+        <v>-1.356044499113437</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-2.084709076234503</v>
+        <v>-2.085820292500351</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-2.33969158851464</v>
+        <v>-2.307071596244135</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-2.202401541730488</v>
+        <v>-1.97047213333061</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-1.744379410200835</v>
+        <v>-1.521268122147291</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-1.194337474324826</v>
+        <v>-0.9545690010319632</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-1.010491390474868</v>
+        <v>-0.8177881503000251</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.5301703550390044</v>
+        <v>-0.4234671041801832</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.1836156190206282</v>
+        <v>-0.06246172688303631</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>0.2988340468538908</v>
+        <v>0.4796246309401795</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 0.3246</t>
+          <t>X &lt; 0.324</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>942</v>
+        <v>975</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.230188806221932</v>
+        <v>-2.216096115865696</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-2.406586254878007</v>
+        <v>-2.103140305387498</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-3.371758144058845</v>
+        <v>-3.100487379407475</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-2.457833877530142</v>
+        <v>-2.309120140870462</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-3.681694902960189</v>
+        <v>-3.554630627564421</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.653572527209612</v>
+        <v>-1.600408244769369</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-2.788694871731408</v>
+        <v>-2.805746667258489</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-2.799265605875142</v>
+        <v>-2.700410700410707</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.962703275604838</v>
+        <v>-2.162225380470183</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.314122639734059</v>
+        <v>-2.548020465433119</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.719659108068186</v>
+        <v>-2.891170066213398</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.623473673987952</v>
+        <v>-2.860059712992388</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.996701041080037</v>
+        <v>-2.231362086853416</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.794946936554119</v>
+        <v>-1.966775635466014</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-2.030257253162155</v>
+        <v>-2.136109504530559</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-2.704369274136717</v>
+        <v>-2.600446511351919</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-2.943994656357319</v>
+        <v>-2.806891025641029</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-2.414585888719721</v>
+        <v>-2.221826412853908</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-2.198694507795395</v>
+        <v>-2.007364185708134</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-1.483307471611731</v>
+        <v>-1.279957227828639</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-1.647205586511106</v>
+        <v>-1.539709421517067</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.7080080540631428</v>
+        <v>-0.5892309178313297</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.3707378996988879</v>
+        <v>-0.3455964325529521</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.2774842748576276</v>
+        <v>-0.2000431191501093</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 0.3665</t>
+          <t>X &lt; 0.3658</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1047</v>
+        <v>1084</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-2.325057639747754</v>
+        <v>-2.394784671177632</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.953046301245564</v>
+        <v>-1.766474740285055</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.682946162319368</v>
+        <v>-2.605325181805405</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.21519264472299</v>
+        <v>-2.228631706134898</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-3.443519528274486</v>
+        <v>-3.376625792632048</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.695629009859324</v>
+        <v>-1.602962885700386</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.415989988402941</v>
+        <v>-2.398044897933104</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.074871840003524</v>
+        <v>-2.05720888377715</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.602276031615951</v>
+        <v>-1.744778129074597</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.943265813641233</v>
+        <v>-1.987324089238584</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.900597306132227</v>
+        <v>-2.084092764671155</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.936343525400567</v>
+        <v>-2.083921951614776</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.58029897997023</v>
+        <v>-1.722799308917942</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.326092685314151</v>
+        <v>-1.417527835295694</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-1.318836743350992</v>
+        <v>-1.361674837106953</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-1.770077197833849</v>
+        <v>-1.722880043379547</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-2.094108403252392</v>
+        <v>-2.011262300123008</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-1.53354986752985</v>
+        <v>-1.313888102701576</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-1.317658486605524</v>
+        <v>-1.099425875555802</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.5045758498601671</v>
+        <v>-0.3313338954414746</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.7054066447121627</v>
+        <v>-0.6220256292945336</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.4388857260994641</v>
+        <v>-0.3281844612129134</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.01223045634367281</v>
+        <v>0.007700946574686895</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.03110243776165333</v>
+        <v>0.03006379730366859</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 0.4083</t>
+          <t>X &lt; 0.4075</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1135</v>
+        <v>1172</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.383902668987524</v>
+        <v>-1.376101664389275</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.412635206308281</v>
+        <v>-1.152479142045763</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.457121221682335</v>
+        <v>-2.277270218897542</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.340696196965695</v>
+        <v>-2.228474838960608</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-3.413606964997904</v>
+        <v>-3.311017501629806</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.523895547437753</v>
+        <v>-1.402718562438046</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.986287926162952</v>
+        <v>-1.94182787842503</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.954402356047524</v>
+        <v>-1.820127161424097</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.340038269378184</v>
+        <v>-1.350901323412344</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.889030886845951</v>
+        <v>-1.890980122385955</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.003615746433042</v>
+        <v>-2.045366268191167</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.619981859345657</v>
+        <v>-1.639354366007169</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.026966980770702</v>
+        <v>-1.047761841819728</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.6340107694979906</v>
+        <v>-0.6134020465975496</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.7658382776048782</v>
+        <v>-0.6982868039092196</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-1.224082934609243</v>
+        <v>-1.07554933799058</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-1.358000071586716</v>
+        <v>-1.179429749715588</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-1.024244284179829</v>
+        <v>-0.7150442303038034</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.4574757102730587</v>
+        <v>-0.1592850748303931</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.218799270173939</v>
+        <v>0.05530137022859094</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.5336767928417103</v>
+        <v>-0.3414946669883179</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.2055521412387407</v>
+        <v>0.0099639714659574</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.1425927829752212</v>
+        <v>-0.0023742395013997</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.07789019720861035</v>
+        <v>0.09145946245487124</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 0.4501</t>
+          <t>X &lt; 0.4493</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1243</v>
+        <v>1282</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.42214663799615</v>
+        <v>-1.483574669058541</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.001793618363855</v>
+        <v>-0.8336346524614342</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.921579468749279</v>
+        <v>-1.891476692943399</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.559480220922715</v>
+        <v>-1.507904007816457</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-2.32884214278689</v>
+        <v>-2.286869999937068</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.9054928657507588</v>
+        <v>-0.840057830752805</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.394503708557544</v>
+        <v>-1.401130482611116</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.628370239970344</v>
+        <v>-1.550044685770118</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.382977786001909</v>
+        <v>-1.422115776086009</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.552620424187296</v>
+        <v>-1.594142310306907</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.712662707372594</v>
+        <v>-1.711922896326605</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.466975430133189</v>
+        <v>-1.442483009924267</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.9448617176128096</v>
+        <v>-0.9973127248789382</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.2386067269657275</v>
+        <v>-0.3095093448143871</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.3363016658593381</v>
+        <v>-0.3676387657010025</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.6226193075672697</v>
+        <v>-0.5083628280045858</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.6764723933037402</v>
+        <v>-0.5342401196047888</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.3809928409199657</v>
+        <v>-0.1211023838927545</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.04269298068511063</v>
+        <v>0.2493660835026361</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.2772815784721132</v>
+        <v>0.385949408436808</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.4582156334762004</v>
+        <v>-0.3375013331935364</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>0.07589025102159752</v>
+        <v>0.1333579857248139</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.08371863778252475</v>
+        <v>-0.01302312962083363</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.5138824144179281</v>
+        <v>-0.4091714842847125</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.492</t>
+          <t>X &lt; 0.4911</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1342</v>
+        <v>1381</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.620274005423148</v>
+        <v>-1.73887492435879</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.475623911781781</v>
+        <v>-1.297558834572591</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.28634347589739</v>
+        <v>-2.225308590561546</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.223798747560373</v>
+        <v>-2.128760739423889</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.519867187511707</v>
+        <v>-2.437960797667159</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.408164629537268</v>
+        <v>-1.300959684640148</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.139620873104981</v>
+        <v>-2.023630400710651</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.860293359898314</v>
+        <v>-1.676849178659474</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.629992217868725</v>
+        <v>-1.621331565137559</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.696063143908489</v>
+        <v>-1.693270098734885</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.046458759521876</v>
+        <v>-2.072736749590369</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.061699650756687</v>
+        <v>-2.059673519412854</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.66076979767211</v>
+        <v>-1.581517121295192</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.09733525281311</v>
+        <v>-1.033226924944088</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-1.087822764043516</v>
+        <v>-0.9912683452071391</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-1.161091628450677</v>
+        <v>-1.00925469568508</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-1.220824789167018</v>
+        <v>-1.040723811247886</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-1.251481516727083</v>
+        <v>-0.9563740279228909</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-1.066431284062766</v>
+        <v>-0.8143230969393187</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.9104724487265941</v>
+        <v>-0.6721479480425288</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-1.483951519911308</v>
+        <v>-1.312003745585464</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-1.144347844216497</v>
+        <v>-0.8802871944053479</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-1.123946279981091</v>
+        <v>-0.9262978937757751</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-1.305199033385797</v>
+        <v>-1.16084818422744</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.5338</t>
+          <t>X &lt; 0.5328</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1440</v>
+        <v>1480</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.586052592884023</v>
+        <v>-1.658373699846805</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.473910409382874</v>
+        <v>-1.397961173242081</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.327223207726348</v>
+        <v>-2.213038986460766</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.180131640516322</v>
+        <v>-2.095508488924253</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.410189650604991</v>
+        <v>-2.334939691523196</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.292603397289597</v>
+        <v>-1.061479246691142</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.233064586084062</v>
+        <v>-2.089876951388781</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.854142992045325</v>
+        <v>-1.651554151554159</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.636711293323941</v>
+        <v>-1.52362524187005</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.751014024549875</v>
+        <v>-1.644001061413711</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.058812316274221</v>
+        <v>-1.979874154917482</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.092065420252901</v>
+        <v>-1.986185839118512</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.450055087778559</v>
+        <v>-1.411888767380098</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.078366302421529</v>
+        <v>-1.052014720705095</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.8380990955100316</v>
+        <v>-0.7882231566442073</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-0.8656886766769318</v>
+        <v>-0.7674596783650784</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-0.8207648673936632</v>
+        <v>-0.7362049549549567</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-1.063918157660211</v>
+        <v>-0.8015214925489929</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-0.7382381700557232</v>
+        <v>-0.5194916978356474</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.718460001874746</v>
+        <v>-0.5076079554793722</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-1.220405159710673</v>
+        <v>-1.075052456860107</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-1.047549416107394</v>
+        <v>-0.8799447085451249</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-1.009801587502601</v>
+        <v>-0.9065804935370139</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-1.11435617860851</v>
+        <v>-1.001151920258906</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.5756</t>
+          <t>X &lt; 0.5746</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1556</v>
+        <v>1594</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-2.056563209756426</v>
+        <v>-2.137255085387302</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.978160373417793</v>
+        <v>-1.851033563814468</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-2.304505904975208</v>
+        <v>-2.322777384280158</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.031358885017418</v>
+        <v>-2.00609294336283</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.586910959791354</v>
+        <v>-2.561156695909787</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.984257884632939</v>
+        <v>-1.932199260770908</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-2.5308305103922</v>
+        <v>-2.505449263512816</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.01049546282178</v>
+        <v>-1.898171534307053</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.487915869485086</v>
+        <v>-1.456566338550168</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.842860749891273</v>
+        <v>-1.75073577605307</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.851827798329111</v>
+        <v>-1.792177047521506</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.903435451650118</v>
+        <v>-1.755082715920032</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.713597349796721</v>
+        <v>-1.678004946294266</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.642362319299018</v>
+        <v>-1.487092207225494</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-1.469834690361999</v>
+        <v>-1.290952988106788</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-1.41343098504224</v>
+        <v>-1.294266284218118</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-1.446224471357738</v>
+        <v>-1.398146695943126</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-1.705893991033399</v>
+        <v>-1.593766058319275</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-1.196599304010761</v>
+        <v>-1.12836280231528</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-1.10058941447506</v>
+        <v>-0.9765116144708514</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-1.477513306491687</v>
+        <v>-1.48122085863703</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-1.323339530749912</v>
+        <v>-1.368177608948663</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-1.332358222109704</v>
+        <v>-1.375484152528493</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-1.242176801287755</v>
+        <v>-1.349417375174298</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.6175</t>
+          <t>X &lt; 0.6164</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1684</v>
+        <v>1723</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.999580993854011</v>
+        <v>-2.097540022908284</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.952163501224597</v>
+        <v>-1.850997415751998</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.892516200249396</v>
+        <v>-1.802486924965301</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.693244073620164</v>
+        <v>-1.553406355539167</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-2.349578992168247</v>
+        <v>-2.145255212029589</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.778066769350907</v>
+        <v>-1.551355847890882</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-2.282664068242823</v>
+        <v>-2.08297910226355</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.057776804412988</v>
+        <v>-1.775905142126859</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.571491151007748</v>
+        <v>-1.357784706035311</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.840156618993305</v>
+        <v>-1.631491453721289</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.827761568063416</v>
+        <v>-1.649447965524374</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.955504960491204</v>
+        <v>-1.751915004151215</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.628781434259807</v>
+        <v>-1.415849489564842</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.815863807290349</v>
+        <v>-1.664083550997951</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-1.351738941846691</v>
+        <v>-1.185471827253295</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-1.372770255748975</v>
+        <v>-1.204550861248492</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-1.472330842333818</v>
+        <v>-1.3084312729735</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-1.897803922921661</v>
+        <v>-1.615430293979557</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-1.233238385166324</v>
+        <v>-1.052738235144865</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-1.189603875527446</v>
+        <v>-1.070305011211822</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-1.223486075654655</v>
+        <v>-1.23148137562216</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-1.145936557993821</v>
+        <v>-1.132528981732996</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-1.192661742727807</v>
+        <v>-1.237124328143523</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-1.174398406109177</v>
+        <v>-1.225148406588531</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.6593</t>
+          <t>X &lt; 0.6581</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1806</v>
+        <v>1847</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-2.163823043410083</v>
+        <v>-2.195643969489915</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-2.032547830774668</v>
+        <v>-1.982603644677006</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-2.018243179870815</v>
+        <v>-1.968794008748119</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.770432596693865</v>
+        <v>-1.669089119776004</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-2.186071663329102</v>
+        <v>-2.07749470007797</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.640204590896303</v>
+        <v>-1.51330356123033</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-2.107743166841644</v>
+        <v>-2.008795870307701</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.916465524947952</v>
+        <v>-1.743386113315808</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.624753554093466</v>
+        <v>-1.477410195655004</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.092194056595417</v>
+        <v>-1.918697793879794</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.787350687352699</v>
+        <v>-1.64646277927546</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.760103613332362</v>
+        <v>-1.54405177218748</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.64080885417669</v>
+        <v>-1.413681301657739</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.719990180836263</v>
+        <v>-1.499489808136872</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-1.441494359959528</v>
+        <v>-1.207090860298052</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-1.31093180982927</v>
+        <v>-1.078921654689005</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-1.357613003530481</v>
+        <v>-1.128660214762675</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-1.761434942945961</v>
+        <v>-1.532253578180921</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-1.237455754253787</v>
+        <v>-1.047082092778503</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-1.349916514630898</v>
+        <v>-1.157346757627487</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-1.473471084418385</v>
+        <v>-1.34579829744893</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-1.295791164907612</v>
+        <v>-1.150251561147584</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-1.376253741532317</v>
+        <v>-1.285610037428498</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-1.475190434791607</v>
+        <v>-1.339465328415301</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.7011</t>
+          <t>X &lt; 0.6999</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1962</v>
+        <v>1997</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.322298726335191</v>
+        <v>-1.4250382876522</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.9246909818775961</v>
+        <v>-1.04675888784238</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.9736833240822023</v>
+        <v>-1.078140383910537</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.154360735934468</v>
+        <v>-1.194512100043212</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.209862200277534</v>
+        <v>-1.193264889286603</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.096037739671551</v>
+        <v>-1.05894970331083</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.536753165964818</v>
+        <v>-1.576822667719803</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.382232887508671</v>
+        <v>-1.404256854256857</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.363041581855178</v>
+        <v>-1.348639100150542</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.500047864154162</v>
+        <v>-1.366223283635932</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.399971523904448</v>
+        <v>-1.266168461241833</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.4980909330679</v>
+        <v>-1.192224627030114</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.121981393069206</v>
+        <v>-0.8549384770797772</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.364337346976704</v>
+        <v>-1.153247651181893</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-1.362916971294958</v>
+        <v>-1.034200230362892</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-1.14482387325026</v>
+        <v>-0.8734971128952651</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-1.147545036080231</v>
+        <v>-0.8772272992822536</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-1.476747493422458</v>
+        <v>-1.210411855119872</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-1.027896423979023</v>
+        <v>-0.7956491772980812</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-1.269095035676514</v>
+        <v>-1.031738746260132</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-1.324090759579477</v>
+        <v>-1.148507233619831</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-1.421054759161699</v>
+        <v>-1.173594642906117</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-1.473374211228901</v>
+        <v>-1.330561058979775</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-1.417618156182421</v>
+        <v>-1.292399602593221</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.743</t>
+          <t>X &lt; 0.7416</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2166</v>
+        <v>2200</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.105442819233701</v>
+        <v>-1.213363951086635</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.004874368820175</v>
+        <v>-1.073601437117631</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.7725821469124483</v>
+        <v>-0.7652738404457509</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.8658467515272434</v>
+        <v>-0.7443255166881855</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.130579672482426</v>
+        <v>-1.040322576430547</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.6893406806248166</v>
+        <v>-0.6318609262673789</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.069358040380457</v>
+        <v>-1.03913232921559</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.9552789205550667</v>
+        <v>-0.8651461464528722</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.6128424940393558</v>
+        <v>-0.5302317121623972</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.130404384883462</v>
+        <v>-0.9828699030073551</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.10557530467446</v>
+        <v>-0.9121162561736682</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.312388355990855</v>
+        <v>-1.02672637965906</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.9395700318066531</v>
+        <v>-0.6416184971098318</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.363661182294692</v>
+        <v>-1.026216194906574</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-1.259486190490527</v>
+        <v>-0.9356433040643566</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-1.328022636670283</v>
+        <v>-0.9197938306992341</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-1.113048068938596</v>
+        <v>-0.7509469696969759</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-1.55928353977739</v>
+        <v>-1.20201289304039</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-1.040237312574519</v>
+        <v>-0.7148233931673502</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-1.102952642644752</v>
+        <v>-0.7729642208356324</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-1.203727134733889</v>
+        <v>-0.9767723585799999</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-1.483150339384309</v>
+        <v>-1.233753062353472</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-1.597027745310371</v>
+        <v>-1.444664031620547</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-1.646058240781493</v>
+        <v>-1.515893935000925</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.7848</t>
+          <t>X &lt; 0.7834</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2389</v>
+        <v>2415</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.2411787883905063</v>
+        <v>-0.3493840416664327</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.5538072382023529</v>
+        <v>-0.5733645613412648</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.7248462803148428</v>
+        <v>-0.6927122017885239</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.3773234227627711</v>
+        <v>-0.3963559371215339</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.6899622036333568</v>
+        <v>-0.6903873442751873</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.4798250888906992</v>
+        <v>-0.4693658767327733</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.6882677062067302</v>
+        <v>-0.7459493806954143</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.6519847217521644</v>
+        <v>-0.6145874327692553</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.6701175079432744</v>
+        <v>-0.5874275725181874</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.0033269930911</v>
+        <v>-0.8226275787499091</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.7887787235784813</v>
+        <v>-0.5683074371860997</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.085439759044903</v>
+        <v>-0.7386469094603783</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.7681950509461473</v>
+        <v>-0.4876449871760471</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.089975608648814</v>
+        <v>-0.7532065958100063</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-1.056577636427278</v>
+        <v>-0.7314272302830673</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.9799180794174518</v>
+        <v>-0.6670176214012926</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.7555339731185171</v>
+        <v>-0.4810429606625277</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-1.086325374169945</v>
+        <v>-0.7795585358034245</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.7624046994125635</v>
+        <v>-0.4822805736679996</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.8853248072338573</v>
+        <v>-0.5989570685676142</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.9017754932549238</v>
+        <v>-0.6280992925156355</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.9947914721068045</v>
+        <v>-0.7446696819657461</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-1.323275203860362</v>
+        <v>-1.20496894409937</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-1.081683279673584</v>
+        <v>-1.03584499843025</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.8266</t>
+          <t>X &lt; 0.8252</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2607</v>
+        <v>2637</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.04736581432468512</v>
+        <v>0.04227893226676116</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.03730876223875867</v>
+        <v>0.0431010152719864</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.2766566594429136</v>
+        <v>-0.1716264572468305</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.02110001251190141</v>
+        <v>0.1256092741332537</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.2552282753465747</v>
+        <v>-0.166667974379294</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.1230403143244558</v>
+        <v>-0.06427330220720506</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.2257236091323449</v>
+        <v>-0.2709702988966569</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.3678993518871465</v>
+        <v>-0.3654184130915183</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.3428280044333647</v>
+        <v>-0.2918086410148462</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.4454112629921738</v>
+        <v>-0.3470670581184834</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.4165380335682372</v>
+        <v>-0.280447455490787</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.5206534499166793</v>
+        <v>-0.2701898127776516</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.2849381118068521</v>
+        <v>0.001292799326868987</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.7892038726226431</v>
+        <v>-0.4522340526650481</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.8133193656460804</v>
+        <v>-0.4517945778948018</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.9228518454139802</v>
+        <v>-0.5730844157304418</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.7665827371258587</v>
+        <v>-0.4494335419036872</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.9637169612801699</v>
+        <v>-0.6202395279905701</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.7636200911333191</v>
+        <v>-0.4057773008447967</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.784078400913117</v>
+        <v>-0.4187221413375752</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.9593748986804087</v>
+        <v>-0.6069478334653766</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.9743205577173839</v>
+        <v>-0.7200322363459577</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-1.175708656128251</v>
+        <v>-0.9693822030964014</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.9989617277710181</v>
+        <v>-0.9039899118341026</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.8685</t>
+          <t>X &lt; 0.8669</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2838</v>
+        <v>2853</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.01172191837509473</v>
+        <v>-0.2116187057876076</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.2343651705230343</v>
+        <v>-0.334241868071274</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.4643599947407182</v>
+        <v>-0.4184458157933051</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.03155557397821696</v>
+        <v>-0.0490376857433148</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.3195803124457655</v>
+        <v>-0.3401087171529085</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.217998297517731</v>
+        <v>-0.2685800450166411</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.05962914499155403</v>
+        <v>-0.06558946921943942</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.1376281351346904</v>
+        <v>0.1737151737151663</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.3745107637828369</v>
+        <v>0.4614999672845386</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.2178849211885634</v>
+        <v>0.3152692655962852</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.0838972834363787</v>
+        <v>0.04772046805690877</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.3774891244408991</v>
+        <v>-0.1737852031884657</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.1115026442537328</v>
+        <v>0.2025146027150413</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.3469518300144614</v>
+        <v>0.009937210202693336</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.4223557567611351</v>
+        <v>-0.05570830741011434</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.509753188952061</v>
+        <v>-0.1954207624775819</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.4120499590470246</v>
+        <v>-0.08899623203645035</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.5664013646447046</v>
+        <v>-0.2569311608924139</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.3297072916887842</v>
+        <v>0.02763271364207043</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.3331630805462709</v>
+        <v>0.03191421653491489</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.7493549526520198</v>
+        <v>-0.3602761663740282</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.7691801715136179</v>
+        <v>-0.4704895120236756</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.7204346138123014</v>
+        <v>-0.4371599689114376</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.7755025258013717</v>
+        <v>-0.5642481395065388</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.9103</t>
+          <t>X &lt; 0.9087</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3017</v>
+        <v>3042</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.1868997450109191</v>
+        <v>-0.2725155443303535</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.3066538558423204</v>
+        <v>-0.206590482362067</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.4103513215764352</v>
+        <v>-0.3966308070673108</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.1503045864458343</v>
+        <v>-0.05461513456337741</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.1053387044496858</v>
+        <v>-0.05002232026521369</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.03159919092287566</v>
+        <v>-0.03856491286380503</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.03898469673450222</v>
+        <v>-0.06178726274863777</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.0103895904737783</v>
+        <v>-0.05320801780979423</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.2027131744286592</v>
+        <v>0.2244917275583944</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.1416044292360752</v>
+        <v>0.1686668048782991</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.06017797008097858</v>
+        <v>0.03332014174137754</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.4519274487098102</v>
+        <v>-0.3229193563574384</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.3671602645084562</v>
+        <v>-0.1714937433343806</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.4697000919120597</v>
+        <v>-0.2363221808746303</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.2821936074363975</v>
+        <v>-0.01221719009947009</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.2961432506887007</v>
+        <v>-0.02286197517388189</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.3112860643463975</v>
+        <v>-0.04160502958580281</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.3965130308065739</v>
+        <v>-0.1087429151550339</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.260266937182152</v>
+        <v>0.007099982602191801</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.3517288741547446</v>
+        <v>-0.07417156050451013</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.6098531915428111</v>
+        <v>-0.3128849639233806</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.7323243895878804</v>
+        <v>-0.4866668152672204</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.6370439165493593</v>
+        <v>-0.4073978789697819</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.7264616549831331</v>
+        <v>-0.5695368732592456</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.9521</t>
+          <t>X &lt; 0.9504</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3137</v>
+        <v>3161</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.1914800248243793</v>
+        <v>-0.2386619704013455</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.3194035888947866</v>
+        <v>-0.2789333120045825</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.1571515105277754</v>
+        <v>-0.09990272867834449</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.06599091964946524</v>
+        <v>0.143897694540847</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.096547908413946</v>
+        <v>0.1694673198980468</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.2697451358302558</v>
+        <v>0.2495275112489566</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.2132514825050649</v>
+        <v>0.1026181919260409</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.1752115003060908</v>
+        <v>0.06784973672390038</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.2666672078856678</v>
+        <v>0.2452808882348236</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.4640945218273771</v>
+        <v>0.4454337504887604</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.2487957844373341</v>
+        <v>0.2624818374385072</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.04328110518666506</v>
+        <v>0.03563547698762193</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.1314945003319963</v>
+        <v>0.01283507206263579</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.270255814904651</v>
+        <v>-0.09048447007531735</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.1149421243163715</v>
+        <v>0.09929520875026299</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.1374235197764548</v>
+        <v>0.07876909862562798</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.1570492211782621</v>
+        <v>0.05682716635040208</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.1793424974189435</v>
+        <v>0.06920450076479057</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.07181231563113499</v>
+        <v>0.1887600528077513</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.2480926593995108</v>
+        <v>0.02371979745547037</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.3578179276966935</v>
+        <v>-0.06919132841118625</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.4784264103355156</v>
+        <v>-0.2076249671016797</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.5036822002949535</v>
+        <v>-0.2487105071317544</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.4969049690310641</v>
+        <v>-0.3159428263183912</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.994</t>
+          <t>X &lt; 0.9922</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3234</v>
+        <v>3259</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.06393584539389252</v>
+        <v>-0.09540281108802162</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.2901202262780913</v>
+        <v>-0.233452697168147</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.2062696889233706</v>
+        <v>-0.1286977511761265</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.1032411105566808</v>
+        <v>-0.002042078254731905</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.008562439604219207</v>
+        <v>0.07537277730452985</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.05914207892805479</v>
+        <v>0.09664691516388757</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.1657952293488805</v>
+        <v>0.1438176233815938</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.002504472271915859</v>
+        <v>-0.02148400191813238</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.08740470931132904</v>
+        <v>0.1238249606260311</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.2557979923027744</v>
+        <v>0.2934663846190517</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.1474470424972836</v>
+        <v>0.2161958440900946</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.07138722539857412</v>
+        <v>0.1714676821713681</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.04772766522452798</v>
+        <v>0.1458891575135723</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.2814029861679117</v>
+        <v>-0.05371167033467117</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.1504237004589513</v>
+        <v>0.1093656085916166</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.1853046192959837</v>
+        <v>0.07602708145633841</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.1466563775784806</v>
+        <v>0.08222843858573015</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.2331461685203138</v>
+        <v>0.0288281763471403</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.153261175789261</v>
+        <v>0.1080990831293676</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.256922066792896</v>
+        <v>0.01593706193068556</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.3796199815760986</v>
+        <v>-0.06070989343778166</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.4988934325383454</v>
+        <v>-0.2404059675949028</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.391520662462348</v>
+        <v>-0.1501927771922453</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.3871865228674309</v>
+        <v>-0.2202789945562813</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 1.036</t>
+          <t>X &lt; 1.034</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3291</v>
+        <v>3313</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.2310704085436086</v>
+        <v>-0.1393283772860059</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.2780688257570318</v>
+        <v>-0.1592594186435008</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2807927192668771</v>
+        <v>-0.0777311160510763</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.1616317129646703</v>
+        <v>0.03663904304875842</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.08776509630732221</v>
+        <v>0.07800443009068658</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.03486520747301114</v>
+        <v>0.07157142721030141</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.00383911625476685</v>
+        <v>0.0442352322878321</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.1438456832230415</v>
+        <v>-0.09343954656454656</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.1153101843960229</v>
+        <v>-0.008564193445614876</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.02372698478075819</v>
+        <v>0.1144215223245624</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.0952989155895736</v>
+        <v>0.04308865751900726</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.1143790331363448</v>
+        <v>0.05450105716404607</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.2205976352384909</v>
+        <v>0.01020214688656296</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.3329324147198065</v>
+        <v>-0.06986459948213053</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.2459020734581472</v>
+        <v>0.04858926553406917</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.2699394674235478</v>
+        <v>0.0254416567049276</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.2342993704706799</v>
+        <v>-0.0003923119413542508</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.2908023992126374</v>
+        <v>-0.08532156748830744</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.1479032353965408</v>
+        <v>0.1168289761696855</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.276886056629067</v>
+        <v>-0.04278547316593517</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.3157804845941996</v>
+        <v>-0.00709366574087511</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.4950177356167274</v>
+        <v>-0.2453395151163917</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.4151271385619637</v>
+        <v>-0.1347117630080561</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.3818027500660293</v>
+        <v>-0.188464799090049</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 1.078</t>
+          <t>X &lt; 1.076</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3336</v>
+        <v>3361</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.1427822131640255</v>
+        <v>-0.1284972572267691</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.2233904394768373</v>
+        <v>-0.1220640191663378</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.2155494249176328</v>
+        <v>-0.08907209043245956</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.1671214141053383</v>
+        <v>-0.01432808936634444</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.1285573484808822</v>
+        <v>0.02252019307801589</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.01424058692008145</v>
+        <v>0.07759876893924655</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.05363299861245707</v>
+        <v>0.009739692201804928</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.1060109896209056</v>
+        <v>-0.04146064572605468</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.1668157890831949</v>
+        <v>-0.04484646309127527</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.1167113820079351</v>
+        <v>0.005777051019997259</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.1239475599393316</v>
+        <v>0.02824276722256513</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.05692067823578384</v>
+        <v>0.1245191719423744</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.02740728080372179</v>
+        <v>0.1836559021782165</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.1710332419972431</v>
+        <v>0.07157177380128132</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.1238746240764357</v>
+        <v>0.1489785151968306</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.1395534290271172</v>
+        <v>0.1341901900306226</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.1659832361988194</v>
+        <v>0.07757585882585261</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.2231166896099239</v>
+        <v>0.02169477184374102</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.1690076079609995</v>
+        <v>0.1348996920683732</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.2039212124176473</v>
+        <v>0.06980953335310858</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.2196324608247693</v>
+        <v>0.1266218690710659</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.337530959283967</v>
+        <v>-0.04978582530862496</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.2849362052107622</v>
+        <v>0.03305485865039515</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.2230692081848531</v>
+        <v>0.007556877798300832</v>
       </c>
     </row>
   </sheetData>
